--- a/stories/arbres/TREE-COL-029.xlsx
+++ b/stories/arbres/TREE-COL-029.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Sara est avec maman, à la ferme. Sara a envie de jouer. maman est là, tout près. On va apprendre : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara écoute maman. Sara entend les mots : écouter, si malaise raconter à la maison.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sara va vers le bac à sable. Le sol est un peu froid. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Sara se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On range un objet. maman dit : je suis là. On reste ensemble.</t>
+          <t>Sara va vers le bac à sable. Le sol est un peu froid. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Sara se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On range un objet. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Sara va vers le bac à sable. Le sol est un peu froid. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Sara se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On range un objet.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1862,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2035,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara respire. Sara retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2183,6 +2226,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2345,6 +2393,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le ballon. L'eau coule, tout petit bruit. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara répète tout bas : écouter, si malaise raconter à la maison. On écoute jusqu'au bout. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2533,6 +2586,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -2697,6 +2755,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Tom. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de le bac à sable, le ballon et Tom. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2859,6 +2922,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3021,6 +3089,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Léa. Un chat miaule une fois. On dit merci. Cette fin-là est celle de le bac à sable, le ballon et Léa. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3183,6 +3256,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3345,6 +3423,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Sami. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon et Sami. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3507,6 +3590,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3669,6 +3757,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le seau. Un vélo passe au loin. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara répète tout bas : écouter, si malaise raconter à la maison. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3857,6 +3950,11 @@
       <c r="AV17" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -4021,6 +4119,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Tom. Un chat miaule une fois. On range un objet. Cette fin-là est celle de le bac à sable, le seau et Tom. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4183,6 +4286,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4345,6 +4453,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Léa. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de le bac à sable, le seau et Léa. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4507,6 +4620,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4669,6 +4787,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Sami. La couverture est douce. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau et Sami. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4831,6 +4954,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4993,6 +5121,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le doudou. La lumière est claire. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara répète tout bas : écouter, si malaise raconter à la maison. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5181,6 +5314,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -5345,6 +5483,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Tom. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de le bac à sable, le doudou et Tom. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5507,6 +5650,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5669,6 +5817,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Léa. La couverture est douce. On dit merci. Cette fin-là est celle de le bac à sable, le doudou et Léa. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5831,6 +5984,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5993,6 +6151,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Sami. On entend un oiseau. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Sami. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6155,6 +6318,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6179,7 +6347,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Sara va vers le toboggan. Une feuille tombe. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Sara se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On dit merci. maman dit : je suis là. On reste ensemble.</t>
+          <t>Sara va vers le toboggan. Une feuille tombe. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Sara se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On dit merci. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6317,6 +6485,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Sara va vers le toboggan. Une feuille tombe. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Sara se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On dit merci.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6497,6 +6671,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
         </is>
       </c>
     </row>
@@ -6665,6 +6844,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara respire. Sara retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6851,6 +7035,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7013,6 +7202,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le ballon. Il y a des miettes sur la table. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara répète tout bas : écouter, si malaise raconter à la maison. On écoute jusqu'au bout. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7201,6 +7395,11 @@
       <c r="AV37" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -7365,6 +7564,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Tom. Un chat miaule une fois. On dit merci. Cette fin-là est celle de le toboggan, le ballon et Tom. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7527,6 +7731,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7689,6 +7898,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Léa. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de le toboggan, le ballon et Léa. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7851,6 +8065,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8013,6 +8232,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Sami. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon et Sami. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8175,6 +8399,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8337,6 +8566,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le seau. Un chat miaule une fois. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara répète tout bas : écouter, si malaise raconter à la maison. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8525,6 +8759,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -8689,6 +8928,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Tom. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de le toboggan, le seau et Tom. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8851,6 +9095,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9013,6 +9262,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Léa. La couverture est douce. On souffle doucement. Cette fin-là est celle de le toboggan, le seau et Léa. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9175,6 +9429,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9337,6 +9596,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Sami. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau et Sami. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9499,6 +9763,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9661,6 +9930,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le doudou. Les chaussures font toc toc. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara répète tout bas : écouter, si malaise raconter à la maison. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9849,6 +10123,11 @@
       <c r="AV53" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -10013,6 +10292,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Tom. La couverture est douce. On dit merci. Cette fin-là est celle de le toboggan, le doudou et Tom. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10175,6 +10459,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10337,6 +10626,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Léa. On entend un oiseau. On souffle doucement. Cette fin-là est celle de le toboggan, le doudou et Léa. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10499,6 +10793,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10661,6 +10960,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Sami. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Sami. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10823,6 +11127,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10847,7 +11156,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Sara va vers les balançoires. L'eau coule, tout petit bruit. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Sara se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On souffle doucement. maman dit : je suis là. On reste ensemble.</t>
+          <t>Sara va vers les balançoires. L'eau coule, tout petit bruit. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Sara se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On souffle doucement. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10985,6 +11294,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Sara va vers les balançoires. L'eau coule, tout petit bruit. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Sara se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On souffle doucement.
+maman|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11165,6 +11480,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
         </is>
       </c>
     </row>
@@ -11333,6 +11653,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara respire. Sara retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11519,6 +11844,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11681,6 +12011,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le ballon. La couverture est douce. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara répète tout bas : écouter, si malaise raconter à la maison. On écoute jusqu'au bout. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11869,6 +12204,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -12033,6 +12373,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Tom. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de les balançoires, le ballon et Tom. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12195,6 +12540,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12357,6 +12707,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Léa. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le ballon et Léa. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12519,6 +12874,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12681,6 +13041,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Sami. On entend un oiseau. On attend son tour. Cette fin-là est celle de les balançoires, le ballon et Sami. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12843,6 +13208,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13005,6 +13375,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le seau. On entend un oiseau. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara répète tout bas : écouter, si malaise raconter à la maison. On attend son tour. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13193,6 +13568,11 @@
       <c r="AV73" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -13357,6 +13737,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Tom. La couverture est douce. On souffle doucement. Cette fin-là est celle de les balançoires, le seau et Tom. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13519,6 +13904,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13681,6 +14071,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Léa. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le seau et Léa. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13843,6 +14238,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14005,6 +14405,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Sami. Ça sent le pain chaud. On attend son tour. Cette fin-là est celle de les balançoires, le seau et Sami. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14167,6 +14572,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14329,6 +14739,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Sara a choisi le doudou. Ça sent le pain chaud. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara répète tout bas : écouter, si malaise raconter à la maison. On montre du doigt, sans courir. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14517,6 +14932,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -14681,6 +15101,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Tom. On entend un oiseau. On souffle doucement. Cette fin-là est celle de les balançoires, le doudou et Tom. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14843,6 +15268,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15005,6 +15435,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Léa. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le doudou et Léa. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15167,6 +15602,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15329,6 +15769,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Sara rejoint Sami. Le vent est doux. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Sami. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15491,6 +15936,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15509,7 +15959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15582,6 +16032,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-COL-029.xlsx
+++ b/stories/arbres/TREE-COL-029.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Sara est avec maman, à la ferme. Sara a envie de jouer. maman est là, tout près. On va apprendre : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara écoute maman. Sara entend les mots : écouter, si malaise raconter à la maison.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1682,6 +1689,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1869,6 +1877,7 @@
           <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2040,6 +2049,7 @@
           <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara respire. Sara retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2231,6 +2241,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2398,6 +2409,7 @@
           <t>narrateur|Sara a choisi le ballon. L'eau coule, tout petit bruit. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara répète tout bas : écouter, si malaise raconter à la maison. On écoute jusqu'au bout. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2593,6 +2605,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2760,6 +2773,7 @@
           <t>narrateur|Sara rejoint Tom. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de le bac à sable, le ballon et Tom. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2927,6 +2941,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3094,6 +3109,7 @@
           <t>narrateur|Sara rejoint Léa. Un chat miaule une fois. On dit merci. Cette fin-là est celle de le bac à sable, le ballon et Léa. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3261,6 +3277,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3428,6 +3445,7 @@
           <t>narrateur|Sara rejoint Sami. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon et Sami. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3595,6 +3613,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3762,6 +3781,7 @@
           <t>narrateur|Sara a choisi le seau. Un vélo passe au loin. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara répète tout bas : écouter, si malaise raconter à la maison. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3957,6 +3977,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4124,6 +4145,7 @@
           <t>narrateur|Sara rejoint Tom. Un chat miaule une fois. On range un objet. Cette fin-là est celle de le bac à sable, le seau et Tom. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4291,6 +4313,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4458,6 +4481,7 @@
           <t>narrateur|Sara rejoint Léa. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de le bac à sable, le seau et Léa. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4625,6 +4649,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4792,6 +4817,7 @@
           <t>narrateur|Sara rejoint Sami. La couverture est douce. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau et Sami. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4959,6 +4985,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5126,6 +5153,7 @@
           <t>narrateur|Sara a choisi le doudou. La lumière est claire. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara répète tout bas : écouter, si malaise raconter à la maison. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5321,6 +5349,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5488,6 +5517,7 @@
           <t>narrateur|Sara rejoint Tom. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de le bac à sable, le doudou et Tom. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5655,6 +5685,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5822,6 +5853,7 @@
           <t>narrateur|Sara rejoint Léa. La couverture est douce. On dit merci. Cette fin-là est celle de le bac à sable, le doudou et Léa. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5989,6 +6021,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6156,6 +6189,7 @@
           <t>narrateur|Sara rejoint Sami. On entend un oiseau. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Sami. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6323,6 +6357,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6491,6 +6526,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6678,6 +6714,7 @@
           <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6849,6 +6886,7 @@
           <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara respire. Sara retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7040,6 +7078,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7207,6 +7246,7 @@
           <t>narrateur|Sara a choisi le ballon. Il y a des miettes sur la table. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara répète tout bas : écouter, si malaise raconter à la maison. On écoute jusqu'au bout. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7402,6 +7442,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7569,6 +7610,7 @@
           <t>narrateur|Sara rejoint Tom. Un chat miaule une fois. On dit merci. Cette fin-là est celle de le toboggan, le ballon et Tom. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7736,6 +7778,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7903,6 +7946,7 @@
           <t>narrateur|Sara rejoint Léa. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de le toboggan, le ballon et Léa. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8070,6 +8114,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8237,6 +8282,7 @@
           <t>narrateur|Sara rejoint Sami. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon et Sami. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8404,6 +8450,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8571,6 +8618,7 @@
           <t>narrateur|Sara a choisi le seau. Un chat miaule une fois. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara répète tout bas : écouter, si malaise raconter à la maison. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8766,6 +8814,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8933,6 +8982,7 @@
           <t>narrateur|Sara rejoint Tom. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de le toboggan, le seau et Tom. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9100,6 +9150,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9267,6 +9318,7 @@
           <t>narrateur|Sara rejoint Léa. La couverture est douce. On souffle doucement. Cette fin-là est celle de le toboggan, le seau et Léa. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9434,6 +9486,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9601,6 +9654,7 @@
           <t>narrateur|Sara rejoint Sami. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau et Sami. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9768,6 +9822,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9935,6 +9990,7 @@
           <t>narrateur|Sara a choisi le doudou. Les chaussures font toc toc. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara répète tout bas : écouter, si malaise raconter à la maison. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10130,6 +10186,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10297,6 +10354,7 @@
           <t>narrateur|Sara rejoint Tom. La couverture est douce. On dit merci. Cette fin-là est celle de le toboggan, le doudou et Tom. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10464,6 +10522,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10631,6 +10690,7 @@
           <t>narrateur|Sara rejoint Léa. On entend un oiseau. On souffle doucement. Cette fin-là est celle de le toboggan, le doudou et Léa. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10798,6 +10858,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10965,6 +11026,7 @@
           <t>narrateur|Sara rejoint Sami. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Sami. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11132,6 +11194,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11300,6 +11363,7 @@
 maman|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11487,6 +11551,7 @@
           <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11658,6 +11723,7 @@
           <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara respire. Sara retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11849,6 +11915,7 @@
           <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12016,6 +12083,7 @@
           <t>narrateur|Sara a choisi le ballon. La couverture est douce. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara répète tout bas : écouter, si malaise raconter à la maison. On écoute jusqu'au bout. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12211,6 +12279,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12378,6 +12447,7 @@
           <t>narrateur|Sara rejoint Tom. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de les balançoires, le ballon et Tom. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12545,6 +12615,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12712,6 +12783,7 @@
           <t>narrateur|Sara rejoint Léa. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le ballon et Léa. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12879,6 +12951,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13046,6 +13119,7 @@
           <t>narrateur|Sara rejoint Sami. On entend un oiseau. On attend son tour. Cette fin-là est celle de les balançoires, le ballon et Sami. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13213,6 +13287,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13380,6 +13455,7 @@
           <t>narrateur|Sara a choisi le seau. On entend un oiseau. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara répète tout bas : écouter, si malaise raconter à la maison. On attend son tour. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13575,6 +13651,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13742,6 +13819,7 @@
           <t>narrateur|Sara rejoint Tom. La couverture est douce. On souffle doucement. Cette fin-là est celle de les balançoires, le seau et Tom. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13909,6 +13987,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14076,6 +14155,7 @@
           <t>narrateur|Sara rejoint Léa. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le seau et Léa. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14243,6 +14323,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14410,6 +14491,7 @@
           <t>narrateur|Sara rejoint Sami. Ça sent le pain chaud. On attend son tour. Cette fin-là est celle de les balançoires, le seau et Sami. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14577,6 +14659,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14744,6 +14827,7 @@
           <t>narrateur|Sara a choisi le doudou. Ça sent le pain chaud. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara répète tout bas : écouter, si malaise raconter à la maison. On montre du doigt, sans courir. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14939,6 +15023,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15106,6 +15191,7 @@
           <t>narrateur|Sara rejoint Tom. On entend un oiseau. On souffle doucement. Cette fin-là est celle de les balançoires, le doudou et Tom. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15273,6 +15359,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15440,6 +15527,7 @@
           <t>narrateur|Sara rejoint Léa. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le doudou et Léa. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15607,6 +15695,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15774,6 +15863,7 @@
           <t>narrateur|Sara rejoint Sami. Le vent est doux. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Sami. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15941,6 +16031,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15959,7 +16050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16039,6 +16130,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16053,7 +16158,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16240,6 +16345,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-COL-029.xlsx
+++ b/stories/arbres/TREE-COL-029.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Écouter la maîtresse, en parler à la maison — à la ferme</t>
+          <t>Le foin et le gilet d'école</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>À la ferme, Sarah a encore son gilet d'école. Elle écoute la maîtresse. Si le ventre se serre, elle raconte à papa ou maman.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aujourd'hui, Sara est avec maman, à la ferme. Sara a envie de jouer. maman est là, tout près. On va apprendre : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara écoute maman. Sara entend les mots : écouter, si malaise raconter à la maison.</t>
+          <t>Une paille d'or colle encore au bois de la barrière. Le coq a chanté, tout loin, derrière le hangar. Ça sent le foin tiède et le lait. Une botte de Sarah est encore mouillée, près du seau. Le seau a une goutte qui tremble. Dehors, le pré est vert, tout plat. Une mouche tourne près de la porte de l'étable. Maman étend un linge rayé sur la corde. Le linge claque une fois, tout doux. Papa rentre avec un panier d'œufs. Les œufs sont chauds, tout blancs. Sarah, tu as encore ton gilet d'école. Il sent la craie, un peu. La ferme est calme, ce soir-là. En ce moment, Sarah pose la main sur la barrière. Le bois est rêche, puis chaud. La maîtresse a parlé, ce matin. Sarah écoute encore, dans sa tête. J'ai écouté, maman. Oui. On écoute la maîtresse. Et si le ventre se serre ? On raconte à papa ou maman, à la maison. À la ferme aussi, on raconte. Le bac à sable attend, près du pré. Le toboggan brille un peu. Les balançoires bougent, tout doux. Papa, on va là-bas ? On y va. On t'écoute, Sarah.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,10 +1337,43 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Aujourd'hui, Sara est avec maman, à la ferme. Sara a envie de jouer. maman est là, tout près. On va apprendre : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara écoute maman. Sara entend les mots : écouter, si malaise raconter à la maison.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Une paille d'or colle encore au bois de la barrière.
+narrateur|Le coq a chanté, tout loin, derrière le hangar.
+narrateur|Ça sent le foin tiède et le lait.
+narrateur|Une botte de Sarah est encore mouillée, près du seau.
+narrateur|Le seau a une goutte qui tremble.
+narrateur|Dehors, le pré est vert, tout plat.
+narrateur|Une mouche tourne près de la porte de l'étable.
+narrateur|Maman étend un linge rayé sur la corde.
+narrateur|Le linge claque une fois, tout doux.
+narrateur|Papa rentre avec un panier d'œufs.
+narrateur|Les œufs sont chauds, tout blancs.
+maman|Sarah, tu as encore ton gilet d'école.
+maman|Il sent la craie, un peu.
+papa|La ferme est calme, ce soir-là.
+narrateur|En ce moment, Sarah pose la main sur la barrière.
+narrateur|Le bois est rêche, puis chaud.
+narrateur|La maîtresse a parlé, ce matin.
+narrateur|Sarah écoute encore, dans sa tête.
+enfant-f|J'ai écouté, maman.
+maman|Oui.
+maman|On écoute la maîtresse.
+papa|Et si le ventre se serre ?
+maman|On raconte à papa ou maman, à la maison.
+papa|À la ferme aussi, on raconte.
+narrateur|Le bac à sable attend, près du pré.
+narrateur|Le toboggan brille un peu.
+narrateur|Les balançoires bougent, tout doux.
+enfant-f|Papa, on va là-bas ?
+papa|On y va.
+maman|On t'écoute, Sarah.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>coq,foin</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1353,7 +1398,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+          <t>Où va Sarah, près du pré ? Le bac à sable, le toboggan, ou les balançoires ? On écoute. Et on raconte, si malaise.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1517,7 +1562,10 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+          <t>narrateur|Où va Sarah, près du pré ?
+papa|Le bac à sable, le toboggan, ou les balançoires ?
+maman|On écoute.
+maman|Et on raconte, si malaise.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1545,7 +1593,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sara va vers le bac à sable. Le sol est un peu froid. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Sara se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On range un objet. Je suis là. On reste ensemble.</t>
+          <t>Sarah va vers le bac à sable. Le sable est frais, un peu humide. Le bois du rebord est gris, tout lisse. Une petite pelle rouge attend dedans. Viens, Sarah. Le sable est doux, aujourd'hui. Sarah s'assoit au bord. Le gilet d'école touche le bois. Maman, la maîtresse a parlé. Tu as écouté ? Oui. J'ai écouté jusqu'au bout. Sarah prend la pelle. Le manche est un peu rêche. Un souvenir revient, tout près. Un camarade a chuchoté, ce matin. Le ventre de Sarah se serre. Maman. J'ai eu un malaise. Il a parlé tout bas, d'un secret. Tu as bien fait de raconter. On écoute la maîtresse. Si malaise, tu viens nous le dire. Je t'écoute, moi aussi. Bravo, Sarah. Le sable coule entre les doigts. Le ventre se desserre, tout doux. Je raconte à la maison. À la ferme aussi, on raconte.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1685,11 +1733,42 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Sara va vers le bac à sable. Le sol est un peu froid. maman sourit. Ici, c'est le bac à sable. Ce n'est pas comme les autres endroits. Sara se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On range un objet.
-maman|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Sarah va vers le bac à sable.
+narrateur|Le sable est frais, un peu humide.
+narrateur|Le bois du rebord est gris, tout lisse.
+narrateur|Une petite pelle rouge attend dedans.
+maman|Viens, Sarah.
+maman|Le sable est doux, aujourd'hui.
+narrateur|Sarah s'assoit au bord.
+narrateur|Le gilet d'école touche le bois.
+enfant-f|Maman, la maîtresse a parlé.
+maman|Tu as écouté ?
+enfant-f|Oui.
+enfant-f|J'ai écouté jusqu'au bout.
+narrateur|Sarah prend la pelle.
+narrateur|Le manche est un peu rêche.
+narrateur|Un souvenir revient, tout près.
+narrateur|Un camarade a chuchoté, ce matin.
+narrateur|Le ventre de Sarah se serre.
+enfant-f|Maman.
+enfant-f|J'ai eu un malaise.
+enfant-f|Il a parlé tout bas, d'un secret.
+maman|Tu as bien fait de raconter.
+maman|On écoute la maîtresse.
+maman|Si malaise, tu viens nous le dire.
+papa|Je t'écoute, moi aussi.
+papa|Bravo, Sarah.
+narrateur|Le sable coule entre les doigts.
+narrateur|Le ventre se desserre, tout doux.
+enfant-f|Je raconte à la maison.
+maman|À la ferme aussi, on raconte.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>sable</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1714,7 +1793,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
+          <t>Sarah a un malaise, dans le sable. Elle raconte à qui ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1874,7 +1953,8 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
+          <t>narrateur|Sarah a un malaise, dans le sable.
+maman|Elle raconte à qui ?</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1902,7 +1982,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara respire. Sara retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
+          <t>Oui. On raconte à papa ou maman. Si malaise, tu viens le dire. Sarah souffle un peu. Le sable est encore frais, sous la paume. J'ai raconté. Bravo. Tu as écouté, puis tu as raconté. C'est du bon travail, Sarah. La petite pelle rouge reste dans le sable.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2046,7 +2126,16 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara respire. Sara retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
+          <t>maman|Oui.
+maman|On raconte à papa ou maman.
+papa|Si malaise, tu viens le dire.
+narrateur|Sarah souffle un peu.
+narrateur|Le sable est encore frais, sous la paume.
+enfant-f|J'ai raconté.
+maman|Bravo.
+maman|Tu as écouté, puis tu as raconté.
+papa|C'est du bon travail, Sarah.
+narrateur|La petite pelle rouge reste dans le sable.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2074,7 +2163,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>Trois jouets attendent, tout proches. Le ballon, le seau, ou le doudou ? On joue. On écoute. Et on raconte, si malaise.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2238,7 +2327,11 @@
       <c r="AV7" s="2" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>narrateur|Trois jouets attendent, tout proches.
+maman|Le ballon, le seau, ou le doudou ?
+papa|On joue.
+papa|On écoute.
+papa|Et on raconte, si malaise.</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr"/>
@@ -2266,7 +2359,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Sara a choisi le ballon. L'eau coule, tout petit bruit. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara répète tout bas : écouter, si malaise raconter à la maison. On écoute jusqu'au bout. papa n'est pas loin.</t>
+          <t>Sarah prend le ballon rouge. Le ballon est un peu sablé, tout doux. Il fait poum contre le bois. Moi, je raconte le pré. Papa parle jusqu'au bout. Sarah écoute. Le ballon est chaud. Tu as écouté. Si le ventre se serre, tu racontes. Oui, maman. Bravo. Le ballon reste près du gilet. Le ballon laisse une trace ronde dans le sable. On est encore près de le bac à sable. On écoute. Si malaise, on raconte.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2406,10 +2499,29 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Sara a choisi le ballon. L'eau coule, tout petit bruit. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara répète tout bas : écouter, si malaise raconter à la maison. On écoute jusqu'au bout. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr"/>
+          <t>narrateur|Sarah prend le ballon rouge.
+narrateur|Le ballon est un peu sablé, tout doux.
+narrateur|Il fait poum contre le bois.
+papa|Moi, je raconte le pré.
+narrateur|Papa parle jusqu'au bout.
+narrateur|Sarah écoute.
+enfant-f|Le ballon est chaud.
+maman|Tu as écouté.
+maman|Si le ventre se serre, tu racontes.
+enfant-f|Oui, maman.
+papa|Bravo.
+narrateur|Le ballon reste près du gilet.
+narrateur|Le ballon laisse une trace ronde dans le sable.
+narrateur|On est encore près de le bac à sable.
+maman|On écoute.
+maman|Si malaise, on raconte.</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>ballon</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2434,7 +2546,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Au fond du pré, trois animaux sont là. La poule, la chèvre, ou le poulain ? On écoute d'abord. Puis on raconte.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2602,7 +2714,10 @@
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Au fond du pré, trois animaux sont là.
+papa|La poule, la chèvre, ou le poulain ?
+maman|On écoute d'abord.
+maman|Puis on raconte.</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr"/>
@@ -2630,7 +2745,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Tom. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de le bac à sable, le ballon et Tom. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+          <t>La poule picore près de la haie. Elle fait cot cot, tout petit. Une plume blonde reste dans l'herbe. Sarah a encore le ballon, près de le bac à sable. Un grain de mil colle au ballon, près de la poule. On dit bonjour à la poule. Sarah écoute d'abord. Bonjour. Tu as écouté. Si malaise, tu racontes. Je raconte à la maison. Bravo, Sarah. On t'écoute. Sarah pose le ballon, tout doux. Le foin sent encore le soleil.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2770,10 +2885,28 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Tom. Il y a des miettes sur la table. On range un objet. Cette fin-là est celle de le bac à sable, le ballon et Tom. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr"/>
+          <t>narrateur|La poule picore près de la haie.
+narrateur|Elle fait cot cot, tout petit.
+narrateur|Une plume blonde reste dans l'herbe.
+narrateur|Sarah a encore le ballon, près de le bac à sable.
+narrateur|Un grain de mil colle au ballon, près de la poule.
+papa|On dit bonjour à la poule.
+narrateur|Sarah écoute d'abord.
+enfant-f|Bonjour.
+maman|Tu as écouté.
+maman|Si malaise, tu racontes.
+enfant-f|Je raconte à la maison.
+papa|Bravo, Sarah.
+papa|On t'écoute.
+narrateur|Sarah pose le ballon, tout doux.
+narrateur|Le foin sent encore le soleil.</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>poule</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2798,7 +2931,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Sarah a vu la poule, près de le bac à sable. Elle avait le ballon. Bravo, Sarah. C'est du bon travail. Merci, papa. Merci, maman. La poule picore encore un grain, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2938,7 +3071,16 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Sarah a vu la poule, près de le bac à sable.
+narrateur|Elle avait le ballon.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|La poule picore encore un grain, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2966,7 +3108,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Léa. Un chat miaule une fois. On dit merci. Cette fin-là est celle de le bac à sable, le ballon et Léa. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+          <t>La chèvre sonne sa clochette, tout léger. Elle mâche une feuille, tout lentement. Son poil est rêche, un peu chaud. Sarah a encore le ballon, près de le bac à sable. La chèvre pose le nez sur le ballon sablé. On dit bonjour à la chèvre. Sarah écoute d'abord. Bonjour. Tu as écouté. Si malaise, tu racontes. Je raconte à la maison. Bravo, Sarah. On t'écoute. Sarah pose le ballon, tout doux. Le foin sent encore le soleil.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3106,10 +3248,28 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Léa. Un chat miaule une fois. On dit merci. Cette fin-là est celle de le bac à sable, le ballon et Léa. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr"/>
+          <t>narrateur|La chèvre sonne sa clochette, tout léger.
+narrateur|Elle mâche une feuille, tout lentement.
+narrateur|Son poil est rêche, un peu chaud.
+narrateur|Sarah a encore le ballon, près de le bac à sable.
+narrateur|La chèvre pose le nez sur le ballon sablé.
+papa|On dit bonjour à la chèvre.
+narrateur|Sarah écoute d'abord.
+enfant-f|Bonjour.
+maman|Tu as écouté.
+maman|Si malaise, tu racontes.
+enfant-f|Je raconte à la maison.
+papa|Bravo, Sarah.
+papa|On t'écoute.
+narrateur|Sarah pose le ballon, tout doux.
+narrateur|Le foin sent encore le soleil.</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>clochette</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3134,7 +3294,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Sarah a vu la chèvre, près de le bac à sable. Elle avait le ballon. Bravo, Sarah. C'est du bon travail. Merci, papa. Merci, maman. La clochette sonne encore, tout léger. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3274,7 +3434,16 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Sarah a vu la chèvre, près de le bac à sable.
+narrateur|Elle avait le ballon.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|La clochette sonne encore, tout léger.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3302,7 +3471,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Sami. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon et Sami. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+          <t>Le poulain souffle par le nez, tout chaud. Sa crinière est douce, un peu en bataille. Le foin sent bon, tout près. Sarah a encore le ballon, près de le bac à sable. Le poulain recule. Le ballon reste dans le sable. On dit bonjour à le poulain. Sarah écoute d'abord. Bonjour. Tu as écouté. Si malaise, tu racontes. Je raconte à la maison. Bravo, Sarah. On t'écoute. Sarah pose le ballon, tout doux. Le foin sent encore le soleil.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3442,10 +3611,29 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Sami. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de le bac à sable, le ballon et Sami. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr"/>
+          <t>narrateur|Le poulain souffle par le nez, tout chaud.
+narrateur|Sa crinière est douce, un peu en bataille.
+narrateur|Le foin sent bon, tout près.
+narrateur|Sarah a encore le ballon, près de le bac à sable.
+narrateur|Le poulain recule.
+narrateur|Le ballon reste dans le sable.
+papa|On dit bonjour à le poulain.
+narrateur|Sarah écoute d'abord.
+enfant-f|Bonjour.
+maman|Tu as écouté.
+maman|Si malaise, tu racontes.
+enfant-f|Je raconte à la maison.
+papa|Bravo, Sarah.
+papa|On t'écoute.
+narrateur|Sarah pose le ballon, tout doux.
+narrateur|Le foin sent encore le soleil.</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>poulain,foin</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3470,7 +3658,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Sarah a vu le poulain, près de le bac à sable. Elle avait le ballon. Bravo, Sarah. C'est du bon travail. Merci, papa. Merci, maman. Le poulain pose le nez dans le foin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3610,7 +3798,16 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Sarah a vu le poulain, près de le bac à sable.
+narrateur|Elle avait le ballon.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|Le poulain pose le nez dans le foin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3638,7 +3835,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Sara a choisi le seau. Un vélo passe au loin. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara répète tout bas : écouter, si malaise raconter à la maison. On attend son tour. papa n'est pas loin.</t>
+          <t>Sarah prend le seau bleu. Un peu de sable tremble au fond. Le seau sonne, tout creux. Moi, je raconte le puits. Maman parle, tout près. Sarah écoute jusqu'au bout. Le seau est lourd. Tu as écouté. Si malaise, tu viens nous le dire. Je raconte à la maison. Bravo, Sarah. Sarah pose le seau, tout droit. Le seau fait un creux, tout propre. On est encore près de le bac à sable. On écoute. Si malaise, on raconte.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3778,10 +3975,29 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Sara a choisi le seau. Un vélo passe au loin. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara répète tout bas : écouter, si malaise raconter à la maison. On attend son tour. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr"/>
+          <t>narrateur|Sarah prend le seau bleu.
+narrateur|Un peu de sable tremble au fond.
+narrateur|Le seau sonne, tout creux.
+maman|Moi, je raconte le puits.
+narrateur|Maman parle, tout près.
+narrateur|Sarah écoute jusqu'au bout.
+enfant-f|Le seau est lourd.
+papa|Tu as écouté.
+papa|Si malaise, tu viens nous le dire.
+enfant-f|Je raconte à la maison.
+maman|Bravo, Sarah.
+narrateur|Sarah pose le seau, tout droit.
+narrateur|Le seau fait un creux, tout propre.
+narrateur|On est encore près de le bac à sable.
+maman|On écoute.
+maman|Si malaise, on raconte.</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>seau</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3806,7 +4022,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Au fond du pré, trois animaux sont là. La poule, la chèvre, ou le poulain ? On écoute d'abord. Puis on raconte.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3974,7 +4190,10 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Au fond du pré, trois animaux sont là.
+papa|La poule, la chèvre, ou le poulain ?
+maman|On écoute d'abord.
+maman|Puis on raconte.</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr"/>
@@ -4002,7 +4221,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Tom. Un chat miaule une fois. On range un objet. Cette fin-là est celle de le bac à sable, le seau et Tom. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+          <t>La poule picore près de la haie. Elle fait cot cot, tout petit. Une plume blonde reste dans l'herbe. Sarah a encore le seau, près de le bac à sable. La poule regarde le seau, puis picore ailleurs. On dit bonjour à la poule. Sarah écoute d'abord. Bonjour. Tu as écouté. Si malaise, tu racontes. Je raconte à la maison. Bravo, Sarah. On t'écoute. Sarah pose le seau, tout doux. Le foin sent encore le soleil.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4142,10 +4361,28 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Tom. Un chat miaule une fois. On range un objet. Cette fin-là est celle de le bac à sable, le seau et Tom. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr"/>
+          <t>narrateur|La poule picore près de la haie.
+narrateur|Elle fait cot cot, tout petit.
+narrateur|Une plume blonde reste dans l'herbe.
+narrateur|Sarah a encore le seau, près de le bac à sable.
+narrateur|La poule regarde le seau, puis picore ailleurs.
+papa|On dit bonjour à la poule.
+narrateur|Sarah écoute d'abord.
+enfant-f|Bonjour.
+maman|Tu as écouté.
+maman|Si malaise, tu racontes.
+enfant-f|Je raconte à la maison.
+papa|Bravo, Sarah.
+papa|On t'écoute.
+narrateur|Sarah pose le seau, tout doux.
+narrateur|Le foin sent encore le soleil.</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>poule</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4170,7 +4407,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Sarah a vu la poule, près de le bac à sable. Elle avait le seau. Bravo, Sarah. C'est du bon travail. Merci, papa. Merci, maman. La poule picore encore un grain, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4310,7 +4547,16 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Sarah a vu la poule, près de le bac à sable.
+narrateur|Elle avait le seau.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|La poule picore encore un grain, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4338,7 +4584,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Léa. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de le bac à sable, le seau et Léa. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+          <t>La chèvre sonne sa clochette, tout léger. Elle mâche une feuille, tout lentement. Son poil est rêche, un peu chaud. Sarah a encore le seau, près de le bac à sable. La clochette sonne. Le seau tremble un peu. On dit bonjour à la chèvre. Sarah écoute d'abord. Bonjour. Tu as écouté. Si malaise, tu racontes. Je raconte à la maison. Bravo, Sarah. On t'écoute. Sarah pose le seau, tout doux. Le foin sent encore le soleil.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4478,10 +4724,29 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Léa. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de le bac à sable, le seau et Léa. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr"/>
+          <t>narrateur|La chèvre sonne sa clochette, tout léger.
+narrateur|Elle mâche une feuille, tout lentement.
+narrateur|Son poil est rêche, un peu chaud.
+narrateur|Sarah a encore le seau, près de le bac à sable.
+narrateur|La clochette sonne.
+narrateur|Le seau tremble un peu.
+papa|On dit bonjour à la chèvre.
+narrateur|Sarah écoute d'abord.
+enfant-f|Bonjour.
+maman|Tu as écouté.
+maman|Si malaise, tu racontes.
+enfant-f|Je raconte à la maison.
+papa|Bravo, Sarah.
+papa|On t'écoute.
+narrateur|Sarah pose le seau, tout doux.
+narrateur|Le foin sent encore le soleil.</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>clochette</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4506,7 +4771,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Sarah a vu la chèvre, près de le bac à sable. Elle avait le seau. Bravo, Sarah. C'est du bon travail. Merci, papa. Merci, maman. La clochette sonne encore, tout léger. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4646,7 +4911,16 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Sarah a vu la chèvre, près de le bac à sable.
+narrateur|Elle avait le seau.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|La clochette sonne encore, tout léger.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4674,7 +4948,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Sami. La couverture est douce. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau et Sami. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+          <t>Le poulain souffle par le nez, tout chaud. Sa crinière est douce, un peu en bataille. Le foin sent bon, tout près. Sarah a encore le seau, près de le bac à sable. Le poulain renifle le seau, tout doux. On dit bonjour à le poulain. Sarah écoute d'abord. Bonjour. Tu as écouté. Si malaise, tu racontes. Je raconte à la maison. Bravo, Sarah. On t'écoute. Sarah pose le seau, tout doux. Le foin sent encore le soleil.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4814,10 +5088,28 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Sami. La couverture est douce. On souffle doucement. Cette fin-là est celle de le bac à sable, le seau et Sami. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr"/>
+          <t>narrateur|Le poulain souffle par le nez, tout chaud.
+narrateur|Sa crinière est douce, un peu en bataille.
+narrateur|Le foin sent bon, tout près.
+narrateur|Sarah a encore le seau, près de le bac à sable.
+narrateur|Le poulain renifle le seau, tout doux.
+papa|On dit bonjour à le poulain.
+narrateur|Sarah écoute d'abord.
+enfant-f|Bonjour.
+maman|Tu as écouté.
+maman|Si malaise, tu racontes.
+enfant-f|Je raconte à la maison.
+papa|Bravo, Sarah.
+papa|On t'écoute.
+narrateur|Sarah pose le seau, tout doux.
+narrateur|Le foin sent encore le soleil.</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>poulain,foin</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4842,7 +5134,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Sarah a vu le poulain, près de le bac à sable. Elle avait le seau. Bravo, Sarah. C'est du bon travail. Merci, papa. Merci, maman. Le poulain pose le nez dans le foin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4982,7 +5274,16 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Sarah a vu le poulain, près de le bac à sable.
+narrateur|Elle avait le seau.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|Le poulain pose le nez dans le foin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -5010,7 +5311,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Sara a choisi le doudou. La lumière est claire. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara répète tout bas : écouter, si malaise raconter à la maison. On montre du doigt, sans courir. papa n'est pas loin.</t>
+          <t>Sarah prend le doudou gris. Une oreille est encore chaude. Le doudou sent le foin, un peu. Le doudou écoute, lui aussi. Papa parle tout bas. Sarah serre le doudou. J'ai encore un peu le ventre serré. Tu peux raconter. On t'écoute. Un camarade a chuchoté. Tu as bien fait de le dire. On écoute la maîtresse. Le doudou reste sur les genoux. Le doudou a un grain de sable sur l'oreille. On est encore près de le bac à sable. On écoute. Si malaise, on raconte.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5150,7 +5451,23 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Sara a choisi le doudou. La lumière est claire. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara répète tout bas : écouter, si malaise raconter à la maison. On montre du doigt, sans courir. papa n'est pas loin.</t>
+          <t>narrateur|Sarah prend le doudou gris.
+narrateur|Une oreille est encore chaude.
+narrateur|Le doudou sent le foin, un peu.
+papa|Le doudou écoute, lui aussi.
+narrateur|Papa parle tout bas.
+narrateur|Sarah serre le doudou.
+enfant-f|J'ai encore un peu le ventre serré.
+maman|Tu peux raconter.
+maman|On t'écoute.
+enfant-f|Un camarade a chuchoté.
+papa|Tu as bien fait de le dire.
+papa|On écoute la maîtresse.
+narrateur|Le doudou reste sur les genoux.
+narrateur|Le doudou a un grain de sable sur l'oreille.
+narrateur|On est encore près de le bac à sable.
+maman|On écoute.
+maman|Si malaise, on raconte.</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr"/>
@@ -5178,7 +5495,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Au fond du pré, trois animaux sont là. La poule, la chèvre, ou le poulain ? On écoute d'abord. Puis on raconte.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5346,7 +5663,10 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Au fond du pré, trois animaux sont là.
+papa|La poule, la chèvre, ou le poulain ?
+maman|On écoute d'abord.
+maman|Puis on raconte.</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr"/>
@@ -5374,7 +5694,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Tom. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de le bac à sable, le doudou et Tom. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+          <t>La poule picore près de la haie. Elle fait cot cot, tout petit. Une plume blonde reste dans l'herbe. Sarah a encore le doudou, près de le bac à sable. Une petite plume blonde colle au doudou. On dit bonjour à la poule. Sarah écoute d'abord. Bonjour. Tu as écouté. Si malaise, tu racontes. Je raconte à la maison. Bravo, Sarah. On t'écoute. Sarah pose le doudou, tout doux. Le foin sent encore le soleil.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5514,10 +5834,28 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Tom. Les chaussures font toc toc. On range un objet. Cette fin-là est celle de le bac à sable, le doudou et Tom. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr"/>
+          <t>narrateur|La poule picore près de la haie.
+narrateur|Elle fait cot cot, tout petit.
+narrateur|Une plume blonde reste dans l'herbe.
+narrateur|Sarah a encore le doudou, près de le bac à sable.
+narrateur|Une petite plume blonde colle au doudou.
+papa|On dit bonjour à la poule.
+narrateur|Sarah écoute d'abord.
+enfant-f|Bonjour.
+maman|Tu as écouté.
+maman|Si malaise, tu racontes.
+enfant-f|Je raconte à la maison.
+papa|Bravo, Sarah.
+papa|On t'écoute.
+narrateur|Sarah pose le doudou, tout doux.
+narrateur|Le foin sent encore le soleil.</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>poule</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5542,7 +5880,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Sarah a vu la poule, près de le bac à sable. Elle avait le doudou. Bravo, Sarah. C'est du bon travail. Merci, papa. Merci, maman. La poule picore encore un grain, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5682,7 +6020,16 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Sarah a vu la poule, près de le bac à sable.
+narrateur|Elle avait le doudou.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|La poule picore encore un grain, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5710,7 +6057,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Léa. La couverture est douce. On dit merci. Cette fin-là est celle de le bac à sable, le doudou et Léa. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+          <t>La chèvre sonne sa clochette, tout léger. Elle mâche une feuille, tout lentement. Son poil est rêche, un peu chaud. Sarah a encore le doudou, près de le bac à sable. Le doudou sent la chèvre, un peu. On dit bonjour à la chèvre. Sarah écoute d'abord. Bonjour. Tu as écouté. Si malaise, tu racontes. Je raconte à la maison. Bravo, Sarah. On t'écoute. Sarah pose le doudou, tout doux. Le foin sent encore le soleil.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5850,10 +6197,28 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Léa. La couverture est douce. On dit merci. Cette fin-là est celle de le bac à sable, le doudou et Léa. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr"/>
+          <t>narrateur|La chèvre sonne sa clochette, tout léger.
+narrateur|Elle mâche une feuille, tout lentement.
+narrateur|Son poil est rêche, un peu chaud.
+narrateur|Sarah a encore le doudou, près de le bac à sable.
+narrateur|Le doudou sent la chèvre, un peu.
+papa|On dit bonjour à la chèvre.
+narrateur|Sarah écoute d'abord.
+enfant-f|Bonjour.
+maman|Tu as écouté.
+maman|Si malaise, tu racontes.
+enfant-f|Je raconte à la maison.
+papa|Bravo, Sarah.
+papa|On t'écoute.
+narrateur|Sarah pose le doudou, tout doux.
+narrateur|Le foin sent encore le soleil.</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>clochette</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5878,7 +6243,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Sarah a vu la chèvre, près de le bac à sable. Elle avait le doudou. Bravo, Sarah. C'est du bon travail. Merci, papa. Merci, maman. La clochette sonne encore, tout léger. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6018,7 +6383,16 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Sarah a vu la chèvre, près de le bac à sable.
+narrateur|Elle avait le doudou.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|La clochette sonne encore, tout léger.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6046,7 +6420,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Sami. On entend un oiseau. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Sami. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+          <t>Le poulain souffle par le nez, tout chaud. Sa crinière est douce, un peu en bataille. Le foin sent bon, tout près. Sarah a encore le doudou, près de le bac à sable. Le poulain cligne. Le doudou reste sur les genoux. On dit bonjour à le poulain. Sarah écoute d'abord. Bonjour. Tu as écouté. Si malaise, tu racontes. Je raconte à la maison. Bravo, Sarah. On t'écoute. Sarah pose le doudou, tout doux. Le foin sent encore le soleil.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6186,10 +6560,29 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Sami. On entend un oiseau. On souffle doucement. Cette fin-là est celle de le bac à sable, le doudou et Sami. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr"/>
+          <t>narrateur|Le poulain souffle par le nez, tout chaud.
+narrateur|Sa crinière est douce, un peu en bataille.
+narrateur|Le foin sent bon, tout près.
+narrateur|Sarah a encore le doudou, près de le bac à sable.
+narrateur|Le poulain cligne.
+narrateur|Le doudou reste sur les genoux.
+papa|On dit bonjour à le poulain.
+narrateur|Sarah écoute d'abord.
+enfant-f|Bonjour.
+maman|Tu as écouté.
+maman|Si malaise, tu racontes.
+enfant-f|Je raconte à la maison.
+papa|Bravo, Sarah.
+papa|On t'écoute.
+narrateur|Sarah pose le doudou, tout doux.
+narrateur|Le foin sent encore le soleil.</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>poulain,foin</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6214,7 +6607,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Sarah a vu le poulain, près de le bac à sable. Elle avait le doudou. Bravo, Sarah. C'est du bon travail. Merci, papa. Merci, maman. Le poulain pose le nez dans le foin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6354,7 +6747,16 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Sarah a vu le poulain, près de le bac à sable.
+narrateur|Elle avait le doudou.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|Le poulain pose le nez dans le foin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6382,7 +6784,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Sara va vers le toboggan. Une feuille tombe. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Sara se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On dit merci. Je suis là. On reste ensemble.</t>
+          <t>Sarah va vers le toboggan. Le métal est tiède, un peu pâle. Une feuille sèche est sur la marche. Les marches sentent le bois et la poussière. Je tiens le côté, Sarah. Tu montes, tout doux. Sarah pose un pied, puis l'autre. Le gilet d'école frotte la rampe. Papa, j'ai écouté la maîtresse. Oui. On écoute d'abord. Sarah s'arrête, en haut. Le pré est vert, tout plat. Le souvenir du chuchotement revient. Son ventre se serre, tout petit. Papa, j'ai eu un malaise. Un camarade a parlé tout bas. Tu as bien fait de le dire. Si malaise, tu racontes à papa ou maman. Je t'écoute, Sarah. On écoute la maîtresse. Ensuite, tu nous racontes. Sarah glisse, tout lentement. Le sable de l'arrivée est tiède. Je raconte à la maison. Bravo. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6522,11 +6924,40 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|Sara va vers le toboggan. Une feuille tombe. maman sourit. Ici, c'est le toboggan. Ce n'est pas comme les autres endroits. Sara se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On dit merci.
-maman|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr"/>
+          <t>narrateur|Sarah va vers le toboggan.
+narrateur|Le métal est tiède, un peu pâle.
+narrateur|Une feuille sèche est sur la marche.
+narrateur|Les marches sentent le bois et la poussière.
+papa|Je tiens le côté, Sarah.
+papa|Tu montes, tout doux.
+narrateur|Sarah pose un pied, puis l'autre.
+narrateur|Le gilet d'école frotte la rampe.
+enfant-f|Papa, j'ai écouté la maîtresse.
+papa|Oui.
+papa|On écoute d'abord.
+narrateur|Sarah s'arrête, en haut.
+narrateur|Le pré est vert, tout plat.
+narrateur|Le souvenir du chuchotement revient.
+narrateur|Son ventre se serre, tout petit.
+enfant-f|Papa, j'ai eu un malaise.
+enfant-f|Un camarade a parlé tout bas.
+papa|Tu as bien fait de le dire.
+papa|Si malaise, tu racontes à papa ou maman.
+maman|Je t'écoute, Sarah.
+maman|On écoute la maîtresse.
+maman|Ensuite, tu nous racontes.
+narrateur|Sarah glisse, tout lentement.
+narrateur|Le sable de l'arrivée est tiède.
+enfant-f|Je raconte à la maison.
+papa|Bravo.
+papa|C'est du bon travail.</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>toboggan</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6551,7 +6982,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
+          <t>Sarah a écouté la maîtresse. Et si le ventre se serre ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6711,7 +7142,8 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
+          <t>narrateur|Sarah a écouté la maîtresse.
+papa|Et si le ventre se serre ?</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr"/>
@@ -6739,7 +7171,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara respire. Sara retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
+          <t>Oui. On raconte à la maison. On écoute la maîtresse. Si malaise, tu nous le dis. Sarah pose les deux pieds dans le sable. Je raconte à papa. Bravo. Tu as fait du bon travail. La feuille sèche vole un peu, tout loin.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6883,7 +7315,15 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara respire. Sara retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
+          <t>papa|Oui.
+papa|On raconte à la maison.
+maman|On écoute la maîtresse.
+maman|Si malaise, tu nous le dis.
+narrateur|Sarah pose les deux pieds dans le sable.
+enfant-f|Je raconte à papa.
+papa|Bravo.
+papa|Tu as fait du bon travail.
+narrateur|La feuille sèche vole un peu, tout loin.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -6911,7 +7351,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>Trois jouets attendent, tout proches. Le ballon, le seau, ou le doudou ? On joue. On écoute. Et on raconte, si malaise.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7075,7 +7515,11 @@
       <c r="AV35" s="2" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>narrateur|Trois jouets attendent, tout proches.
+maman|Le ballon, le seau, ou le doudou ?
+papa|On joue.
+papa|On écoute.
+papa|Et on raconte, si malaise.</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr"/>
@@ -7103,7 +7547,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Sara a choisi le ballon. Il y a des miettes sur la table. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara répète tout bas : écouter, si malaise raconter à la maison. On écoute jusqu'au bout. papa n'est pas loin.</t>
+          <t>Sarah prend le ballon rouge. Le ballon est un peu sablé, tout doux. Il fait poum contre le bois. Moi, je raconte le pré. Papa parle jusqu'au bout. Sarah écoute. Le ballon est chaud. Tu as écouté. Si le ventre se serre, tu racontes. Oui, maman. Bravo. Le ballon reste près du gilet. Le ballon attend au pied du toboggan. On est encore près de le toboggan. On écoute. Si malaise, on raconte.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7243,10 +7687,29 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Sara a choisi le ballon. Il y a des miettes sur la table. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara répète tout bas : écouter, si malaise raconter à la maison. On écoute jusqu'au bout. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr"/>
+          <t>narrateur|Sarah prend le ballon rouge.
+narrateur|Le ballon est un peu sablé, tout doux.
+narrateur|Il fait poum contre le bois.
+papa|Moi, je raconte le pré.
+narrateur|Papa parle jusqu'au bout.
+narrateur|Sarah écoute.
+enfant-f|Le ballon est chaud.
+maman|Tu as écouté.
+maman|Si le ventre se serre, tu racontes.
+enfant-f|Oui, maman.
+papa|Bravo.
+narrateur|Le ballon reste près du gilet.
+narrateur|Le ballon attend au pied du toboggan.
+narrateur|On est encore près de le toboggan.
+maman|On écoute.
+maman|Si malaise, on raconte.</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>ballon</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7271,7 +7734,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Au fond du pré, trois animaux sont là. La poule, la chèvre, ou le poulain ? On écoute d'abord. Puis on raconte.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7439,7 +7902,10 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Au fond du pré, trois animaux sont là.
+papa|La poule, la chèvre, ou le poulain ?
+maman|On écoute d'abord.
+maman|Puis on raconte.</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr"/>
@@ -7467,7 +7933,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Tom. Un chat miaule une fois. On dit merci. Cette fin-là est celle de le toboggan, le ballon et Tom. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+          <t>La poule picore près de la haie. Elle fait cot cot, tout petit. Une plume blonde reste dans l'herbe. Sarah a encore le ballon, près de le toboggan. La poule contourne le ballon, au pied du toboggan. On dit bonjour à la poule. Sarah écoute d'abord. Bonjour. Tu as écouté. Si malaise, tu racontes. Je raconte à la maison. Bravo, Sarah. On t'écoute. Sarah pose le ballon, tout doux. Le foin sent encore le soleil.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7607,10 +8073,28 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Tom. Un chat miaule une fois. On dit merci. Cette fin-là est celle de le toboggan, le ballon et Tom. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr"/>
+          <t>narrateur|La poule picore près de la haie.
+narrateur|Elle fait cot cot, tout petit.
+narrateur|Une plume blonde reste dans l'herbe.
+narrateur|Sarah a encore le ballon, près de le toboggan.
+narrateur|La poule contourne le ballon, au pied du toboggan.
+papa|On dit bonjour à la poule.
+narrateur|Sarah écoute d'abord.
+enfant-f|Bonjour.
+maman|Tu as écouté.
+maman|Si malaise, tu racontes.
+enfant-f|Je raconte à la maison.
+papa|Bravo, Sarah.
+papa|On t'écoute.
+narrateur|Sarah pose le ballon, tout doux.
+narrateur|Le foin sent encore le soleil.</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>poule</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7635,7 +8119,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Sarah a vu la poule, près de le toboggan. Elle avait le ballon. Bravo, Sarah. C'est du bon travail. Merci, papa. Merci, maman. La poule picore encore un grain, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7775,7 +8259,16 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Sarah a vu la poule, près de le toboggan.
+narrateur|Elle avait le ballon.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|La poule picore encore un grain, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7803,7 +8296,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Léa. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de le toboggan, le ballon et Léa. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+          <t>La chèvre sonne sa clochette, tout léger. Elle mâche une feuille, tout lentement. Son poil est rêche, un peu chaud. Sarah a encore le ballon, près de le toboggan. La chèvre lève la tête. Le ballon attend en bas. On dit bonjour à la chèvre. Sarah écoute d'abord. Bonjour. Tu as écouté. Si malaise, tu racontes. Je raconte à la maison. Bravo, Sarah. On t'écoute. Sarah pose le ballon, tout doux. Le foin sent encore le soleil.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7943,10 +8436,29 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Léa. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de le toboggan, le ballon et Léa. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr"/>
+          <t>narrateur|La chèvre sonne sa clochette, tout léger.
+narrateur|Elle mâche une feuille, tout lentement.
+narrateur|Son poil est rêche, un peu chaud.
+narrateur|Sarah a encore le ballon, près de le toboggan.
+narrateur|La chèvre lève la tête.
+narrateur|Le ballon attend en bas.
+papa|On dit bonjour à la chèvre.
+narrateur|Sarah écoute d'abord.
+enfant-f|Bonjour.
+maman|Tu as écouté.
+maman|Si malaise, tu racontes.
+enfant-f|Je raconte à la maison.
+papa|Bravo, Sarah.
+papa|On t'écoute.
+narrateur|Sarah pose le ballon, tout doux.
+narrateur|Le foin sent encore le soleil.</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>clochette</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7971,7 +8483,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Sarah a vu la chèvre, près de le toboggan. Elle avait le ballon. Bravo, Sarah. C'est du bon travail. Merci, papa. Merci, maman. La clochette sonne encore, tout léger. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8111,7 +8623,16 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Sarah a vu la chèvre, près de le toboggan.
+narrateur|Elle avait le ballon.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|La clochette sonne encore, tout léger.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8139,7 +8660,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Sami. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon et Sami. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+          <t>Le poulain souffle par le nez, tout chaud. Sa crinière est douce, un peu en bataille. Le foin sent bon, tout près. Sarah a encore le ballon, près de le toboggan. Le poulain fait un pas. Le ballon reste calme. On dit bonjour à le poulain. Sarah écoute d'abord. Bonjour. Tu as écouté. Si malaise, tu racontes. Je raconte à la maison. Bravo, Sarah. On t'écoute. Sarah pose le ballon, tout doux. Le foin sent encore le soleil.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8279,10 +8800,29 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Sami. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le ballon et Sami. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr"/>
+          <t>narrateur|Le poulain souffle par le nez, tout chaud.
+narrateur|Sa crinière est douce, un peu en bataille.
+narrateur|Le foin sent bon, tout près.
+narrateur|Sarah a encore le ballon, près de le toboggan.
+narrateur|Le poulain fait un pas.
+narrateur|Le ballon reste calme.
+papa|On dit bonjour à le poulain.
+narrateur|Sarah écoute d'abord.
+enfant-f|Bonjour.
+maman|Tu as écouté.
+maman|Si malaise, tu racontes.
+enfant-f|Je raconte à la maison.
+papa|Bravo, Sarah.
+papa|On t'écoute.
+narrateur|Sarah pose le ballon, tout doux.
+narrateur|Le foin sent encore le soleil.</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>poulain,foin</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8307,7 +8847,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Sarah a vu le poulain, près de le toboggan. Elle avait le ballon. Bravo, Sarah. C'est du bon travail. Merci, papa. Merci, maman. Le poulain pose le nez dans le foin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8447,7 +8987,16 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Sarah a vu le poulain, près de le toboggan.
+narrateur|Elle avait le ballon.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|Le poulain pose le nez dans le foin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8475,7 +9024,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Sara a choisi le seau. Un chat miaule une fois. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara répète tout bas : écouter, si malaise raconter à la maison. On attend son tour. papa n'est pas loin.</t>
+          <t>Sarah prend le seau bleu. Un peu de sable tremble au fond. Le seau sonne, tout creux. Moi, je raconte le puits. Maman parle, tout près. Sarah écoute jusqu'au bout. Le seau est lourd. Tu as écouté. Si malaise, tu viens nous le dire. Je raconte à la maison. Bravo, Sarah. Sarah pose le seau, tout droit. Le seau sonne contre la rampe, tout doux. On est encore près de le toboggan. On écoute. Si malaise, on raconte.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8615,10 +9164,29 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Sara a choisi le seau. Un chat miaule une fois. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara répète tout bas : écouter, si malaise raconter à la maison. On attend son tour. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr"/>
+          <t>narrateur|Sarah prend le seau bleu.
+narrateur|Un peu de sable tremble au fond.
+narrateur|Le seau sonne, tout creux.
+maman|Moi, je raconte le puits.
+narrateur|Maman parle, tout près.
+narrateur|Sarah écoute jusqu'au bout.
+enfant-f|Le seau est lourd.
+papa|Tu as écouté.
+papa|Si malaise, tu viens nous le dire.
+enfant-f|Je raconte à la maison.
+maman|Bravo, Sarah.
+narrateur|Sarah pose le seau, tout droit.
+narrateur|Le seau sonne contre la rampe, tout doux.
+narrateur|On est encore près de le toboggan.
+maman|On écoute.
+maman|Si malaise, on raconte.</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>seau</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8643,7 +9211,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Au fond du pré, trois animaux sont là. La poule, la chèvre, ou le poulain ? On écoute d'abord. Puis on raconte.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8811,7 +9379,10 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Au fond du pré, trois animaux sont là.
+papa|La poule, la chèvre, ou le poulain ?
+maman|On écoute d'abord.
+maman|Puis on raconte.</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr"/>
@@ -8839,7 +9410,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Tom. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de le toboggan, le seau et Tom. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+          <t>La poule picore près de la haie. Elle fait cot cot, tout petit. Une plume blonde reste dans l'herbe. Sarah a encore le seau, près de le toboggan. Un grain tombe près du seau, au pied du toboggan. On dit bonjour à la poule. Sarah écoute d'abord. Bonjour. Tu as écouté. Si malaise, tu racontes. Je raconte à la maison. Bravo, Sarah. On t'écoute. Sarah pose le seau, tout doux. Le foin sent encore le soleil.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8979,10 +9550,28 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Tom. Les chaussures font toc toc. On dit merci. Cette fin-là est celle de le toboggan, le seau et Tom. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr"/>
+          <t>narrateur|La poule picore près de la haie.
+narrateur|Elle fait cot cot, tout petit.
+narrateur|Une plume blonde reste dans l'herbe.
+narrateur|Sarah a encore le seau, près de le toboggan.
+narrateur|Un grain tombe près du seau, au pied du toboggan.
+papa|On dit bonjour à la poule.
+narrateur|Sarah écoute d'abord.
+enfant-f|Bonjour.
+maman|Tu as écouté.
+maman|Si malaise, tu racontes.
+enfant-f|Je raconte à la maison.
+papa|Bravo, Sarah.
+papa|On t'écoute.
+narrateur|Sarah pose le seau, tout doux.
+narrateur|Le foin sent encore le soleil.</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>poule</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9007,7 +9596,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Sarah a vu la poule, près de le toboggan. Elle avait le seau. Bravo, Sarah. C'est du bon travail. Merci, papa. Merci, maman. La poule picore encore un grain, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9147,7 +9736,16 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Sarah a vu la poule, près de le toboggan.
+narrateur|Elle avait le seau.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|La poule picore encore un grain, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9175,7 +9773,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Léa. La couverture est douce. On souffle doucement. Cette fin-là est celle de le toboggan, le seau et Léa. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+          <t>La chèvre sonne sa clochette, tout léger. Elle mâche une feuille, tout lentement. Son poil est rêche, un peu chaud. Sarah a encore le seau, près de le toboggan. La chèvre mâche. Le seau sonne, tout creux. On dit bonjour à la chèvre. Sarah écoute d'abord. Bonjour. Tu as écouté. Si malaise, tu racontes. Je raconte à la maison. Bravo, Sarah. On t'écoute. Sarah pose le seau, tout doux. Le foin sent encore le soleil.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9315,10 +9913,29 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Léa. La couverture est douce. On souffle doucement. Cette fin-là est celle de le toboggan, le seau et Léa. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr"/>
+          <t>narrateur|La chèvre sonne sa clochette, tout léger.
+narrateur|Elle mâche une feuille, tout lentement.
+narrateur|Son poil est rêche, un peu chaud.
+narrateur|Sarah a encore le seau, près de le toboggan.
+narrateur|La chèvre mâche.
+narrateur|Le seau sonne, tout creux.
+papa|On dit bonjour à la chèvre.
+narrateur|Sarah écoute d'abord.
+enfant-f|Bonjour.
+maman|Tu as écouté.
+maman|Si malaise, tu racontes.
+enfant-f|Je raconte à la maison.
+papa|Bravo, Sarah.
+papa|On t'écoute.
+narrateur|Sarah pose le seau, tout doux.
+narrateur|Le foin sent encore le soleil.</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>clochette</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9343,7 +9960,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Sarah a vu la chèvre, près de le toboggan. Elle avait le seau. Bravo, Sarah. C'est du bon travail. Merci, papa. Merci, maman. La clochette sonne encore, tout léger. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9483,7 +10100,16 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Sarah a vu la chèvre, près de le toboggan.
+narrateur|Elle avait le seau.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|La clochette sonne encore, tout léger.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9511,7 +10137,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Sami. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau et Sami. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+          <t>Le poulain souffle par le nez, tout chaud. Sa crinière est douce, un peu en bataille. Le foin sent bon, tout près. Sarah a encore le seau, près de le toboggan. Le foin touche le seau, près du poulain. On dit bonjour à le poulain. Sarah écoute d'abord. Bonjour. Tu as écouté. Si malaise, tu racontes. Je raconte à la maison. Bravo, Sarah. On t'écoute. Sarah pose le seau, tout doux. Le foin sent encore le soleil.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9651,10 +10277,28 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Sami. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le seau et Sami. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr"/>
+          <t>narrateur|Le poulain souffle par le nez, tout chaud.
+narrateur|Sa crinière est douce, un peu en bataille.
+narrateur|Le foin sent bon, tout près.
+narrateur|Sarah a encore le seau, près de le toboggan.
+narrateur|Le foin touche le seau, près du poulain.
+papa|On dit bonjour à le poulain.
+narrateur|Sarah écoute d'abord.
+enfant-f|Bonjour.
+maman|Tu as écouté.
+maman|Si malaise, tu racontes.
+enfant-f|Je raconte à la maison.
+papa|Bravo, Sarah.
+papa|On t'écoute.
+narrateur|Sarah pose le seau, tout doux.
+narrateur|Le foin sent encore le soleil.</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>poulain,foin</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9679,7 +10323,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Sarah a vu le poulain, près de le toboggan. Elle avait le seau. Bravo, Sarah. C'est du bon travail. Merci, papa. Merci, maman. Le poulain pose le nez dans le foin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9819,7 +10463,16 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Sarah a vu le poulain, près de le toboggan.
+narrateur|Elle avait le seau.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|Le poulain pose le nez dans le foin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9847,7 +10500,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Sara a choisi le doudou. Les chaussures font toc toc. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara répète tout bas : écouter, si malaise raconter à la maison. On montre du doigt, sans courir. papa n'est pas loin.</t>
+          <t>Sarah prend le doudou gris. Une oreille est encore chaude. Le doudou sent le foin, un peu. Le doudou écoute, lui aussi. Papa parle tout bas. Sarah serre le doudou. J'ai encore un peu le ventre serré. Tu peux raconter. On t'écoute. Un camarade a chuchoté. Tu as bien fait de le dire. On écoute la maîtresse. Le doudou reste sur les genoux. Le doudou voyage sur les genoux, en haut. On est encore près de le toboggan. On écoute. Si malaise, on raconte.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9987,7 +10640,23 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Sara a choisi le doudou. Les chaussures font toc toc. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara répète tout bas : écouter, si malaise raconter à la maison. On montre du doigt, sans courir. papa n'est pas loin.</t>
+          <t>narrateur|Sarah prend le doudou gris.
+narrateur|Une oreille est encore chaude.
+narrateur|Le doudou sent le foin, un peu.
+papa|Le doudou écoute, lui aussi.
+narrateur|Papa parle tout bas.
+narrateur|Sarah serre le doudou.
+enfant-f|J'ai encore un peu le ventre serré.
+maman|Tu peux raconter.
+maman|On t'écoute.
+enfant-f|Un camarade a chuchoté.
+papa|Tu as bien fait de le dire.
+papa|On écoute la maîtresse.
+narrateur|Le doudou reste sur les genoux.
+narrateur|Le doudou voyage sur les genoux, en haut.
+narrateur|On est encore près de le toboggan.
+maman|On écoute.
+maman|Si malaise, on raconte.</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr"/>
@@ -10015,7 +10684,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Au fond du pré, trois animaux sont là. La poule, la chèvre, ou le poulain ? On écoute d'abord. Puis on raconte.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10183,7 +10852,10 @@
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Au fond du pré, trois animaux sont là.
+papa|La poule, la chèvre, ou le poulain ?
+maman|On écoute d'abord.
+maman|Puis on raconte.</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr"/>
@@ -10211,7 +10883,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Tom. La couverture est douce. On dit merci. Cette fin-là est celle de le toboggan, le doudou et Tom. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+          <t>La poule picore près de la haie. Elle fait cot cot, tout petit. Une plume blonde reste dans l'herbe. Sarah a encore le doudou, près de le toboggan. La poule picore loin du doudou, en bas. On dit bonjour à la poule. Sarah écoute d'abord. Bonjour. Tu as écouté. Si malaise, tu racontes. Je raconte à la maison. Bravo, Sarah. On t'écoute. Sarah pose le doudou, tout doux. Le foin sent encore le soleil.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10351,10 +11023,28 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Tom. La couverture est douce. On dit merci. Cette fin-là est celle de le toboggan, le doudou et Tom. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr"/>
+          <t>narrateur|La poule picore près de la haie.
+narrateur|Elle fait cot cot, tout petit.
+narrateur|Une plume blonde reste dans l'herbe.
+narrateur|Sarah a encore le doudou, près de le toboggan.
+narrateur|La poule picore loin du doudou, en bas.
+papa|On dit bonjour à la poule.
+narrateur|Sarah écoute d'abord.
+enfant-f|Bonjour.
+maman|Tu as écouté.
+maman|Si malaise, tu racontes.
+enfant-f|Je raconte à la maison.
+papa|Bravo, Sarah.
+papa|On t'écoute.
+narrateur|Sarah pose le doudou, tout doux.
+narrateur|Le foin sent encore le soleil.</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>poule</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10379,7 +11069,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Sarah a vu la poule, près de le toboggan. Elle avait le doudou. Bravo, Sarah. C'est du bon travail. Merci, papa. Merci, maman. La poule picore encore un grain, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10519,7 +11209,16 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Sarah a vu la poule, près de le toboggan.
+narrateur|Elle avait le doudou.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|La poule picore encore un grain, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10547,7 +11246,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Léa. On entend un oiseau. On souffle doucement. Cette fin-là est celle de le toboggan, le doudou et Léa. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+          <t>La chèvre sonne sa clochette, tout léger. Elle mâche une feuille, tout lentement. Son poil est rêche, un peu chaud. Sarah a encore le doudou, près de le toboggan. La clochette sonne. Sarah serre le doudou. On dit bonjour à la chèvre. Sarah écoute d'abord. Bonjour. Tu as écouté. Si malaise, tu racontes. Je raconte à la maison. Bravo, Sarah. On t'écoute. Sarah pose le doudou, tout doux. Le foin sent encore le soleil.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10687,10 +11386,29 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Léa. On entend un oiseau. On souffle doucement. Cette fin-là est celle de le toboggan, le doudou et Léa. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr"/>
+          <t>narrateur|La chèvre sonne sa clochette, tout léger.
+narrateur|Elle mâche une feuille, tout lentement.
+narrateur|Son poil est rêche, un peu chaud.
+narrateur|Sarah a encore le doudou, près de le toboggan.
+narrateur|La clochette sonne.
+narrateur|Sarah serre le doudou.
+papa|On dit bonjour à la chèvre.
+narrateur|Sarah écoute d'abord.
+enfant-f|Bonjour.
+maman|Tu as écouté.
+maman|Si malaise, tu racontes.
+enfant-f|Je raconte à la maison.
+papa|Bravo, Sarah.
+papa|On t'écoute.
+narrateur|Sarah pose le doudou, tout doux.
+narrateur|Le foin sent encore le soleil.</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>clochette</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10715,7 +11433,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Sarah a vu la chèvre, près de le toboggan. Elle avait le doudou. Bravo, Sarah. C'est du bon travail. Merci, papa. Merci, maman. La clochette sonne encore, tout léger. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10855,7 +11573,16 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Sarah a vu la chèvre, près de le toboggan.
+narrateur|Elle avait le doudou.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|La clochette sonne encore, tout léger.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10883,7 +11610,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Sami. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Sami. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+          <t>Le poulain souffle par le nez, tout chaud. Sa crinière est douce, un peu en bataille. Le foin sent bon, tout près. Sarah a encore le doudou, près de le toboggan. Le poulain souffle. Le doudou est encore chaud. On dit bonjour à le poulain. Sarah écoute d'abord. Bonjour. Tu as écouté. Si malaise, tu racontes. Je raconte à la maison. Bravo, Sarah. On t'écoute. Sarah pose le doudou, tout doux. Le foin sent encore le soleil.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -11023,10 +11750,29 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Sami. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de le toboggan, le doudou et Sami. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr"/>
+          <t>narrateur|Le poulain souffle par le nez, tout chaud.
+narrateur|Sa crinière est douce, un peu en bataille.
+narrateur|Le foin sent bon, tout près.
+narrateur|Sarah a encore le doudou, près de le toboggan.
+narrateur|Le poulain souffle.
+narrateur|Le doudou est encore chaud.
+papa|On dit bonjour à le poulain.
+narrateur|Sarah écoute d'abord.
+enfant-f|Bonjour.
+maman|Tu as écouté.
+maman|Si malaise, tu racontes.
+enfant-f|Je raconte à la maison.
+papa|Bravo, Sarah.
+papa|On t'écoute.
+narrateur|Sarah pose le doudou, tout doux.
+narrateur|Le foin sent encore le soleil.</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>poulain,foin</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11051,7 +11797,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Sarah a vu le poulain, près de le toboggan. Elle avait le doudou. Bravo, Sarah. C'est du bon travail. Merci, papa. Merci, maman. Le poulain pose le nez dans le foin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11191,7 +11937,16 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Sarah a vu le poulain, près de le toboggan.
+narrateur|Elle avait le doudou.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|Le poulain pose le nez dans le foin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11219,7 +11974,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Sara va vers les balançoires. L'eau coule, tout petit bruit. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Sara se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On souffle doucement. Je suis là. On reste ensemble.</t>
+          <t>Sarah va vers les balançoires. La corde est rêche, un peu tiède. L'herbe sous les pieds est plate. Un oiseau passe, tout loin. Je suis près de toi. On pousse tout doux. Sarah s'assoit. Le bois de l'assise est lisse. Maman, la maîtresse a dit d'écouter. Tu as écouté ? Oui, jusqu'au bout. La balançoire avance, tout petit. Sarah pense à la cour, ce matin. Un camarade a chuchoté, trop près. Son ventre se serre encore. Maman, j'ai eu un malaise. Il a parlé d'un secret. Tu viens me le dire. C'est bien. On écoute la maîtresse. Si malaise, on raconte à la maison. La corde se tait un peu. Le ventre de Sarah se desserre. Je raconte à papa et maman. Bravo, Sarah. On t'écoute.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11359,11 +12114,39 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Sara va vers les balançoires. L'eau coule, tout petit bruit. maman sourit. Ici, c'est les balançoires. Ce n'est pas comme les autres endroits. Sara se souvient : écouter, si malaise raconter à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. On souffle doucement.
-maman|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX60" t="inlineStr"/>
+          <t>narrateur|Sarah va vers les balançoires.
+narrateur|La corde est rêche, un peu tiède.
+narrateur|L'herbe sous les pieds est plate.
+narrateur|Un oiseau passe, tout loin.
+maman|Je suis près de toi.
+maman|On pousse tout doux.
+narrateur|Sarah s'assoit.
+narrateur|Le bois de l'assise est lisse.
+enfant-f|Maman, la maîtresse a dit d'écouter.
+maman|Tu as écouté ?
+enfant-f|Oui, jusqu'au bout.
+narrateur|La balançoire avance, tout petit.
+narrateur|Sarah pense à la cour, ce matin.
+narrateur|Un camarade a chuchoté, trop près.
+narrateur|Son ventre se serre encore.
+enfant-f|Maman, j'ai eu un malaise.
+enfant-f|Il a parlé d'un secret.
+maman|Tu viens me le dire.
+maman|C'est bien.
+papa|On écoute la maîtresse.
+papa|Si malaise, on raconte à la maison.
+narrateur|La corde se tait un peu.
+narrateur|Le ventre de Sarah se desserre.
+enfant-f|Je raconte à papa et maman.
+maman|Bravo, Sarah.
+maman|On t'écoute.</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>balancoire,oiseau</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11388,7 +12171,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
+          <t>Sarah écoute, puis elle raconte. On raconte à la maison ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11548,7 +12331,8 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Écouter la maîtresse, en parler à la maison.</t>
+          <t>narrateur|Sarah écoute, puis elle raconte.
+maman|On raconte à la maison ?</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr"/>
@@ -11576,7 +12360,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara respire. Sara retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
+          <t>Oui. On raconte à la maison. On t'écoute, Sarah. La corde ne bouge plus. J'ai écouté. Puis j'ai raconté. Bravo. C'est du bon travail. L'herbe sous les pieds est encore plate.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11720,7 +12504,15 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara respire. Sara retient : écouter, si malaise raconter à la maison. On continue, avec maman.</t>
+          <t>maman|Oui.
+maman|On raconte à la maison.
+papa|On t'écoute, Sarah.
+narrateur|La corde ne bouge plus.
+enfant-f|J'ai écouté.
+enfant-f|Puis j'ai raconté.
+maman|Bravo.
+maman|C'est du bon travail.
+narrateur|L'herbe sous les pieds est encore plate.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11748,7 +12540,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>Trois jouets attendent, tout proches. Le ballon, le seau, ou le doudou ? On joue. On écoute. Et on raconte, si malaise.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11912,7 +12704,11 @@
       <c r="AV63" s="2" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon, le seau, ou le doudou.</t>
+          <t>narrateur|Trois jouets attendent, tout proches.
+maman|Le ballon, le seau, ou le doudou ?
+papa|On joue.
+papa|On écoute.
+papa|Et on raconte, si malaise.</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr"/>
@@ -11940,7 +12736,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Sara a choisi le ballon. La couverture est douce. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara répète tout bas : écouter, si malaise raconter à la maison. On écoute jusqu'au bout. papa n'est pas loin.</t>
+          <t>Sarah prend le ballon rouge. Le ballon est un peu sablé, tout doux. Il fait poum contre le bois. Moi, je raconte le pré. Papa parle jusqu'au bout. Sarah écoute. Le ballon est chaud. Tu as écouté. Si le ventre se serre, tu racontes. Oui, maman. Bravo. Le ballon reste près du gilet. Le ballon repose dans l'herbe, sous la corde. On est encore près de les balançoires. On écoute. Si malaise, on raconte.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12080,10 +12876,29 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Sara a choisi le ballon. La couverture est douce. Le ballon reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara répète tout bas : écouter, si malaise raconter à la maison. On écoute jusqu'au bout. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr"/>
+          <t>narrateur|Sarah prend le ballon rouge.
+narrateur|Le ballon est un peu sablé, tout doux.
+narrateur|Il fait poum contre le bois.
+papa|Moi, je raconte le pré.
+narrateur|Papa parle jusqu'au bout.
+narrateur|Sarah écoute.
+enfant-f|Le ballon est chaud.
+maman|Tu as écouté.
+maman|Si le ventre se serre, tu racontes.
+enfant-f|Oui, maman.
+papa|Bravo.
+narrateur|Le ballon reste près du gilet.
+narrateur|Le ballon repose dans l'herbe, sous la corde.
+narrateur|On est encore près de les balançoires.
+maman|On écoute.
+maman|Si malaise, on raconte.</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>ballon</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12108,7 +12923,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Au fond du pré, trois animaux sont là. La poule, la chèvre, ou le poulain ? On écoute d'abord. Puis on raconte.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12276,7 +13091,10 @@
       </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Au fond du pré, trois animaux sont là.
+papa|La poule, la chèvre, ou le poulain ?
+maman|On écoute d'abord.
+maman|Puis on raconte.</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr"/>
@@ -12304,7 +13122,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Tom. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de les balançoires, le ballon et Tom. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+          <t>La poule picore près de la haie. Elle fait cot cot, tout petit. Une plume blonde reste dans l'herbe. Sarah a encore le ballon, près de les balançoires. La poule passe sous la corde, loin du ballon. On dit bonjour à la poule. Sarah écoute d'abord. Bonjour. Tu as écouté. Si malaise, tu racontes. Je raconte à la maison. Bravo, Sarah. On t'écoute. Sarah pose le ballon, tout doux. Le foin sent encore le soleil.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12444,10 +13262,28 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Tom. Les chaussures font toc toc. On souffle doucement. Cette fin-là est celle de les balançoires, le ballon et Tom. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr"/>
+          <t>narrateur|La poule picore près de la haie.
+narrateur|Elle fait cot cot, tout petit.
+narrateur|Une plume blonde reste dans l'herbe.
+narrateur|Sarah a encore le ballon, près de les balançoires.
+narrateur|La poule passe sous la corde, loin du ballon.
+papa|On dit bonjour à la poule.
+narrateur|Sarah écoute d'abord.
+enfant-f|Bonjour.
+maman|Tu as écouté.
+maman|Si malaise, tu racontes.
+enfant-f|Je raconte à la maison.
+papa|Bravo, Sarah.
+papa|On t'écoute.
+narrateur|Sarah pose le ballon, tout doux.
+narrateur|Le foin sent encore le soleil.</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>poule</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12472,7 +13308,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Sarah a vu la poule, près de les balançoires. Elle avait le ballon. Bravo, Sarah. C'est du bon travail. Merci, papa. Merci, maman. La poule picore encore un grain, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12612,7 +13448,16 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Sarah a vu la poule, près de les balançoires.
+narrateur|Elle avait le ballon.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|La poule picore encore un grain, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12640,7 +13485,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Léa. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le ballon et Léa. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+          <t>La chèvre sonne sa clochette, tout léger. Elle mâche une feuille, tout lentement. Son poil est rêche, un peu chaud. Sarah a encore le ballon, près de les balançoires. La chèvre broute. Le ballon dort dans l'herbe. On dit bonjour à la chèvre. Sarah écoute d'abord. Bonjour. Tu as écouté. Si malaise, tu racontes. Je raconte à la maison. Bravo, Sarah. On t'écoute. Sarah pose le ballon, tout doux. Le foin sent encore le soleil.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12780,10 +13625,29 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Léa. La couverture est douce. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le ballon et Léa. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX68" t="inlineStr"/>
+          <t>narrateur|La chèvre sonne sa clochette, tout léger.
+narrateur|Elle mâche une feuille, tout lentement.
+narrateur|Son poil est rêche, un peu chaud.
+narrateur|Sarah a encore le ballon, près de les balançoires.
+narrateur|La chèvre broute.
+narrateur|Le ballon dort dans l'herbe.
+papa|On dit bonjour à la chèvre.
+narrateur|Sarah écoute d'abord.
+enfant-f|Bonjour.
+maman|Tu as écouté.
+maman|Si malaise, tu racontes.
+enfant-f|Je raconte à la maison.
+papa|Bravo, Sarah.
+papa|On t'écoute.
+narrateur|Sarah pose le ballon, tout doux.
+narrateur|Le foin sent encore le soleil.</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>clochette</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12808,7 +13672,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Sarah a vu la chèvre, près de les balançoires. Elle avait le ballon. Bravo, Sarah. C'est du bon travail. Merci, papa. Merci, maman. La clochette sonne encore, tout léger. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12948,7 +13812,16 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Sarah a vu la chèvre, près de les balançoires.
+narrateur|Elle avait le ballon.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|La clochette sonne encore, tout léger.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -12976,7 +13849,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Sami. On entend un oiseau. On attend son tour. Cette fin-là est celle de les balançoires, le ballon et Sami. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+          <t>Le poulain souffle par le nez, tout chaud. Sa crinière est douce, un peu en bataille. Le foin sent bon, tout près. Sarah a encore le ballon, près de les balançoires. Le poulain secoue la crinière, près du ballon. On dit bonjour à le poulain. Sarah écoute d'abord. Bonjour. Tu as écouté. Si malaise, tu racontes. Je raconte à la maison. Bravo, Sarah. On t'écoute. Sarah pose le ballon, tout doux. Le foin sent encore le soleil.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13116,10 +13989,28 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Sami. On entend un oiseau. On attend son tour. Cette fin-là est celle de les balançoires, le ballon et Sami. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr"/>
+          <t>narrateur|Le poulain souffle par le nez, tout chaud.
+narrateur|Sa crinière est douce, un peu en bataille.
+narrateur|Le foin sent bon, tout près.
+narrateur|Sarah a encore le ballon, près de les balançoires.
+narrateur|Le poulain secoue la crinière, près du ballon.
+papa|On dit bonjour à le poulain.
+narrateur|Sarah écoute d'abord.
+enfant-f|Bonjour.
+maman|Tu as écouté.
+maman|Si malaise, tu racontes.
+enfant-f|Je raconte à la maison.
+papa|Bravo, Sarah.
+papa|On t'écoute.
+narrateur|Sarah pose le ballon, tout doux.
+narrateur|Le foin sent encore le soleil.</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>poulain,foin</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13144,7 +14035,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Sarah a vu le poulain, près de les balançoires. Elle avait le ballon. Bravo, Sarah. C'est du bon travail. Merci, papa. Merci, maman. Le poulain pose le nez dans le foin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13284,7 +14175,16 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Sarah a vu le poulain, près de les balançoires.
+narrateur|Elle avait le ballon.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|Le poulain pose le nez dans le foin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13312,7 +14212,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Sara a choisi le seau. On entend un oiseau. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara répète tout bas : écouter, si malaise raconter à la maison. On attend son tour. papa n'est pas loin.</t>
+          <t>Sarah prend le seau bleu. Un peu de sable tremble au fond. Le seau sonne, tout creux. Moi, je raconte le puits. Maman parle, tout près. Sarah écoute jusqu'au bout. Le seau est lourd. Tu as écouté. Si malaise, tu viens nous le dire. Je raconte à la maison. Bravo, Sarah. Sarah pose le seau, tout droit. Le seau penche un peu, près de l'herbe. On est encore près de les balançoires. On écoute. Si malaise, on raconte.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13452,10 +14352,29 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Sara a choisi le seau. On entend un oiseau. Le seau reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara répète tout bas : écouter, si malaise raconter à la maison. On attend son tour. papa n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr"/>
+          <t>narrateur|Sarah prend le seau bleu.
+narrateur|Un peu de sable tremble au fond.
+narrateur|Le seau sonne, tout creux.
+maman|Moi, je raconte le puits.
+narrateur|Maman parle, tout près.
+narrateur|Sarah écoute jusqu'au bout.
+enfant-f|Le seau est lourd.
+papa|Tu as écouté.
+papa|Si malaise, tu viens nous le dire.
+enfant-f|Je raconte à la maison.
+maman|Bravo, Sarah.
+narrateur|Sarah pose le seau, tout droit.
+narrateur|Le seau penche un peu, près de l'herbe.
+narrateur|On est encore près de les balançoires.
+maman|On écoute.
+maman|Si malaise, on raconte.</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>seau</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13480,7 +14399,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Au fond du pré, trois animaux sont là. La poule, la chèvre, ou le poulain ? On écoute d'abord. Puis on raconte.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13648,7 +14567,10 @@
       </c>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Au fond du pré, trois animaux sont là.
+papa|La poule, la chèvre, ou le poulain ?
+maman|On écoute d'abord.
+maman|Puis on raconte.</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr"/>
@@ -13676,7 +14598,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Tom. La couverture est douce. On souffle doucement. Cette fin-là est celle de les balançoires, le seau et Tom. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+          <t>La poule picore près de la haie. Elle fait cot cot, tout petit. Une plume blonde reste dans l'herbe. Sarah a encore le seau, près de les balançoires. La poule saute un peu, près du seau. On dit bonjour à la poule. Sarah écoute d'abord. Bonjour. Tu as écouté. Si malaise, tu racontes. Je raconte à la maison. Bravo, Sarah. On t'écoute. Sarah pose le seau, tout doux. Le foin sent encore le soleil.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13816,10 +14738,28 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Tom. La couverture est douce. On souffle doucement. Cette fin-là est celle de les balançoires, le seau et Tom. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr"/>
+          <t>narrateur|La poule picore près de la haie.
+narrateur|Elle fait cot cot, tout petit.
+narrateur|Une plume blonde reste dans l'herbe.
+narrateur|Sarah a encore le seau, près de les balançoires.
+narrateur|La poule saute un peu, près du seau.
+papa|On dit bonjour à la poule.
+narrateur|Sarah écoute d'abord.
+enfant-f|Bonjour.
+maman|Tu as écouté.
+maman|Si malaise, tu racontes.
+enfant-f|Je raconte à la maison.
+papa|Bravo, Sarah.
+papa|On t'écoute.
+narrateur|Sarah pose le seau, tout doux.
+narrateur|Le foin sent encore le soleil.</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>poule</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13844,7 +14784,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Sarah a vu la poule, près de les balançoires. Elle avait le seau. Bravo, Sarah. C'est du bon travail. Merci, papa. Merci, maman. La poule picore encore un grain, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -13984,7 +14924,16 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Sarah a vu la poule, près de les balançoires.
+narrateur|Elle avait le seau.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|La poule picore encore un grain, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -14012,7 +14961,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Léa. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le seau et Léa. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+          <t>La chèvre sonne sa clochette, tout léger. Elle mâche une feuille, tout lentement. Son poil est rêche, un peu chaud. Sarah a encore le seau, près de les balançoires. La chèvre s'approche. Sarah pose le seau. On dit bonjour à la chèvre. Sarah écoute d'abord. Bonjour. Tu as écouté. Si malaise, tu racontes. Je raconte à la maison. Bravo, Sarah. On t'écoute. Sarah pose le seau, tout doux. Le foin sent encore le soleil.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14152,10 +15101,29 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Léa. On entend un oiseau. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le seau et Léa. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX76" t="inlineStr"/>
+          <t>narrateur|La chèvre sonne sa clochette, tout léger.
+narrateur|Elle mâche une feuille, tout lentement.
+narrateur|Son poil est rêche, un peu chaud.
+narrateur|Sarah a encore le seau, près de les balançoires.
+narrateur|La chèvre s'approche.
+narrateur|Sarah pose le seau.
+papa|On dit bonjour à la chèvre.
+narrateur|Sarah écoute d'abord.
+enfant-f|Bonjour.
+maman|Tu as écouté.
+maman|Si malaise, tu racontes.
+enfant-f|Je raconte à la maison.
+papa|Bravo, Sarah.
+papa|On t'écoute.
+narrateur|Sarah pose le seau, tout doux.
+narrateur|Le foin sent encore le soleil.</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>clochette</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14180,7 +15148,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Sarah a vu la chèvre, près de les balançoires. Elle avait le seau. Bravo, Sarah. C'est du bon travail. Merci, papa. Merci, maman. La clochette sonne encore, tout léger. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14320,7 +15288,16 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Sarah a vu la chèvre, près de les balançoires.
+narrateur|Elle avait le seau.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|La clochette sonne encore, tout léger.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14348,7 +15325,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Sami. Ça sent le pain chaud. On attend son tour. Cette fin-là est celle de les balançoires, le seau et Sami. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+          <t>Le poulain souffle par le nez, tout chaud. Sa crinière est douce, un peu en bataille. Le foin sent bon, tout près. Sarah a encore le seau, près de les balançoires. Le poulain écoute. Le seau reste dans l'herbe. On dit bonjour à le poulain. Sarah écoute d'abord. Bonjour. Tu as écouté. Si malaise, tu racontes. Je raconte à la maison. Bravo, Sarah. On t'écoute. Sarah pose le seau, tout doux. Le foin sent encore le soleil.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14488,10 +15465,29 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Sami. Ça sent le pain chaud. On attend son tour. Cette fin-là est celle de les balançoires, le seau et Sami. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX78" t="inlineStr"/>
+          <t>narrateur|Le poulain souffle par le nez, tout chaud.
+narrateur|Sa crinière est douce, un peu en bataille.
+narrateur|Le foin sent bon, tout près.
+narrateur|Sarah a encore le seau, près de les balançoires.
+narrateur|Le poulain écoute.
+narrateur|Le seau reste dans l'herbe.
+papa|On dit bonjour à le poulain.
+narrateur|Sarah écoute d'abord.
+enfant-f|Bonjour.
+maman|Tu as écouté.
+maman|Si malaise, tu racontes.
+enfant-f|Je raconte à la maison.
+papa|Bravo, Sarah.
+papa|On t'écoute.
+narrateur|Sarah pose le seau, tout doux.
+narrateur|Le foin sent encore le soleil.</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>poulain,foin</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14516,7 +15512,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Sarah a vu le poulain, près de les balançoires. Elle avait le seau. Bravo, Sarah. C'est du bon travail. Merci, papa. Merci, maman. Le poulain pose le nez dans le foin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14656,7 +15652,16 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Sarah a vu le poulain, près de les balançoires.
+narrateur|Elle avait le seau.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|Le poulain pose le nez dans le foin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14684,7 +15689,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Sara a choisi le doudou. Ça sent le pain chaud. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara répète tout bas : écouter, si malaise raconter à la maison. On montre du doigt, sans courir. papa n'est pas loin.</t>
+          <t>Sarah prend le doudou gris. Une oreille est encore chaude. Le doudou sent le foin, un peu. Le doudou écoute, lui aussi. Papa parle tout bas. Sarah serre le doudou. J'ai encore un peu le ventre serré. Tu peux raconter. On t'écoute. Un camarade a chuchoté. Tu as bien fait de le dire. On écoute la maîtresse. Le doudou reste sur les genoux. Le doudou s'assoit sur l'assise, tout calme. On est encore près de les balançoires. On écoute. Si malaise, on raconte.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14824,7 +15829,23 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Sara a choisi le doudou. Ça sent le pain chaud. Le doudou reste à sa place, près de maman. maman montre le geste, lentement. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara répète tout bas : écouter, si malaise raconter à la maison. On montre du doigt, sans courir. papa n'est pas loin.</t>
+          <t>narrateur|Sarah prend le doudou gris.
+narrateur|Une oreille est encore chaude.
+narrateur|Le doudou sent le foin, un peu.
+papa|Le doudou écoute, lui aussi.
+narrateur|Papa parle tout bas.
+narrateur|Sarah serre le doudou.
+enfant-f|J'ai encore un peu le ventre serré.
+maman|Tu peux raconter.
+maman|On t'écoute.
+enfant-f|Un camarade a chuchoté.
+papa|Tu as bien fait de le dire.
+papa|On écoute la maîtresse.
+narrateur|Le doudou reste sur les genoux.
+narrateur|Le doudou s'assoit sur l'assise, tout calme.
+narrateur|On est encore près de les balançoires.
+maman|On écoute.
+maman|Si malaise, on raconte.</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr"/>
@@ -14852,7 +15873,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>Au fond du pré, trois animaux sont là. La poule, la chèvre, ou le poulain ? On écoute d'abord. Puis on raconte.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -15020,7 +16041,10 @@
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|Au fond du pré, trois animaux sont là.
+papa|La poule, la chèvre, ou le poulain ?
+maman|On écoute d'abord.
+maman|Puis on raconte.</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr"/>
@@ -15048,7 +16072,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Tom. On entend un oiseau. On souffle doucement. Cette fin-là est celle de les balançoires, le doudou et Tom. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+          <t>La poule picore près de la haie. Elle fait cot cot, tout petit. Une plume blonde reste dans l'herbe. Sarah a encore le doudou, près de les balançoires. Une plume blonde tombe près du doudou. On dit bonjour à la poule. Sarah écoute d'abord. Bonjour. Tu as écouté. Si malaise, tu racontes. Je raconte à la maison. Bravo, Sarah. On t'écoute. Sarah pose le doudou, tout doux. Le foin sent encore le soleil.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15188,10 +16212,28 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Tom. On entend un oiseau. On souffle doucement. Cette fin-là est celle de les balançoires, le doudou et Tom. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX82" t="inlineStr"/>
+          <t>narrateur|La poule picore près de la haie.
+narrateur|Elle fait cot cot, tout petit.
+narrateur|Une plume blonde reste dans l'herbe.
+narrateur|Sarah a encore le doudou, près de les balançoires.
+narrateur|Une plume blonde tombe près du doudou.
+papa|On dit bonjour à la poule.
+narrateur|Sarah écoute d'abord.
+enfant-f|Bonjour.
+maman|Tu as écouté.
+maman|Si malaise, tu racontes.
+enfant-f|Je raconte à la maison.
+papa|Bravo, Sarah.
+papa|On t'écoute.
+narrateur|Sarah pose le doudou, tout doux.
+narrateur|Le foin sent encore le soleil.</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>poule</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15216,7 +16258,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Sarah a vu la poule, près de les balançoires. Elle avait le doudou. Bravo, Sarah. C'est du bon travail. Merci, papa. Merci, maman. La poule picore encore un grain, tout loin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15356,7 +16398,16 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Sarah a vu la poule, près de les balançoires.
+narrateur|Elle avait le doudou.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|La poule picore encore un grain, tout loin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15384,7 +16435,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Léa. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le doudou et Léa. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+          <t>La chèvre sonne sa clochette, tout léger. Elle mâche une feuille, tout lentement. Son poil est rêche, un peu chaud. Sarah a encore le doudou, près de les balançoires. La chèvre cligne. Le doudou reste sur l'assise. On dit bonjour à la chèvre. Sarah écoute d'abord. Bonjour. Tu as écouté. Si malaise, tu racontes. Je raconte à la maison. Bravo, Sarah. On t'écoute. Sarah pose le doudou, tout doux. Le foin sent encore le soleil.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15524,10 +16575,29 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Léa. Ça sent le pain chaud. On écoute jusqu'au bout. Cette fin-là est celle de les balançoires, le doudou et Léa. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX84" t="inlineStr"/>
+          <t>narrateur|La chèvre sonne sa clochette, tout léger.
+narrateur|Elle mâche une feuille, tout lentement.
+narrateur|Son poil est rêche, un peu chaud.
+narrateur|Sarah a encore le doudou, près de les balançoires.
+narrateur|La chèvre cligne.
+narrateur|Le doudou reste sur l'assise.
+papa|On dit bonjour à la chèvre.
+narrateur|Sarah écoute d'abord.
+enfant-f|Bonjour.
+maman|Tu as écouté.
+maman|Si malaise, tu racontes.
+enfant-f|Je raconte à la maison.
+papa|Bravo, Sarah.
+papa|On t'écoute.
+narrateur|Sarah pose le doudou, tout doux.
+narrateur|Le foin sent encore le soleil.</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>clochette</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15552,7 +16622,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Sarah a vu la chèvre, près de les balançoires. Elle avait le doudou. Bravo, Sarah. C'est du bon travail. Merci, papa. Merci, maman. La clochette sonne encore, tout léger. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15692,7 +16762,16 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Sarah a vu la chèvre, près de les balançoires.
+narrateur|Elle avait le doudou.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|La clochette sonne encore, tout léger.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15720,7 +16799,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Sara rejoint Sami. Le vent est doux. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Sami. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
+          <t>Le poulain souffle par le nez, tout chaud. Sa crinière est douce, un peu en bataille. Le foin sent bon, tout près. Sarah a encore le doudou, près de les balançoires. Le poulain souffle chaud, loin du doudou. On dit bonjour à le poulain. Sarah écoute d'abord. Bonjour. Tu as écouté. Si malaise, tu racontes. Je raconte à la maison. Bravo, Sarah. On t'écoute. Sarah pose le doudou, tout doux. Le foin sent encore le soleil.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15860,10 +16939,28 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Sara rejoint Sami. Le vent est doux. On attend son tour. Cette fin-là est celle de les balançoires, le doudou et Sami. Sara a appris : Écouter la maîtresse, en parler à la maison. Voici le geste : écouter ; raconter à papa ou maman si malaise. Sara a entendu : écouter, si malaise raconter à la maison. Sara dit merci à maman. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX86" t="inlineStr"/>
+          <t>narrateur|Le poulain souffle par le nez, tout chaud.
+narrateur|Sa crinière est douce, un peu en bataille.
+narrateur|Le foin sent bon, tout près.
+narrateur|Sarah a encore le doudou, près de les balançoires.
+narrateur|Le poulain souffle chaud, loin du doudou.
+papa|On dit bonjour à le poulain.
+narrateur|Sarah écoute d'abord.
+enfant-f|Bonjour.
+maman|Tu as écouté.
+maman|Si malaise, tu racontes.
+enfant-f|Je raconte à la maison.
+papa|Bravo, Sarah.
+papa|On t'écoute.
+narrateur|Sarah pose le doudou, tout doux.
+narrateur|Le foin sent encore le soleil.</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>poulain,foin</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15888,7 +16985,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Tu as écouté la maîtresse. Puis tu as raconté. Sarah a vu le poulain, près de les balançoires. Elle avait le doudou. Bravo, Sarah. C'est du bon travail. Merci, papa. Merci, maman. Le poulain pose le nez dans le foin. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -16028,7 +17125,16 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>maman|Tu as écouté la maîtresse.
+maman|Puis tu as raconté.
+narrateur|Sarah a vu le poulain, près de les balançoires.
+narrateur|Elle avait le doudou.
+papa|Bravo, Sarah.
+papa|C'est du bon travail.
+enfant-f|Merci, papa.
+enfant-f|Merci, maman.
+narrateur|Le poulain pose le nez dans le foin.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -16050,7 +17156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16144,6 +17250,13 @@
       <c r="A13" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-COL-029.xlsx
+++ b/stories/arbres/TREE-COL-029.xlsx
@@ -2752,17 +2752,17 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Près de le bac à sable, la poule picore autour du ballon. Elle tourne. Une plume blonde reste dans l'herbe. La voix a dit : son œuf est à nous. Sarah avance la main. Puis elle la retire. Elle se baisse. Elle regarde d'abord. Sous l'aile, un creux tiède, un œuf. On ne prend pas. On pose le foin à côté. Le ballon sert de borne, loin de l'œuf. Elle a son nid. Nous, le nôtre. J'ai regardé avant la main. La poule se recouche, cot cot, rassurée. Bravo. Tu as vu, puis tu as parlé.</t>
+          <t>Près du bac à sable, la poule picore autour du ballon. Elle tourne. Une plume blonde reste dans l'herbe. La voix a dit : son œuf est à nous. Sarah avance la main. Puis elle la retire. Elle se baisse. Elle regarde d'abord. Sous l'aile, un creux tiède, un œuf. On ne prend pas. On pose le foin à côté. Le ballon sert de borne, loin de l'œuf. Elle a son nid. Nous, le nôtre. J'ai regardé avant la main. La poule se recouche, cot cot, rassurée. Tes yeux ont parlé avant ta main.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Près de le bac à sable, la &lt;emphasis level="moderate"&gt;poule&lt;/emphasis&gt; picore autour du ballon. Elle tourne. Une plume blonde reste dans l'herbe. La voix a dit : son œuf est à nous. Sarah avance la main. Puis elle la retire. Elle se baisse. Elle regarde d'abord. Sous l'aile, un creux tiède, un œuf. On ne prend pas. On pose le foin à côté. Le ballon sert de borne, loin de l'œuf. Elle a son nid. Nous, le nôtre. J'ai regardé avant la main. La poule se recouche, cot cot, rassurée. Bravo. Tu as vu, puis tu as parlé.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Près du bac à sable, la &lt;emphasis level="moderate"&gt;poule&lt;/emphasis&gt; picore autour du ballon. Elle tourne. Une plume blonde reste dans l'herbe. La voix a dit : son œuf est à nous. Sarah avance la main. Puis elle la retire. Elle se baisse. Elle regarde d'abord. Sous l'aile, un creux tiède, un œuf. On ne prend pas. On pose le foin à côté. Le ballon sert de borne, loin de l'œuf. Elle a son nid. Nous, le nôtre. J'ai regardé avant la main. La poule se recouche, cot cot, rassurée. Tes yeux ont parlé avant ta main.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Près de le bac à sable, la &lt;emphasis&gt;poule&lt;/emphasis&gt; picore autour du ballon. Elle tourne. Une plume blonde reste dans l'herbe. La voix a dit : son œuf est à nous. Sarah avance la main. Puis elle la retire. Elle se baisse. Elle regarde d'abord. Sous l'aile, un creux tiède, un œuf. On ne prend pas. On pose le foin à côté. Le ballon sert de borne, loin de l'œuf. Elle a son nid. Nous, le nôtre. J'ai regardé avant la main. La poule se recouche, cot cot, rassurée. Bravo. Tu as vu, puis tu as parlé. [pause]</t>
+          <t>Près du bac à sable, la &lt;emphasis&gt;poule&lt;/emphasis&gt; picore autour du ballon. Elle tourne. Une plume blonde reste dans l'herbe. La voix a dit : son œuf est à nous. Sarah avance la main. Puis elle la retire. Elle se baisse. Elle regarde d'abord. Sous l'aile, un creux tiède, un œuf. On ne prend pas. On pose le foin à côté. Le ballon sert de borne, loin de l'œuf. Elle a son nid. Nous, le nôtre. J'ai regardé avant la main. La poule se recouche, cot cot, rassurée. Tes yeux ont parlé avant ta main. [pause]</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Près de le bac à sable, la poule picore autour du ballon.
+          <t>narrateur|Près du bac à sable, la poule picore autour du ballon.
 narrateur|Elle tourne.
 narrateur|Une plume blonde reste dans l'herbe.
 enfant-f|La voix a dit : son œuf est à nous.
@@ -2912,8 +2912,7 @@
 maman|Nous, le nôtre.
 enfant-f|J'ai regardé avant la main.
 narrateur|La poule se recouche, cot cot, rassurée.
-papa|Bravo.
-papa|Tu as vu, puis tu as parlé.</t>
+papa|Tes yeux ont parlé avant ta main.</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
@@ -3133,17 +3132,17 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>La chèvre pose le nez sur le ballon, près de le bac à sable. Sa clochette sonne, courte, un peu rêche. La voix a dit : elle ouvre le loquet, c'est drôle. Sarah voit le loquet, à demi tiré. Elle n'y touche pas toute seule. Papa, le loquet. La voix voulait que je rie. Moi, je n'ai pas ri. On le referme ensemble, alors. Le ballon roule hors du passage. Le foin, lui, va dans son coin à elle. La chèvre mâche. La clochette se tait. Merci d'avoir dit drôle, et pas drôle.</t>
+          <t>La chèvre pose le nez sur le ballon, près du bac à sable. Sa clochette sonne, courte, un peu rêche. La voix a dit : elle ouvre le loquet, c'est drôle. Sarah voit le loquet, à demi tiré. Elle n'y touche pas toute seule. Papa, le loquet. La voix voulait que je rie. Moi, je n'ai pas ri. On le referme ensemble, alors. Le ballon roule hors du passage. Le foin, lui, va dans son coin à elle. La chèvre mâche. La clochette se tait. Merci d'avoir dit drôle, et pas drôle.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La &lt;emphasis level="moderate"&gt;chèvre&lt;/emphasis&gt; pose le nez sur le ballon, près de le bac à sable. Sa clochette sonne, courte, un peu rêche. La voix a dit : elle ouvre le loquet, c'est drôle. Sarah voit le loquet, à demi tiré. Elle n'y touche pas toute seule. Papa, le loquet. La voix voulait que je rie. Moi, je n'ai pas ri. On le referme ensemble, alors. Le ballon roule hors du passage. Le foin, lui, va dans son coin à elle. La chèvre mâche. La clochette se tait. Merci d'avoir dit drôle, et pas drôle.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La &lt;emphasis level="moderate"&gt;chèvre&lt;/emphasis&gt; pose le nez sur le ballon, près du bac à sable. Sa clochette sonne, courte, un peu rêche. La voix a dit : elle ouvre le loquet, c'est drôle. Sarah voit le loquet, à demi tiré. Elle n'y touche pas toute seule. Papa, le loquet. La voix voulait que je rie. Moi, je n'ai pas ri. On le referme ensemble, alors. Le ballon roule hors du passage. Le foin, lui, va dans son coin à elle. La chèvre mâche. La clochette se tait. Merci d'avoir dit drôle, et pas drôle.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>La &lt;emphasis&gt;chèvre&lt;/emphasis&gt; pose le nez sur le ballon, près de le bac à sable. Sa clochette sonne, courte, un peu rêche. La voix a dit : elle ouvre le loquet, c'est drôle. Sarah voit le loquet, à demi tiré. Elle n'y touche pas toute seule. Papa, le loquet. La voix voulait que je rie. Moi, je n'ai pas ri. On le referme ensemble, alors. Le ballon roule hors du passage. Le foin, lui, va dans son coin à elle. La chèvre mâche. La clochette se tait. Merci d'avoir dit drôle, et pas drôle. [pause]</t>
+          <t>La &lt;emphasis&gt;chèvre&lt;/emphasis&gt; pose le nez sur le ballon, près du bac à sable. Sa clochette sonne, courte, un peu rêche. La voix a dit : elle ouvre le loquet, c'est drôle. Sarah voit le loquet, à demi tiré. Elle n'y touche pas toute seule. Papa, le loquet. La voix voulait que je rie. Moi, je n'ai pas ri. On le referme ensemble, alors. Le ballon roule hors du passage. Le foin, lui, va dans son coin à elle. La chèvre mâche. La clochette se tait. Merci d'avoir dit drôle, et pas drôle. [pause]</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
@@ -3277,7 +3276,7 @@
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|La chèvre pose le nez sur le ballon, près de le bac à sable.
+          <t>narrateur|La chèvre pose le nez sur le ballon, près du bac à sable.
 narrateur|Sa clochette sonne, courte, un peu rêche.
 enfant-f|La voix a dit : elle ouvre le loquet, c'est drôle.
 narrateur|Sarah voit le loquet, à demi tiré.
@@ -3322,17 +3321,17 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>La clochette sonne une dernière fois, courte. Le ballon, sablé, repose hors du passage. Le loquet est fermé. J'ai dit, au lieu de rire. Le gilet a perdu son brin de sable. La paille d'or brille encore sur le bois. Le linge rayé ne claque plus. La chèvre mâche, le poil tiède au vent. Le pré redevient large, jusqu'au saule.</t>
+          <t>La clochette sonne une dernière fois, courte. Le ballon, sablé, repose hors du passage. Le loquet est fermé. J'ai dit, au lieu de rire. Le gilet a perdu son brin de sable. La paille d'or brille sur le bois. Le linge rayé ne claque plus. La chèvre mâche, le poil tiède au vent. Le pré redevient large, jusqu'au saule.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;La clochette sonne une dernière fois, courte. Le ballon, sablé, repose hors du passage. Le loquet est fermé. J'ai dit, au lieu de rire. Le gilet a perdu son brin de sable. La &lt;emphasis level="moderate"&gt;paille d'or&lt;/emphasis&gt; brille encore sur le bois. Le linge rayé ne claque plus. La chèvre mâche, le poil tiède au vent. Le pré redevient large, jusqu'au saule.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;La clochette sonne une dernière fois, courte. Le ballon, sablé, repose hors du passage. Le loquet est fermé. J'ai dit, au lieu de rire. Le gilet a perdu son brin de sable. La &lt;emphasis level="moderate"&gt;paille d'or&lt;/emphasis&gt; brille sur le bois. Le linge rayé ne claque plus. La chèvre mâche, le poil tiède au vent. Le pré redevient large, jusqu'au saule.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;La clochette sonne une dernière fois, courte. Le ballon, sablé, repose hors du passage. Le loquet est fermé. J'ai dit, au lieu de rire. Le gilet a perdu son brin de sable. La &lt;emphasis&gt;paille d'or&lt;/emphasis&gt; brille encore sur le bois. Le linge rayé ne claque plus. La chèvre mâche, le poil tiède au vent. Le pré redevient large, jusqu'au saule.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;La clochette sonne une dernière fois, courte. Le ballon, sablé, repose hors du passage. Le loquet est fermé. J'ai dit, au lieu de rire. Le gilet a perdu son brin de sable. La &lt;emphasis&gt;paille d'or&lt;/emphasis&gt; brille sur le bois. Le linge rayé ne claque plus. La chèvre mâche, le poil tiède au vent. Le pré redevient large, jusqu'au saule.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
@@ -3475,7 +3474,7 @@
 enfant-f|Le loquet est fermé.
 enfant-f|J'ai dit, au lieu de rire.
 papa|Le gilet a perdu son brin de sable.
-narrateur|La paille d'or brille encore sur le bois.
+narrateur|La paille d'or brille sur le bois.
 maman|Le linge rayé ne claque plus.
 narrateur|La chèvre mâche, le poil tiède au vent.
 narrateur|Le pré redevient large, jusqu'au saule.</t>
@@ -3510,17 +3509,17 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Le poulain souffle, près de le bac à sable, loin du ballon. Sa crinière est en bataille, un peu claire. La voix a dit : agite le gilet, il court. Le gilet claque. Le poulain recule. Sarah s'arrête. Elle dégrafe le bouton. Je ne veux pas qu'il ait peur. On le plie, alors. Tout petit. Papa pose le ballon, loin des sabots. Sarah étale le foin, plat, sans le jeter. Le poulain avance. Son nez touche le foin. Il mange. Il ne court plus. Merci d'avoir retiré le gilet.</t>
+          <t>Le poulain souffle, près du bac à sable, loin du ballon. Sa crinière est en bataille, un peu claire. La voix a dit : agite le gilet, il court. Le gilet claque. Le poulain recule. Sarah s'arrête. Elle dégrafe le bouton. Je ne veux pas qu'il ait peur. On le plie, alors. Tout petit. Papa pose le ballon, loin des sabots. Sarah étale le foin, plat, sans le jeter. Le poulain avance. Son nez touche le foin. Il mange. Il ne court plus. Merci d'avoir retiré le gilet.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;poulain&lt;/emphasis&gt; souffle, près de le bac à sable, loin du ballon. Sa crinière est en bataille, un peu claire. La voix a dit : agite le gilet, il court. Le gilet claque. Le poulain recule. Sarah s'arrête. Elle dégrafe le bouton. Je ne veux pas qu'il ait peur. On le plie, alors. Tout petit. Papa pose le ballon, loin des sabots. Sarah étale le foin, plat, sans le jeter. Le poulain avance. Son nez touche le foin. Il mange. Il ne court plus. Merci d'avoir retiré le gilet.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;poulain&lt;/emphasis&gt; souffle, près du bac à sable, loin du ballon. Sa crinière est en bataille, un peu claire. La voix a dit : agite le gilet, il court. Le gilet claque. Le poulain recule. Sarah s'arrête. Elle dégrafe le bouton. Je ne veux pas qu'il ait peur. On le plie, alors. Tout petit. Papa pose le ballon, loin des sabots. Sarah étale le foin, plat, sans le jeter. Le poulain avance. Son nez touche le foin. Il mange. Il ne court plus. Merci d'avoir retiré le gilet.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Le &lt;emphasis&gt;poulain&lt;/emphasis&gt; souffle, près de le bac à sable, loin du ballon. Sa crinière est en bataille, un peu claire. La voix a dit : agite le gilet, il court. Le gilet claque. Le poulain recule. Sarah s'arrête. Elle dégrafe le bouton. Je ne veux pas qu'il ait peur. On le plie, alors. Tout petit. Papa pose le ballon, loin des sabots. Sarah étale le foin, plat, sans le jeter. Le poulain avance. Son nez touche le foin. Il mange. Il ne court plus. Merci d'avoir retiré le gilet. [pause]</t>
+          <t>Le &lt;emphasis&gt;poulain&lt;/emphasis&gt; souffle, près du bac à sable, loin du ballon. Sa crinière est en bataille, un peu claire. La voix a dit : agite le gilet, il court. Le gilet claque. Le poulain recule. Sarah s'arrête. Elle dégrafe le bouton. Je ne veux pas qu'il ait peur. On le plie, alors. Tout petit. Papa pose le ballon, loin des sabots. Sarah étale le foin, plat, sans le jeter. Le poulain avance. Son nez touche le foin. Il mange. Il ne court plus. Merci d'avoir retiré le gilet. [pause]</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
@@ -3654,7 +3653,7 @@
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Le poulain souffle, près de le bac à sable, loin du ballon.
+          <t>narrateur|Le poulain souffle, près du bac à sable, loin du ballon.
 narrateur|Sa crinière est en bataille, un peu claire.
 enfant-f|La voix a dit : agite le gilet, il court.
 narrateur|Le gilet claque.
@@ -4277,17 +4276,17 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>La poule s'approche du seau, près de le bac à sable. Elle saute un peu. Un grain tombe. La voix a dit de prendre l'œuf, vite. Sarah pose le seau. Elle ne plonge pas. Elle compte les plumes, une, deux, trois. Tu regardes. C'est bien. Derrière le seau, un nid bas, un œuf chaud. Le foin va autour, pas dessus. Ils font un croissant de foin, à distance. Son nid à elle. Le nôtre à côté. La poule picore le bord, puis s'installe. Merci d'avoir posé le seau, pas la main.</t>
+          <t>La poule s'approche du seau, près du bac à sable. Elle saute un peu. Un grain tombe. La voix a dit de prendre l'œuf, vite. Sarah pose le seau. Elle ne plonge pas. Elle compte les plumes, une, deux, trois. Tu regardes. C'est bien. Derrière le seau, un nid bas, un œuf chaud. Le foin va autour, pas dessus. Ils font un croissant de foin, à distance. Son nid à elle. Le nôtre à côté. La poule picore le bord, puis s'installe. Merci d'avoir posé le seau, pas la main.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La &lt;emphasis level="moderate"&gt;poule&lt;/emphasis&gt; s'approche du seau, près de le bac à sable. Elle saute un peu. Un grain tombe. La voix a dit de prendre l'œuf, vite. Sarah pose le seau. Elle ne plonge pas. Elle compte les plumes, une, deux, trois. Tu regardes. C'est bien. Derrière le seau, un nid bas, un œuf chaud. Le foin va autour, pas dessus. Ils font un croissant de foin, à distance. Son nid à elle. Le nôtre à côté. La poule picore le bord, puis s'installe. Merci d'avoir posé le seau, pas la main.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La &lt;emphasis level="moderate"&gt;poule&lt;/emphasis&gt; s'approche du seau, près du bac à sable. Elle saute un peu. Un grain tombe. La voix a dit de prendre l'œuf, vite. Sarah pose le seau. Elle ne plonge pas. Elle compte les plumes, une, deux, trois. Tu regardes. C'est bien. Derrière le seau, un nid bas, un œuf chaud. Le foin va autour, pas dessus. Ils font un croissant de foin, à distance. Son nid à elle. Le nôtre à côté. La poule picore le bord, puis s'installe. Merci d'avoir posé le seau, pas la main.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>La &lt;emphasis&gt;poule&lt;/emphasis&gt; s'approche du seau, près de le bac à sable. Elle saute un peu. Un grain tombe. La voix a dit de prendre l'œuf, vite. Sarah pose le seau. Elle ne plonge pas. Elle compte les plumes, une, deux, trois. Tu regardes. C'est bien. Derrière le seau, un nid bas, un œuf chaud. Le foin va autour, pas dessus. Ils font un croissant de foin, à distance. Son nid à elle. Le nôtre à côté. La poule picore le bord, puis s'installe. Merci d'avoir posé le seau, pas la main. [pause]</t>
+          <t>La &lt;emphasis&gt;poule&lt;/emphasis&gt; s'approche du seau, près du bac à sable. Elle saute un peu. Un grain tombe. La voix a dit de prendre l'œuf, vite. Sarah pose le seau. Elle ne plonge pas. Elle compte les plumes, une, deux, trois. Tu regardes. C'est bien. Derrière le seau, un nid bas, un œuf chaud. Le foin va autour, pas dessus. Ils font un croissant de foin, à distance. Son nid à elle. Le nôtre à côté. La poule picore le bord, puis s'installe. Merci d'avoir posé le seau, pas la main. [pause]</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
@@ -4421,7 +4420,7 @@
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|La poule s'approche du seau, près de le bac à sable.
+          <t>narrateur|La poule s'approche du seau, près du bac à sable.
 narrateur|Elle saute un peu.
 narrateur|Un grain tombe.
 enfant-f|La voix a dit de prendre l'œuf, vite.
@@ -4655,17 +4654,17 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>La chèvre tire le foin du seau, près de le bac à sable. L'anse penche. La clochette s'énerve. La voix a dit de la laisser sortir. Sarah voit le loquet. Elle recule d'un pas. Maman, je n'ouvre pas. Ça me serre. On ferme. On lui donne le foin ici. Papa rabat le loquet. Clic, net. Sarah pose le seau contre la planche. La chèvre mange, le poil chaud, rassuré. Son dîner, pas la porte. Bravo. Tu as fermé la phrase, et le loquet. Un brin de foin reste sur sa barbe.</t>
+          <t>La chèvre tire le foin du seau, près du bac à sable. L'anse penche. La clochette s'énerve. La voix a dit de la laisser sortir. Sarah voit le loquet. Elle recule d'un pas. Maman, je n'ouvre pas. Ça me serre. On ferme. On lui donne le foin ici. Papa rabat le loquet. Clic, net. Sarah pose le seau contre la planche. La chèvre mange, le poil chaud, rassuré. Son dîner, pas la porte. La phrase est fermée, et le loquet aussi. Un brin de foin reste sur sa barbe.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La &lt;emphasis level="moderate"&gt;chèvre&lt;/emphasis&gt; tire le foin du seau, près de le bac à sable. L'anse penche. La clochette s'énerve. La voix a dit de la laisser sortir. Sarah voit le loquet. Elle recule d'un pas. Maman, je n'ouvre pas. Ça me serre. On ferme. On lui donne le foin ici. Papa rabat le loquet. Clic, net. Sarah pose le seau contre la planche. La chèvre mange, le poil chaud, rassuré. Son dîner, pas la porte. Bravo. Tu as fermé la phrase, et le loquet. Un brin de foin reste sur sa barbe.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La &lt;emphasis level="moderate"&gt;chèvre&lt;/emphasis&gt; tire le foin du seau, près du bac à sable. L'anse penche. La clochette s'énerve. La voix a dit de la laisser sortir. Sarah voit le loquet. Elle recule d'un pas. Maman, je n'ouvre pas. Ça me serre. On ferme. On lui donne le foin ici. Papa rabat le loquet. Clic, net. Sarah pose le seau contre la planche. La chèvre mange, le poil chaud, rassuré. Son dîner, pas la porte. La phrase est fermée, et le loquet aussi. Un brin de foin reste sur sa barbe.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>La &lt;emphasis&gt;chèvre&lt;/emphasis&gt; tire le foin du seau, près de le bac à sable. L'anse penche. La clochette s'énerve. La voix a dit de la laisser sortir. Sarah voit le loquet. Elle recule d'un pas. Maman, je n'ouvre pas. Ça me serre. On ferme. On lui donne le foin ici. Papa rabat le loquet. Clic, net. Sarah pose le seau contre la planche. La chèvre mange, le poil chaud, rassuré. Son dîner, pas la porte. Bravo. Tu as fermé la phrase, et le loquet. Un brin de foin reste sur sa barbe. [pause]</t>
+          <t>La &lt;emphasis&gt;chèvre&lt;/emphasis&gt; tire le foin du seau, près du bac à sable. L'anse penche. La clochette s'énerve. La voix a dit de la laisser sortir. Sarah voit le loquet. Elle recule d'un pas. Maman, je n'ouvre pas. Ça me serre. On ferme. On lui donne le foin ici. Papa rabat le loquet. Clic, net. Sarah pose le seau contre la planche. La chèvre mange, le poil chaud, rassuré. Son dîner, pas la porte. La phrase est fermée, et le loquet aussi. Un brin de foin reste sur sa barbe. [pause]</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
@@ -4799,7 +4798,7 @@
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|La chèvre tire le foin du seau, près de le bac à sable.
+          <t>narrateur|La chèvre tire le foin du seau, près du bac à sable.
 narrateur|L'anse penche.
 narrateur|La clochette s'énerve.
 enfant-f|La voix a dit de la laisser sortir.
@@ -4814,8 +4813,7 @@
 narrateur|Sarah pose le seau contre la planche.
 narrateur|La chèvre mange, le poil chaud, rassuré.
 enfant-f|Son dîner, pas la porte.
-papa|Bravo.
-papa|Tu as fermé la phrase, et le loquet.
+papa|La phrase est fermée, et le loquet aussi.
 narrateur|Un brin de foin reste sur sa barbe.</t>
         </is>
       </c>
@@ -5035,17 +5033,17 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Le poulain renifle le seau, près de le bac à sable. Le gilet claque au vent. Il recule. La voix a dit de faire peur, pour rire. Rire, là, ça me serre. Sarah enlève le gilet. Elle le tend à maman. Je le tiens, plié, contre moi. Papa pose le seau. Le foin dépasse, calme. Le poulain revient. Son souffle est chaud. Il croque. Une paille d'or bouge sur sa lèvre. J'ai dit le rire. Puis je l'ai arrêté. Bravo. Il mange, sans courir. Le seau reste, vide, comme une auge.</t>
+          <t>Le poulain renifle le seau, près du bac à sable. Le gilet claque au vent. Il recule. La voix a dit de faire peur, pour rire. Rire, là, ça me serre. Sarah enlève le gilet. Elle le tend à maman. Je le tiens, plié, contre moi. Papa pose le seau. Le foin dépasse, calme. Le poulain revient. Son souffle est chaud. Il croque. Une paille d'or bouge sur sa lèvre. J'ai dit le rire. Puis je l'ai arrêté. Il mange, sans courir. Le seau reste, vide, comme une auge.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;poulain&lt;/emphasis&gt; renifle le seau, près de le bac à sable. Le gilet claque au vent. Il recule. La voix a dit de faire peur, pour rire. Rire, là, ça me serre. Sarah enlève le gilet. Elle le tend à maman. Je le tiens, plié, contre moi. Papa pose le seau. Le foin dépasse, calme. Le poulain revient. Son souffle est chaud. Il croque. Une paille d'or bouge sur sa lèvre. J'ai dit le rire. Puis je l'ai arrêté. Bravo. Il mange, sans courir. Le seau reste, vide, comme une auge.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;poulain&lt;/emphasis&gt; renifle le seau, près du bac à sable. Le gilet claque au vent. Il recule. La voix a dit de faire peur, pour rire. Rire, là, ça me serre. Sarah enlève le gilet. Elle le tend à maman. Je le tiens, plié, contre moi. Papa pose le seau. Le foin dépasse, calme. Le poulain revient. Son souffle est chaud. Il croque. Une paille d'or bouge sur sa lèvre. J'ai dit le rire. Puis je l'ai arrêté. Il mange, sans courir. Le seau reste, vide, comme une auge.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Le &lt;emphasis&gt;poulain&lt;/emphasis&gt; renifle le seau, près de le bac à sable. Le gilet claque au vent. Il recule. La voix a dit de faire peur, pour rire. Rire, là, ça me serre. Sarah enlève le gilet. Elle le tend à maman. Je le tiens, plié, contre moi. Papa pose le seau. Le foin dépasse, calme. Le poulain revient. Son souffle est chaud. Il croque. Une paille d'or bouge sur sa lèvre. J'ai dit le rire. Puis je l'ai arrêté. Bravo. Il mange, sans courir. Le seau reste, vide, comme une auge. [pause]</t>
+          <t>Le &lt;emphasis&gt;poulain&lt;/emphasis&gt; renifle le seau, près du bac à sable. Le gilet claque au vent. Il recule. La voix a dit de faire peur, pour rire. Rire, là, ça me serre. Sarah enlève le gilet. Elle le tend à maman. Je le tiens, plié, contre moi. Papa pose le seau. Le foin dépasse, calme. Le poulain revient. Son souffle est chaud. Il croque. Une paille d'or bouge sur sa lèvre. J'ai dit le rire. Puis je l'ai arrêté. Il mange, sans courir. Le seau reste, vide, comme une auge. [pause]</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
@@ -5179,7 +5177,7 @@
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Le poulain renifle le seau, près de le bac à sable.
+          <t>narrateur|Le poulain renifle le seau, près du bac à sable.
 narrateur|Le gilet claque au vent.
 narrateur|Il recule.
 enfant-f|La voix a dit de faire peur, pour rire.
@@ -5195,7 +5193,6 @@
 narrateur|Une paille d'or bouge sur sa lèvre.
 enfant-f|J'ai dit le rire.
 enfant-f|Puis je l'ai arrêté.
-papa|Bravo.
 papa|Il mange, sans courir.
 narrateur|Le seau reste, vide, comme une auge.</t>
         </is>
@@ -5805,17 +5802,17 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>La poule frôle le doudou, près de le bac à sable. Elle tire un fil gris, puis recule. La voix a dit : cache l'œuf dans le doudou. Sarah serre le doudou. Son ventre dit non. L'œuf n'est pas à cacher. Elle pose le doudou. Elle se penche. Un nid d'herbe, un œuf, tout près du bois. Le doudou veille, loin des pattes. Le foin fait un mur bas, pour le vent. Je n'ai rien pris. J'ai dit. La poule s'installe. L'œuf reste à elle. On a deux nids, et zéro secret lourd.</t>
+          <t>La poule frôle le doudou, près du bac à sable. Elle tire un fil gris, puis recule. La voix a dit : cache l'œuf dans le doudou. Sarah serre le doudou. Son ventre dit non. L'œuf n'est pas à cacher. Elle pose le doudou. Elle se penche. Un nid d'herbe, un œuf, tout près du bois. Le doudou veille, loin des pattes. Le foin fait un mur bas, pour le vent. Je n'ai rien pris. J'ai dit. La poule s'installe. L'œuf reste à elle. On a deux nids, et zéro secret lourd.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La &lt;emphasis level="moderate"&gt;poule&lt;/emphasis&gt; frôle le doudou, près de le bac à sable. Elle tire un fil gris, puis recule. La voix a dit : cache l'œuf dans le doudou. Sarah serre le doudou. Son ventre dit non. L'œuf n'est pas à cacher. Elle pose le doudou. Elle se penche. Un nid d'herbe, un œuf, tout près du bois. Le doudou veille, loin des pattes. Le foin fait un mur bas, pour le vent. Je n'ai rien pris. J'ai dit. La poule s'installe. L'œuf reste à elle. On a deux nids, et zéro secret lourd.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La &lt;emphasis level="moderate"&gt;poule&lt;/emphasis&gt; frôle le doudou, près du bac à sable. Elle tire un fil gris, puis recule. La voix a dit : cache l'œuf dans le doudou. Sarah serre le doudou. Son ventre dit non. L'œuf n'est pas à cacher. Elle pose le doudou. Elle se penche. Un nid d'herbe, un œuf, tout près du bois. Le doudou veille, loin des pattes. Le foin fait un mur bas, pour le vent. Je n'ai rien pris. J'ai dit. La poule s'installe. L'œuf reste à elle. On a deux nids, et zéro secret lourd.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>La &lt;emphasis&gt;poule&lt;/emphasis&gt; frôle le doudou, près de le bac à sable. Elle tire un fil gris, puis recule. La voix a dit : cache l'œuf dans le doudou. Sarah serre le doudou. Son ventre dit non. L'œuf n'est pas à cacher. Elle pose le doudou. Elle se penche. Un nid d'herbe, un œuf, tout près du bois. Le doudou veille, loin des pattes. Le foin fait un mur bas, pour le vent. Je n'ai rien pris. J'ai dit. La poule s'installe. L'œuf reste à elle. On a deux nids, et zéro secret lourd. [pause]</t>
+          <t>La &lt;emphasis&gt;poule&lt;/emphasis&gt; frôle le doudou, près du bac à sable. Elle tire un fil gris, puis recule. La voix a dit : cache l'œuf dans le doudou. Sarah serre le doudou. Son ventre dit non. L'œuf n'est pas à cacher. Elle pose le doudou. Elle se penche. Un nid d'herbe, un œuf, tout près du bois. Le doudou veille, loin des pattes. Le foin fait un mur bas, pour le vent. Je n'ai rien pris. J'ai dit. La poule s'installe. L'œuf reste à elle. On a deux nids, et zéro secret lourd. [pause]</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
@@ -5949,7 +5946,7 @@
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|La poule frôle le doudou, près de le bac à sable.
+          <t>narrateur|La poule frôle le doudou, près du bac à sable.
 narrateur|Elle tire un fil gris, puis recule.
 enfant-f|La voix a dit : cache l'œuf dans le doudou.
 narrateur|Sarah serre le doudou.
@@ -6185,17 +6182,17 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>La chèvre mâchonne le doudou, près de le bac à sable. Un fil gris pend à sa lèvre. Non ! Il n'est pas à manger ! Sarah tend la main, trop vite, trop près. Elle s'arrête. Elle appelle. Papa, le doudou. La voix a dit : laisse-la. On échange. Du foin contre le doudou. Maman tend le foin. La chèvre lâche le fil. Sarah reprend le doudou, un peu mouillé. J'ai demandé, au lieu de tirer. Merci. Le loquet, on le vérifie aussi. Clic. La clochette redevient petite.</t>
+          <t>La chèvre mâchonne le doudou, près du bac à sable. Un fil gris pend à sa lèvre. Non ! Il n'est pas à manger ! Sarah tend la main, trop vite, trop près. Elle s'arrête. Elle appelle. Papa, le doudou. La voix a dit : laisse-la. On échange. Du foin contre le doudou. Maman tend le foin. La chèvre lâche le fil. Sarah reprend le doudou, un peu mouillé. J'ai demandé, au lieu de tirer. Merci. Le loquet, on le vérifie aussi. Clic. La clochette redevient petite.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La &lt;emphasis level="moderate"&gt;chèvre&lt;/emphasis&gt; mâchonne le doudou, près de le bac à sable. Un fil gris pend à sa lèvre. Non ! Il n'est pas à manger ! Sarah tend la main, trop vite, trop près. Elle s'arrête. Elle appelle. Papa, le doudou. La voix a dit : laisse-la. On échange. Du foin contre le doudou. Maman tend le foin. La chèvre lâche le fil. Sarah reprend le doudou, un peu mouillé. J'ai demandé, au lieu de tirer. Merci. Le loquet, on le vérifie aussi. Clic. La clochette redevient petite.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La &lt;emphasis level="moderate"&gt;chèvre&lt;/emphasis&gt; mâchonne le doudou, près du bac à sable. Un fil gris pend à sa lèvre. Non ! Il n'est pas à manger ! Sarah tend la main, trop vite, trop près. Elle s'arrête. Elle appelle. Papa, le doudou. La voix a dit : laisse-la. On échange. Du foin contre le doudou. Maman tend le foin. La chèvre lâche le fil. Sarah reprend le doudou, un peu mouillé. J'ai demandé, au lieu de tirer. Merci. Le loquet, on le vérifie aussi. Clic. La clochette redevient petite.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>La &lt;emphasis&gt;chèvre&lt;/emphasis&gt; mâchonne le doudou, près de le bac à sable. Un fil gris pend à sa lèvre. Non ! Il n'est pas à manger ! Sarah tend la main, trop vite, trop près. Elle s'arrête. Elle appelle. Papa, le doudou. La voix a dit : laisse-la. On échange. Du foin contre le doudou. Maman tend le foin. La chèvre lâche le fil. Sarah reprend le doudou, un peu mouillé. J'ai demandé, au lieu de tirer. Merci. Le loquet, on le vérifie aussi. Clic. La clochette redevient petite. [pause]</t>
+          <t>La &lt;emphasis&gt;chèvre&lt;/emphasis&gt; mâchonne le doudou, près du bac à sable. Un fil gris pend à sa lèvre. Non ! Il n'est pas à manger ! Sarah tend la main, trop vite, trop près. Elle s'arrête. Elle appelle. Papa, le doudou. La voix a dit : laisse-la. On échange. Du foin contre le doudou. Maman tend le foin. La chèvre lâche le fil. Sarah reprend le doudou, un peu mouillé. J'ai demandé, au lieu de tirer. Merci. Le loquet, on le vérifie aussi. Clic. La clochette redevient petite. [pause]</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
@@ -6329,7 +6326,7 @@
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|La chèvre mâchonne le doudou, près de le bac à sable.
+          <t>narrateur|La chèvre mâchonne le doudou, près du bac à sable.
 narrateur|Un fil gris pend à sa lèvre.
 enfant-f|Non !
 enfant-f|Il n'est pas à manger !
@@ -6757,17 +6754,17 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Le doudou dort loin des sabots, dans l'herbe. Le poulain a refermé les naseaux, rassasié. Je me suis assise, au lieu de sauter. Le gilet, plié, tient chaud au panier. La paille d'or reste la gardienne du bois. Son souffle a fait un nid invisible. Une oreille grise a un brin, comme une broche. Le bac à sable garde un creux, vide et calme.</t>
+          <t>Le doudou dort loin des sabots, dans l'herbe. Le poulain a refermé les naseaux, rassasié. Je me suis assise, au lieu de sauter. Le gilet, plié, tient chaud au panier. La paille d'or reste la gardienne du bois. Son souffle a fait un nid invisible. Une oreille grise a un brin, comme une broche. Le bac à sable garde un creux, vide et lisse.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le doudou dort loin des sabots, dans l'herbe. Le poulain a refermé les naseaux, rassasié. Je me suis assise, au lieu de sauter. Le gilet, plié, tient chaud au panier. La &lt;emphasis level="moderate"&gt;paille d'or&lt;/emphasis&gt; reste la gardienne du bois. Son souffle a fait un nid invisible. Une oreille grise a un brin, comme une broche. Le bac à sable garde un creux, vide et calme.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le doudou dort loin des sabots, dans l'herbe. Le poulain a refermé les naseaux, rassasié. Je me suis assise, au lieu de sauter. Le gilet, plié, tient chaud au panier. La &lt;emphasis level="moderate"&gt;paille d'or&lt;/emphasis&gt; reste la gardienne du bois. Son souffle a fait un nid invisible. Une oreille grise a un brin, comme une broche. Le bac à sable garde un creux, vide et lisse.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le doudou dort loin des sabots, dans l'herbe. Le poulain a refermé les naseaux, rassasié. Je me suis assise, au lieu de sauter. Le gilet, plié, tient chaud au panier. La &lt;emphasis&gt;paille d'or&lt;/emphasis&gt; reste la gardienne du bois. Son souffle a fait un nid invisible. Une oreille grise a un brin, comme une broche. Le bac à sable garde un creux, vide et calme.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le doudou dort loin des sabots, dans l'herbe. Le poulain a refermé les naseaux, rassasié. Je me suis assise, au lieu de sauter. Le gilet, plié, tient chaud au panier. La &lt;emphasis&gt;paille d'or&lt;/emphasis&gt; reste la gardienne du bois. Son souffle a fait un nid invisible. Une oreille grise a un brin, comme une broche. Le bac à sable garde un creux, vide et lisse.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
@@ -6912,7 +6909,7 @@
 narrateur|La paille d'or reste la gardienne du bois.
 papa|Son souffle a fait un nid invisible.
 narrateur|Une oreille grise a un brin, comme une broche.
-narrateur|Le bac à sable garde un creux, vide et calme.</t>
+narrateur|Le bac à sable garde un creux, vide et lisse.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
@@ -8091,17 +8088,17 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Près de le toboggan, la poule picore autour du ballon. Elle tourne. Une plume blonde reste dans l'herbe. La voix a dit : son œuf est à nous. Sarah avance la main. Puis elle la retire. Elle se baisse. Elle regarde d'abord. Sous l'aile, un creux tiède, un œuf. On ne prend pas. On pose le foin à côté. Le ballon sert de borne, loin de l'œuf. Elle a son nid. Nous, le nôtre. J'ai regardé avant la main. La poule se recouche, cot cot, rassurée. Bravo. Tu as vu, puis tu as parlé.</t>
+          <t>Près du toboggan, la poule picore autour du ballon. Elle tourne. Une plume blonde reste dans l'herbe. La voix a dit : son œuf est à nous. Sarah avance la main. Puis elle la retire. Elle se baisse. Elle regarde d'abord. Sous l'aile, un creux tiède, un œuf. On ne prend pas. On pose le foin à côté. Le ballon sert de borne, loin de l'œuf. Elle a son nid. Nous, le nôtre. J'ai regardé avant la main. La poule se recouche, cot cot, rassurée. Tes yeux ont parlé avant ta main.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Près de le toboggan, la &lt;emphasis level="moderate"&gt;poule&lt;/emphasis&gt; picore autour du ballon. Elle tourne. Une plume blonde reste dans l'herbe. La voix a dit : son œuf est à nous. Sarah avance la main. Puis elle la retire. Elle se baisse. Elle regarde d'abord. Sous l'aile, un creux tiède, un œuf. On ne prend pas. On pose le foin à côté. Le ballon sert de borne, loin de l'œuf. Elle a son nid. Nous, le nôtre. J'ai regardé avant la main. La poule se recouche, cot cot, rassurée. Bravo. Tu as vu, puis tu as parlé.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Près du toboggan, la &lt;emphasis level="moderate"&gt;poule&lt;/emphasis&gt; picore autour du ballon. Elle tourne. Une plume blonde reste dans l'herbe. La voix a dit : son œuf est à nous. Sarah avance la main. Puis elle la retire. Elle se baisse. Elle regarde d'abord. Sous l'aile, un creux tiède, un œuf. On ne prend pas. On pose le foin à côté. Le ballon sert de borne, loin de l'œuf. Elle a son nid. Nous, le nôtre. J'ai regardé avant la main. La poule se recouche, cot cot, rassurée. Tes yeux ont parlé avant ta main.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Près de le toboggan, la &lt;emphasis&gt;poule&lt;/emphasis&gt; picore autour du ballon. Elle tourne. Une plume blonde reste dans l'herbe. La voix a dit : son œuf est à nous. Sarah avance la main. Puis elle la retire. Elle se baisse. Elle regarde d'abord. Sous l'aile, un creux tiède, un œuf. On ne prend pas. On pose le foin à côté. Le ballon sert de borne, loin de l'œuf. Elle a son nid. Nous, le nôtre. J'ai regardé avant la main. La poule se recouche, cot cot, rassurée. Bravo. Tu as vu, puis tu as parlé. [pause]</t>
+          <t>Près du toboggan, la &lt;emphasis&gt;poule&lt;/emphasis&gt; picore autour du ballon. Elle tourne. Une plume blonde reste dans l'herbe. La voix a dit : son œuf est à nous. Sarah avance la main. Puis elle la retire. Elle se baisse. Elle regarde d'abord. Sous l'aile, un creux tiède, un œuf. On ne prend pas. On pose le foin à côté. Le ballon sert de borne, loin de l'œuf. Elle a son nid. Nous, le nôtre. J'ai regardé avant la main. La poule se recouche, cot cot, rassurée. Tes yeux ont parlé avant ta main. [pause]</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr"/>
@@ -8235,7 +8232,7 @@
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Près de le toboggan, la poule picore autour du ballon.
+          <t>narrateur|Près du toboggan, la poule picore autour du ballon.
 narrateur|Elle tourne.
 narrateur|Une plume blonde reste dans l'herbe.
 enfant-f|La voix a dit : son œuf est à nous.
@@ -8251,8 +8248,7 @@
 maman|Nous, le nôtre.
 enfant-f|J'ai regardé avant la main.
 narrateur|La poule se recouche, cot cot, rassurée.
-papa|Bravo.
-papa|Tu as vu, puis tu as parlé.</t>
+papa|Tes yeux ont parlé avant ta main.</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
@@ -8472,17 +8468,17 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>La chèvre pose le nez sur le ballon, près de le toboggan. Sa clochette sonne, courte, un peu rêche. La voix a dit : elle ouvre le loquet, c'est drôle. Sarah voit le loquet, à demi tiré. Elle n'y touche pas toute seule. Papa, le loquet. La voix voulait que je rie. Moi, je n'ai pas ri. On le referme ensemble, alors. Le ballon roule hors du passage. Le foin, lui, va dans son coin à elle. La chèvre mâche. La clochette se tait. Merci d'avoir dit drôle, et pas drôle.</t>
+          <t>La chèvre pose le nez sur le ballon, près du toboggan. Sa clochette sonne, courte, un peu rêche. La voix a dit : elle ouvre le loquet, c'est drôle. Sarah voit le loquet, à demi tiré. Elle n'y touche pas toute seule. Papa, le loquet. La voix voulait que je rie. Moi, je n'ai pas ri. On le referme ensemble, alors. Le ballon roule hors du passage. Le foin, lui, va dans son coin à elle. La chèvre mâche. La clochette se tait. Merci d'avoir dit drôle, et pas drôle.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La &lt;emphasis level="moderate"&gt;chèvre&lt;/emphasis&gt; pose le nez sur le ballon, près de le toboggan. Sa clochette sonne, courte, un peu rêche. La voix a dit : elle ouvre le loquet, c'est drôle. Sarah voit le loquet, à demi tiré. Elle n'y touche pas toute seule. Papa, le loquet. La voix voulait que je rie. Moi, je n'ai pas ri. On le referme ensemble, alors. Le ballon roule hors du passage. Le foin, lui, va dans son coin à elle. La chèvre mâche. La clochette se tait. Merci d'avoir dit drôle, et pas drôle.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La &lt;emphasis level="moderate"&gt;chèvre&lt;/emphasis&gt; pose le nez sur le ballon, près du toboggan. Sa clochette sonne, courte, un peu rêche. La voix a dit : elle ouvre le loquet, c'est drôle. Sarah voit le loquet, à demi tiré. Elle n'y touche pas toute seule. Papa, le loquet. La voix voulait que je rie. Moi, je n'ai pas ri. On le referme ensemble, alors. Le ballon roule hors du passage. Le foin, lui, va dans son coin à elle. La chèvre mâche. La clochette se tait. Merci d'avoir dit drôle, et pas drôle.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>La &lt;emphasis&gt;chèvre&lt;/emphasis&gt; pose le nez sur le ballon, près de le toboggan. Sa clochette sonne, courte, un peu rêche. La voix a dit : elle ouvre le loquet, c'est drôle. Sarah voit le loquet, à demi tiré. Elle n'y touche pas toute seule. Papa, le loquet. La voix voulait que je rie. Moi, je n'ai pas ri. On le referme ensemble, alors. Le ballon roule hors du passage. Le foin, lui, va dans son coin à elle. La chèvre mâche. La clochette se tait. Merci d'avoir dit drôle, et pas drôle. [pause]</t>
+          <t>La &lt;emphasis&gt;chèvre&lt;/emphasis&gt; pose le nez sur le ballon, près du toboggan. Sa clochette sonne, courte, un peu rêche. La voix a dit : elle ouvre le loquet, c'est drôle. Sarah voit le loquet, à demi tiré. Elle n'y touche pas toute seule. Papa, le loquet. La voix voulait que je rie. Moi, je n'ai pas ri. On le referme ensemble, alors. Le ballon roule hors du passage. Le foin, lui, va dans son coin à elle. La chèvre mâche. La clochette se tait. Merci d'avoir dit drôle, et pas drôle. [pause]</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
@@ -8616,7 +8612,7 @@
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|La chèvre pose le nez sur le ballon, près de le toboggan.
+          <t>narrateur|La chèvre pose le nez sur le ballon, près du toboggan.
 narrateur|Sa clochette sonne, courte, un peu rêche.
 enfant-f|La voix a dit : elle ouvre le loquet, c'est drôle.
 narrateur|Sarah voit le loquet, à demi tiré.
@@ -8849,17 +8845,17 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Le poulain souffle, près de le toboggan, loin du ballon. Sa crinière est en bataille, un peu claire. La voix a dit : agite le gilet, il court. Le gilet claque. Le poulain recule. Sarah s'arrête. Elle dégrafe le bouton. Je ne veux pas qu'il ait peur. On le plie, alors. Tout petit. Papa pose le ballon, loin des sabots. Sarah étale le foin, plat, sans le jeter. Le poulain avance. Son nez touche le foin. Il mange. Il ne court plus. Merci d'avoir retiré le gilet.</t>
+          <t>Le poulain souffle, près du toboggan, loin du ballon. Sa crinière est en bataille, un peu claire. La voix a dit : agite le gilet, il court. Le gilet claque. Le poulain recule. Sarah s'arrête. Elle dégrafe le bouton. Je ne veux pas qu'il ait peur. On le plie, alors. Tout petit. Papa pose le ballon, loin des sabots. Sarah étale le foin, plat, sans le jeter. Le poulain avance. Son nez touche le foin. Il mange. Il ne court plus. Merci d'avoir retiré le gilet.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;poulain&lt;/emphasis&gt; souffle, près de le toboggan, loin du ballon. Sa crinière est en bataille, un peu claire. La voix a dit : agite le gilet, il court. Le gilet claque. Le poulain recule. Sarah s'arrête. Elle dégrafe le bouton. Je ne veux pas qu'il ait peur. On le plie, alors. Tout petit. Papa pose le ballon, loin des sabots. Sarah étale le foin, plat, sans le jeter. Le poulain avance. Son nez touche le foin. Il mange. Il ne court plus. Merci d'avoir retiré le gilet.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;poulain&lt;/emphasis&gt; souffle, près du toboggan, loin du ballon. Sa crinière est en bataille, un peu claire. La voix a dit : agite le gilet, il court. Le gilet claque. Le poulain recule. Sarah s'arrête. Elle dégrafe le bouton. Je ne veux pas qu'il ait peur. On le plie, alors. Tout petit. Papa pose le ballon, loin des sabots. Sarah étale le foin, plat, sans le jeter. Le poulain avance. Son nez touche le foin. Il mange. Il ne court plus. Merci d'avoir retiré le gilet.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Le &lt;emphasis&gt;poulain&lt;/emphasis&gt; souffle, près de le toboggan, loin du ballon. Sa crinière est en bataille, un peu claire. La voix a dit : agite le gilet, il court. Le gilet claque. Le poulain recule. Sarah s'arrête. Elle dégrafe le bouton. Je ne veux pas qu'il ait peur. On le plie, alors. Tout petit. Papa pose le ballon, loin des sabots. Sarah étale le foin, plat, sans le jeter. Le poulain avance. Son nez touche le foin. Il mange. Il ne court plus. Merci d'avoir retiré le gilet. [pause]</t>
+          <t>Le &lt;emphasis&gt;poulain&lt;/emphasis&gt; souffle, près du toboggan, loin du ballon. Sa crinière est en bataille, un peu claire. La voix a dit : agite le gilet, il court. Le gilet claque. Le poulain recule. Sarah s'arrête. Elle dégrafe le bouton. Je ne veux pas qu'il ait peur. On le plie, alors. Tout petit. Papa pose le ballon, loin des sabots. Sarah étale le foin, plat, sans le jeter. Le poulain avance. Son nez touche le foin. Il mange. Il ne court plus. Merci d'avoir retiré le gilet. [pause]</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr"/>
@@ -8993,7 +8989,7 @@
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Le poulain souffle, près de le toboggan, loin du ballon.
+          <t>narrateur|Le poulain souffle, près du toboggan, loin du ballon.
 narrateur|Sa crinière est en bataille, un peu claire.
 enfant-f|La voix a dit : agite le gilet, il court.
 narrateur|Le gilet claque.
@@ -9041,17 +9037,17 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Le poulain a quitté l'ombre du toboggan. Le ballon reste au pied, comme une borne. Le gilet est plié. Il ne fait plus peur. Sa crinière est redescendue. La paille d'or accroche le bois, pas le tissu. Tes paumes n'ont plus le piquant du métal. Un brin de foin glisse encore sur la rampe. Le hangar avale le dernier rond de soleil.</t>
+          <t>Le poulain a quitté l'ombre du toboggan. Le ballon reste au pied, comme une borne. Le gilet est plié. Il ne fait plus peur. Sa crinière est redescendue. La paille d'or accroche le bois, pas le tissu. Tes paumes n'ont plus le piquant du métal. Un brin de foin glisse sur la rampe. Le hangar avale le dernier rond de soleil.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le poulain a quitté l'ombre du toboggan. Le ballon reste au pied, comme une borne. Le gilet est plié. Il ne fait plus peur. Sa crinière est redescendue. La &lt;emphasis level="moderate"&gt;paille d'or&lt;/emphasis&gt; accroche le bois, pas le tissu. Tes paumes n'ont plus le piquant du métal. Un brin de foin glisse encore sur la rampe. Le hangar avale le dernier rond de soleil.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le poulain a quitté l'ombre du toboggan. Le ballon reste au pied, comme une borne. Le gilet est plié. Il ne fait plus peur. Sa crinière est redescendue. La &lt;emphasis level="moderate"&gt;paille d'or&lt;/emphasis&gt; accroche le bois, pas le tissu. Tes paumes n'ont plus le piquant du métal. Un brin de foin glisse sur la rampe. Le hangar avale le dernier rond de soleil.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le poulain a quitté l'ombre du toboggan. Le ballon reste au pied, comme une borne. Le gilet est plié. Il ne fait plus peur. Sa crinière est redescendue. La &lt;emphasis&gt;paille d'or&lt;/emphasis&gt; accroche le bois, pas le tissu. Tes paumes n'ont plus le piquant du métal. Un brin de foin glisse encore sur la rampe. Le hangar avale le dernier rond de soleil.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le poulain a quitté l'ombre du toboggan. Le ballon reste au pied, comme une borne. Le gilet est plié. Il ne fait plus peur. Sa crinière est redescendue. La &lt;emphasis&gt;paille d'or&lt;/emphasis&gt; accroche le bois, pas le tissu. Tes paumes n'ont plus le piquant du métal. Un brin de foin glisse sur la rampe. Le hangar avale le dernier rond de soleil.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
@@ -9196,7 +9192,7 @@
 papa|Sa crinière est redescendue.
 narrateur|La paille d'or accroche le bois, pas le tissu.
 maman|Tes paumes n'ont plus le piquant du métal.
-narrateur|Un brin de foin glisse encore sur la rampe.
+narrateur|Un brin de foin glisse sur la rampe.
 narrateur|Le hangar avale le dernier rond de soleil.</t>
         </is>
       </c>
@@ -9614,17 +9610,17 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>La poule s'approche du seau, près de le toboggan. Elle saute un peu. Un grain tombe. La voix a dit de prendre l'œuf, vite. Sarah pose le seau. Elle ne plonge pas. Elle compte les plumes, une, deux, trois. Tu regardes. C'est bien. Derrière le seau, un nid bas, un œuf chaud. Le foin va autour, pas dessus. Ils font un croissant de foin, à distance. Son nid à elle. Le nôtre à côté. La poule picore le bord, puis s'installe. Merci d'avoir posé le seau, pas la main.</t>
+          <t>La poule s'approche du seau, près du toboggan. Elle saute un peu. Un grain tombe. La voix a dit de prendre l'œuf, vite. Sarah pose le seau. Elle ne plonge pas. Elle compte les plumes, une, deux, trois. Tu regardes. C'est bien. Derrière le seau, un nid bas, un œuf chaud. Le foin va autour, pas dessus. Ils font un croissant de foin, à distance. Son nid à elle. Le nôtre à côté. La poule picore le bord, puis s'installe. Merci d'avoir posé le seau, pas la main.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La &lt;emphasis level="moderate"&gt;poule&lt;/emphasis&gt; s'approche du seau, près de le toboggan. Elle saute un peu. Un grain tombe. La voix a dit de prendre l'œuf, vite. Sarah pose le seau. Elle ne plonge pas. Elle compte les plumes, une, deux, trois. Tu regardes. C'est bien. Derrière le seau, un nid bas, un œuf chaud. Le foin va autour, pas dessus. Ils font un croissant de foin, à distance. Son nid à elle. Le nôtre à côté. La poule picore le bord, puis s'installe. Merci d'avoir posé le seau, pas la main.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La &lt;emphasis level="moderate"&gt;poule&lt;/emphasis&gt; s'approche du seau, près du toboggan. Elle saute un peu. Un grain tombe. La voix a dit de prendre l'œuf, vite. Sarah pose le seau. Elle ne plonge pas. Elle compte les plumes, une, deux, trois. Tu regardes. C'est bien. Derrière le seau, un nid bas, un œuf chaud. Le foin va autour, pas dessus. Ils font un croissant de foin, à distance. Son nid à elle. Le nôtre à côté. La poule picore le bord, puis s'installe. Merci d'avoir posé le seau, pas la main.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>La &lt;emphasis&gt;poule&lt;/emphasis&gt; s'approche du seau, près de le toboggan. Elle saute un peu. Un grain tombe. La voix a dit de prendre l'œuf, vite. Sarah pose le seau. Elle ne plonge pas. Elle compte les plumes, une, deux, trois. Tu regardes. C'est bien. Derrière le seau, un nid bas, un œuf chaud. Le foin va autour, pas dessus. Ils font un croissant de foin, à distance. Son nid à elle. Le nôtre à côté. La poule picore le bord, puis s'installe. Merci d'avoir posé le seau, pas la main. [pause]</t>
+          <t>La &lt;emphasis&gt;poule&lt;/emphasis&gt; s'approche du seau, près du toboggan. Elle saute un peu. Un grain tombe. La voix a dit de prendre l'œuf, vite. Sarah pose le seau. Elle ne plonge pas. Elle compte les plumes, une, deux, trois. Tu regardes. C'est bien. Derrière le seau, un nid bas, un œuf chaud. Le foin va autour, pas dessus. Ils font un croissant de foin, à distance. Son nid à elle. Le nôtre à côté. La poule picore le bord, puis s'installe. Merci d'avoir posé le seau, pas la main. [pause]</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
@@ -9758,7 +9754,7 @@
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|La poule s'approche du seau, près de le toboggan.
+          <t>narrateur|La poule s'approche du seau, près du toboggan.
 narrateur|Elle saute un peu.
 narrateur|Un grain tombe.
 enfant-f|La voix a dit de prendre l'œuf, vite.
@@ -9992,17 +9988,17 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>La chèvre tire le foin du seau, près de le toboggan. L'anse penche. La clochette s'énerve. La voix a dit de la laisser sortir. Sarah voit le loquet. Elle recule d'un pas. Maman, je n'ouvre pas. Ça me serre. On ferme. On lui donne le foin ici. Papa rabat le loquet. Clic, net. Sarah pose le seau contre la planche. La chèvre mange, le poil chaud, rassuré. Son dîner, pas la porte. Bravo. Tu as fermé la phrase, et le loquet. Un brin de foin reste sur sa barbe.</t>
+          <t>La chèvre tire le foin du seau, près du toboggan. L'anse penche. La clochette s'énerve. La voix a dit de la laisser sortir. Sarah voit le loquet. Elle recule d'un pas. Maman, je n'ouvre pas. Ça me serre. On ferme. On lui donne le foin ici. Papa rabat le loquet. Clic, net. Sarah pose le seau contre la planche. La chèvre mange, le poil chaud, rassuré. Son dîner, pas la porte. La phrase est fermée, et le loquet aussi. Un brin de foin reste sur sa barbe.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La &lt;emphasis level="moderate"&gt;chèvre&lt;/emphasis&gt; tire le foin du seau, près de le toboggan. L'anse penche. La clochette s'énerve. La voix a dit de la laisser sortir. Sarah voit le loquet. Elle recule d'un pas. Maman, je n'ouvre pas. Ça me serre. On ferme. On lui donne le foin ici. Papa rabat le loquet. Clic, net. Sarah pose le seau contre la planche. La chèvre mange, le poil chaud, rassuré. Son dîner, pas la porte. Bravo. Tu as fermé la phrase, et le loquet. Un brin de foin reste sur sa barbe.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La &lt;emphasis level="moderate"&gt;chèvre&lt;/emphasis&gt; tire le foin du seau, près du toboggan. L'anse penche. La clochette s'énerve. La voix a dit de la laisser sortir. Sarah voit le loquet. Elle recule d'un pas. Maman, je n'ouvre pas. Ça me serre. On ferme. On lui donne le foin ici. Papa rabat le loquet. Clic, net. Sarah pose le seau contre la planche. La chèvre mange, le poil chaud, rassuré. Son dîner, pas la porte. La phrase est fermée, et le loquet aussi. Un brin de foin reste sur sa barbe.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>La &lt;emphasis&gt;chèvre&lt;/emphasis&gt; tire le foin du seau, près de le toboggan. L'anse penche. La clochette s'énerve. La voix a dit de la laisser sortir. Sarah voit le loquet. Elle recule d'un pas. Maman, je n'ouvre pas. Ça me serre. On ferme. On lui donne le foin ici. Papa rabat le loquet. Clic, net. Sarah pose le seau contre la planche. La chèvre mange, le poil chaud, rassuré. Son dîner, pas la porte. Bravo. Tu as fermé la phrase, et le loquet. Un brin de foin reste sur sa barbe. [pause]</t>
+          <t>La &lt;emphasis&gt;chèvre&lt;/emphasis&gt; tire le foin du seau, près du toboggan. L'anse penche. La clochette s'énerve. La voix a dit de la laisser sortir. Sarah voit le loquet. Elle recule d'un pas. Maman, je n'ouvre pas. Ça me serre. On ferme. On lui donne le foin ici. Papa rabat le loquet. Clic, net. Sarah pose le seau contre la planche. La chèvre mange, le poil chaud, rassuré. Son dîner, pas la porte. La phrase est fermée, et le loquet aussi. Un brin de foin reste sur sa barbe. [pause]</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr"/>
@@ -10136,7 +10132,7 @@
       </c>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|La chèvre tire le foin du seau, près de le toboggan.
+          <t>narrateur|La chèvre tire le foin du seau, près du toboggan.
 narrateur|L'anse penche.
 narrateur|La clochette s'énerve.
 enfant-f|La voix a dit de la laisser sortir.
@@ -10151,8 +10147,7 @@
 narrateur|Sarah pose le seau contre la planche.
 narrateur|La chèvre mange, le poil chaud, rassuré.
 enfant-f|Son dîner, pas la porte.
-papa|Bravo.
-papa|Tu as fermé la phrase, et le loquet.
+papa|La phrase est fermée, et le loquet aussi.
 narrateur|Un brin de foin reste sur sa barbe.</t>
         </is>
       </c>
@@ -10373,17 +10368,17 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Le poulain renifle le seau, près de le toboggan. Le gilet claque au vent. Il recule. La voix a dit de faire peur, pour rire. Rire, là, ça me serre. Sarah enlève le gilet. Elle le tend à maman. Je le tiens, plié, contre moi. Papa pose le seau. Le foin dépasse, calme. Le poulain revient. Son souffle est chaud. Il croque. Une paille d'or bouge sur sa lèvre. J'ai dit le rire. Puis je l'ai arrêté. Bravo. Il mange, sans courir. Le seau reste, vide, comme une auge.</t>
+          <t>Le poulain renifle le seau, près du toboggan. Le gilet claque au vent. Il recule. La voix a dit de faire peur, pour rire. Rire, là, ça me serre. Sarah enlève le gilet. Elle le tend à maman. Je le tiens, plié, contre moi. Papa pose le seau. Le foin dépasse, calme. Le poulain revient. Son souffle est chaud. Il croque. Une paille d'or bouge sur sa lèvre. J'ai dit le rire. Puis je l'ai arrêté. Il mange, sans courir. Le seau reste, vide, comme une auge.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;poulain&lt;/emphasis&gt; renifle le seau, près de le toboggan. Le gilet claque au vent. Il recule. La voix a dit de faire peur, pour rire. Rire, là, ça me serre. Sarah enlève le gilet. Elle le tend à maman. Je le tiens, plié, contre moi. Papa pose le seau. Le foin dépasse, calme. Le poulain revient. Son souffle est chaud. Il croque. Une paille d'or bouge sur sa lèvre. J'ai dit le rire. Puis je l'ai arrêté. Bravo. Il mange, sans courir. Le seau reste, vide, comme une auge.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;poulain&lt;/emphasis&gt; renifle le seau, près du toboggan. Le gilet claque au vent. Il recule. La voix a dit de faire peur, pour rire. Rire, là, ça me serre. Sarah enlève le gilet. Elle le tend à maman. Je le tiens, plié, contre moi. Papa pose le seau. Le foin dépasse, calme. Le poulain revient. Son souffle est chaud. Il croque. Une paille d'or bouge sur sa lèvre. J'ai dit le rire. Puis je l'ai arrêté. Il mange, sans courir. Le seau reste, vide, comme une auge.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Le &lt;emphasis&gt;poulain&lt;/emphasis&gt; renifle le seau, près de le toboggan. Le gilet claque au vent. Il recule. La voix a dit de faire peur, pour rire. Rire, là, ça me serre. Sarah enlève le gilet. Elle le tend à maman. Je le tiens, plié, contre moi. Papa pose le seau. Le foin dépasse, calme. Le poulain revient. Son souffle est chaud. Il croque. Une paille d'or bouge sur sa lèvre. J'ai dit le rire. Puis je l'ai arrêté. Bravo. Il mange, sans courir. Le seau reste, vide, comme une auge. [pause]</t>
+          <t>Le &lt;emphasis&gt;poulain&lt;/emphasis&gt; renifle le seau, près du toboggan. Le gilet claque au vent. Il recule. La voix a dit de faire peur, pour rire. Rire, là, ça me serre. Sarah enlève le gilet. Elle le tend à maman. Je le tiens, plié, contre moi. Papa pose le seau. Le foin dépasse, calme. Le poulain revient. Son souffle est chaud. Il croque. Une paille d'or bouge sur sa lèvre. J'ai dit le rire. Puis je l'ai arrêté. Il mange, sans courir. Le seau reste, vide, comme une auge. [pause]</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
@@ -10517,7 +10512,7 @@
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Le poulain renifle le seau, près de le toboggan.
+          <t>narrateur|Le poulain renifle le seau, près du toboggan.
 narrateur|Le gilet claque au vent.
 narrateur|Il recule.
 enfant-f|La voix a dit de faire peur, pour rire.
@@ -10533,7 +10528,6 @@
 narrateur|Une paille d'or bouge sur sa lèvre.
 enfant-f|J'ai dit le rire.
 enfant-f|Puis je l'ai arrêté.
-papa|Bravo.
 papa|Il mange, sans courir.
 narrateur|Le seau reste, vide, comme une auge.</t>
         </is>
@@ -11140,17 +11134,17 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>La poule frôle le doudou, près de le toboggan. Elle tire un fil gris, puis recule. La voix a dit : cache l'œuf dans le doudou. Sarah serre le doudou. Son ventre dit non. L'œuf n'est pas à cacher. Elle pose le doudou. Elle se penche. Un nid d'herbe, un œuf, tout près du bois. Le doudou veille, loin des pattes. Le foin fait un mur bas, pour le vent. Je n'ai rien pris. J'ai dit. La poule s'installe. L'œuf reste à elle. On a deux nids, et zéro secret lourd.</t>
+          <t>La poule frôle le doudou, près du toboggan. Elle tire un fil gris, puis recule. La voix a dit : cache l'œuf dans le doudou. Sarah serre le doudou. Son ventre dit non. L'œuf n'est pas à cacher. Elle pose le doudou. Elle se penche. Un nid d'herbe, un œuf, tout près du bois. Le doudou veille, loin des pattes. Le foin fait un mur bas, pour le vent. Je n'ai rien pris. J'ai dit. La poule s'installe. L'œuf reste à elle. On a deux nids, et zéro secret lourd.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La &lt;emphasis level="moderate"&gt;poule&lt;/emphasis&gt; frôle le doudou, près de le toboggan. Elle tire un fil gris, puis recule. La voix a dit : cache l'œuf dans le doudou. Sarah serre le doudou. Son ventre dit non. L'œuf n'est pas à cacher. Elle pose le doudou. Elle se penche. Un nid d'herbe, un œuf, tout près du bois. Le doudou veille, loin des pattes. Le foin fait un mur bas, pour le vent. Je n'ai rien pris. J'ai dit. La poule s'installe. L'œuf reste à elle. On a deux nids, et zéro secret lourd.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La &lt;emphasis level="moderate"&gt;poule&lt;/emphasis&gt; frôle le doudou, près du toboggan. Elle tire un fil gris, puis recule. La voix a dit : cache l'œuf dans le doudou. Sarah serre le doudou. Son ventre dit non. L'œuf n'est pas à cacher. Elle pose le doudou. Elle se penche. Un nid d'herbe, un œuf, tout près du bois. Le doudou veille, loin des pattes. Le foin fait un mur bas, pour le vent. Je n'ai rien pris. J'ai dit. La poule s'installe. L'œuf reste à elle. On a deux nids, et zéro secret lourd.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>La &lt;emphasis&gt;poule&lt;/emphasis&gt; frôle le doudou, près de le toboggan. Elle tire un fil gris, puis recule. La voix a dit : cache l'œuf dans le doudou. Sarah serre le doudou. Son ventre dit non. L'œuf n'est pas à cacher. Elle pose le doudou. Elle se penche. Un nid d'herbe, un œuf, tout près du bois. Le doudou veille, loin des pattes. Le foin fait un mur bas, pour le vent. Je n'ai rien pris. J'ai dit. La poule s'installe. L'œuf reste à elle. On a deux nids, et zéro secret lourd. [pause]</t>
+          <t>La &lt;emphasis&gt;poule&lt;/emphasis&gt; frôle le doudou, près du toboggan. Elle tire un fil gris, puis recule. La voix a dit : cache l'œuf dans le doudou. Sarah serre le doudou. Son ventre dit non. L'œuf n'est pas à cacher. Elle pose le doudou. Elle se penche. Un nid d'herbe, un œuf, tout près du bois. Le doudou veille, loin des pattes. Le foin fait un mur bas, pour le vent. Je n'ai rien pris. J'ai dit. La poule s'installe. L'œuf reste à elle. On a deux nids, et zéro secret lourd. [pause]</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
@@ -11284,7 +11278,7 @@
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|La poule frôle le doudou, près de le toboggan.
+          <t>narrateur|La poule frôle le doudou, près du toboggan.
 narrateur|Elle tire un fil gris, puis recule.
 enfant-f|La voix a dit : cache l'œuf dans le doudou.
 narrateur|Sarah serre le doudou.
@@ -11518,17 +11512,17 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>La chèvre mâchonne le doudou, près de le toboggan. Un fil gris pend à sa lèvre. Non ! Il n'est pas à manger ! Sarah tend la main, trop vite, trop près. Elle s'arrête. Elle appelle. Papa, le doudou. La voix a dit : laisse-la. On échange. Du foin contre le doudou. Maman tend le foin. La chèvre lâche le fil. Sarah reprend le doudou, un peu mouillé. J'ai demandé, au lieu de tirer. Merci. Le loquet, on le vérifie aussi. Clic. La clochette redevient petite.</t>
+          <t>La chèvre mâchonne le doudou, près du toboggan. Un fil gris pend à sa lèvre. Non ! Il n'est pas à manger ! Sarah tend la main, trop vite, trop près. Elle s'arrête. Elle appelle. Papa, le doudou. La voix a dit : laisse-la. On échange. Du foin contre le doudou. Maman tend le foin. La chèvre lâche le fil. Sarah reprend le doudou, un peu mouillé. J'ai demandé, au lieu de tirer. Merci. Le loquet, on le vérifie aussi. Clic. La clochette redevient petite.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La &lt;emphasis level="moderate"&gt;chèvre&lt;/emphasis&gt; mâchonne le doudou, près de le toboggan. Un fil gris pend à sa lèvre. Non ! Il n'est pas à manger ! Sarah tend la main, trop vite, trop près. Elle s'arrête. Elle appelle. Papa, le doudou. La voix a dit : laisse-la. On échange. Du foin contre le doudou. Maman tend le foin. La chèvre lâche le fil. Sarah reprend le doudou, un peu mouillé. J'ai demandé, au lieu de tirer. Merci. Le loquet, on le vérifie aussi. Clic. La clochette redevient petite.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La &lt;emphasis level="moderate"&gt;chèvre&lt;/emphasis&gt; mâchonne le doudou, près du toboggan. Un fil gris pend à sa lèvre. Non ! Il n'est pas à manger ! Sarah tend la main, trop vite, trop près. Elle s'arrête. Elle appelle. Papa, le doudou. La voix a dit : laisse-la. On échange. Du foin contre le doudou. Maman tend le foin. La chèvre lâche le fil. Sarah reprend le doudou, un peu mouillé. J'ai demandé, au lieu de tirer. Merci. Le loquet, on le vérifie aussi. Clic. La clochette redevient petite.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>La &lt;emphasis&gt;chèvre&lt;/emphasis&gt; mâchonne le doudou, près de le toboggan. Un fil gris pend à sa lèvre. Non ! Il n'est pas à manger ! Sarah tend la main, trop vite, trop près. Elle s'arrête. Elle appelle. Papa, le doudou. La voix a dit : laisse-la. On échange. Du foin contre le doudou. Maman tend le foin. La chèvre lâche le fil. Sarah reprend le doudou, un peu mouillé. J'ai demandé, au lieu de tirer. Merci. Le loquet, on le vérifie aussi. Clic. La clochette redevient petite. [pause]</t>
+          <t>La &lt;emphasis&gt;chèvre&lt;/emphasis&gt; mâchonne le doudou, près du toboggan. Un fil gris pend à sa lèvre. Non ! Il n'est pas à manger ! Sarah tend la main, trop vite, trop près. Elle s'arrête. Elle appelle. Papa, le doudou. La voix a dit : laisse-la. On échange. Du foin contre le doudou. Maman tend le foin. La chèvre lâche le fil. Sarah reprend le doudou, un peu mouillé. J'ai demandé, au lieu de tirer. Merci. Le loquet, on le vérifie aussi. Clic. La clochette redevient petite. [pause]</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
@@ -11662,7 +11656,7 @@
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|La chèvre mâchonne le doudou, près de le toboggan.
+          <t>narrateur|La chèvre mâchonne le doudou, près du toboggan.
 narrateur|Un fil gris pend à sa lèvre.
 enfant-f|Non !
 enfant-f|Il n'est pas à manger !
@@ -11712,17 +11706,17 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Le doudou a un fil repris, encore un peu humide. La chèvre a échangé le gris contre le foin. J'étais sur la marche. J'ai parlé. Le loquet a entendu, lui aussi. Le gilet n'accroche plus la rampe. La paille d'or garde la barrière. Une clochette, très loin, fait un point d'or. Le toboggan devient gris, comme le doudou.</t>
+          <t>Le doudou a un fil repris, un peu humide. La chèvre a échangé le gris contre le foin. J'étais sur la marche. J'ai parlé. Le loquet a entendu, lui aussi. Le gilet n'accroche plus la rampe. La paille d'or garde la barrière. Une clochette, très loin, fait un point d'or. Le toboggan devient gris, comme le doudou.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le doudou a un fil repris, encore un peu humide. La chèvre a échangé le gris contre le foin. J'étais sur la marche. J'ai parlé. Le loquet a entendu, lui aussi. Le gilet n'accroche plus la rampe. La &lt;emphasis level="moderate"&gt;paille d'or&lt;/emphasis&gt; garde la barrière. Une clochette, très loin, fait un point d'or. Le toboggan devient gris, comme le doudou.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le doudou a un fil repris, un peu humide. La chèvre a échangé le gris contre le foin. J'étais sur la marche. J'ai parlé. Le loquet a entendu, lui aussi. Le gilet n'accroche plus la rampe. La &lt;emphasis level="moderate"&gt;paille d'or&lt;/emphasis&gt; garde la barrière. Une clochette, très loin, fait un point d'or. Le toboggan devient gris, comme le doudou.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le doudou a un fil repris, encore un peu humide. La chèvre a échangé le gris contre le foin. J'étais sur la marche. J'ai parlé. Le loquet a entendu, lui aussi. Le gilet n'accroche plus la rampe. La &lt;emphasis&gt;paille d'or&lt;/emphasis&gt; garde la barrière. Une clochette, très loin, fait un point d'or. Le toboggan devient gris, comme le doudou.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le doudou a un fil repris, un peu humide. La chèvre a échangé le gris contre le foin. J'étais sur la marche. J'ai parlé. Le loquet a entendu, lui aussi. Le gilet n'accroche plus la rampe. La &lt;emphasis&gt;paille d'or&lt;/emphasis&gt; garde la barrière. Une clochette, très loin, fait un point d'or. Le toboggan devient gris, comme le doudou.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr"/>
@@ -11860,7 +11854,7 @@
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|Le doudou a un fil repris, encore un peu humide.
+          <t>narrateur|Le doudou a un fil repris, un peu humide.
 narrateur|La chèvre a échangé le gris contre le foin.
 enfant-f|J'étais sur la marche.
 enfant-f|J'ai parlé.
@@ -12091,17 +12085,17 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Le doudou dort au pied du toboggan, loin des sabots. Le poulain a soufflé le foin, puis mangé. Je n'ai pas sauté. Tu t'es assise. Il est venu. Le gilet, plié, tient chaud aux œufs. La paille d'or n'a plus rien à retenir. La rampe garde une trace de poil gris. Le hangar ferme le jour, tout doucement.</t>
+          <t>Le doudou dort au pied du toboggan, loin des sabots. Le poulain a soufflé le foin, puis mangé. Je n'ai pas sauté. Tu t'es assise. Il est venu. Le gilet, plié, tient chaud aux œufs. La paille d'or n'a plus rien à retenir. La rampe garde une trace de poil gris. Le hangar ferme le jour, sans bruit.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le doudou dort au pied du toboggan, loin des sabots. Le poulain a soufflé le foin, puis mangé. Je n'ai pas sauté. Tu t'es assise. Il est venu. Le gilet, plié, tient chaud aux œufs. La &lt;emphasis level="moderate"&gt;paille d'or&lt;/emphasis&gt; n'a plus rien à retenir. La rampe garde une trace de poil gris. Le hangar ferme le jour, tout doucement.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Le doudou dort au pied du toboggan, loin des sabots. Le poulain a soufflé le foin, puis mangé. Je n'ai pas sauté. Tu t'es assise. Il est venu. Le gilet, plié, tient chaud aux œufs. La &lt;emphasis level="moderate"&gt;paille d'or&lt;/emphasis&gt; n'a plus rien à retenir. La rampe garde une trace de poil gris. Le hangar ferme le jour, sans bruit.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le doudou dort au pied du toboggan, loin des sabots. Le poulain a soufflé le foin, puis mangé. Je n'ai pas sauté. Tu t'es assise. Il est venu. Le gilet, plié, tient chaud aux œufs. La &lt;emphasis&gt;paille d'or&lt;/emphasis&gt; n'a plus rien à retenir. La rampe garde une trace de poil gris. Le hangar ferme le jour, tout doucement.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Le doudou dort au pied du toboggan, loin des sabots. Le poulain a soufflé le foin, puis mangé. Je n'ai pas sauté. Tu t'es assise. Il est venu. Le gilet, plié, tient chaud aux œufs. La &lt;emphasis&gt;paille d'or&lt;/emphasis&gt; n'a plus rien à retenir. La rampe garde une trace de poil gris. Le hangar ferme le jour, sans bruit.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
@@ -12247,7 +12241,7 @@
 narrateur|Le gilet, plié, tient chaud aux œufs.
 maman|La paille d'or n'a plus rien à retenir.
 narrateur|La rampe garde une trace de poil gris.
-narrateur|Le hangar ferme le jour, tout doucement.</t>
+narrateur|Le hangar ferme le jour, sans bruit.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
@@ -13425,17 +13419,17 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Près de les balançoires, la poule picore autour du ballon. Elle tourne. Une plume blonde reste dans l'herbe. La voix a dit : son œuf est à nous. Sarah avance la main. Puis elle la retire. Elle se baisse. Elle regarde d'abord. Sous l'aile, un creux tiède, un œuf. On ne prend pas. On pose le foin à côté. Le ballon sert de borne, loin de l'œuf. Elle a son nid. Nous, le nôtre. J'ai regardé avant la main. La poule se recouche, cot cot, rassurée. Bravo. Tu as vu, puis tu as parlé.</t>
+          <t>Près des balançoires, la poule picore autour du ballon. Elle tourne. Une plume blonde reste dans l'herbe. La voix a dit : son œuf est à nous. Sarah avance la main. Puis elle la retire. Elle se baisse. Elle regarde d'abord. Sous l'aile, un creux tiède, un œuf. On ne prend pas. On pose le foin à côté. Le ballon sert de borne, loin de l'œuf. Elle a son nid. Nous, le nôtre. J'ai regardé avant la main. La poule se recouche, cot cot, rassurée. Tes yeux ont parlé avant ta main.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Près de les balançoires, la &lt;emphasis level="moderate"&gt;poule&lt;/emphasis&gt; picore autour du ballon. Elle tourne. Une plume blonde reste dans l'herbe. La voix a dit : son œuf est à nous. Sarah avance la main. Puis elle la retire. Elle se baisse. Elle regarde d'abord. Sous l'aile, un creux tiède, un œuf. On ne prend pas. On pose le foin à côté. Le ballon sert de borne, loin de l'œuf. Elle a son nid. Nous, le nôtre. J'ai regardé avant la main. La poule se recouche, cot cot, rassurée. Bravo. Tu as vu, puis tu as parlé.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Près des balançoires, la &lt;emphasis level="moderate"&gt;poule&lt;/emphasis&gt; picore autour du ballon. Elle tourne. Une plume blonde reste dans l'herbe. La voix a dit : son œuf est à nous. Sarah avance la main. Puis elle la retire. Elle se baisse. Elle regarde d'abord. Sous l'aile, un creux tiède, un œuf. On ne prend pas. On pose le foin à côté. Le ballon sert de borne, loin de l'œuf. Elle a son nid. Nous, le nôtre. J'ai regardé avant la main. La poule se recouche, cot cot, rassurée. Tes yeux ont parlé avant ta main.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Près de les balançoires, la &lt;emphasis&gt;poule&lt;/emphasis&gt; picore autour du ballon. Elle tourne. Une plume blonde reste dans l'herbe. La voix a dit : son œuf est à nous. Sarah avance la main. Puis elle la retire. Elle se baisse. Elle regarde d'abord. Sous l'aile, un creux tiède, un œuf. On ne prend pas. On pose le foin à côté. Le ballon sert de borne, loin de l'œuf. Elle a son nid. Nous, le nôtre. J'ai regardé avant la main. La poule se recouche, cot cot, rassurée. Bravo. Tu as vu, puis tu as parlé. [pause]</t>
+          <t>Près des balançoires, la &lt;emphasis&gt;poule&lt;/emphasis&gt; picore autour du ballon. Elle tourne. Une plume blonde reste dans l'herbe. La voix a dit : son œuf est à nous. Sarah avance la main. Puis elle la retire. Elle se baisse. Elle regarde d'abord. Sous l'aile, un creux tiède, un œuf. On ne prend pas. On pose le foin à côté. Le ballon sert de borne, loin de l'œuf. Elle a son nid. Nous, le nôtre. J'ai regardé avant la main. La poule se recouche, cot cot, rassurée. Tes yeux ont parlé avant ta main. [pause]</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr"/>
@@ -13569,7 +13563,7 @@
       </c>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Près de les balançoires, la poule picore autour du ballon.
+          <t>narrateur|Près des balançoires, la poule picore autour du ballon.
 narrateur|Elle tourne.
 narrateur|Une plume blonde reste dans l'herbe.
 enfant-f|La voix a dit : son œuf est à nous.
@@ -13585,8 +13579,7 @@
 maman|Nous, le nôtre.
 enfant-f|J'ai regardé avant la main.
 narrateur|La poule se recouche, cot cot, rassurée.
-papa|Bravo.
-papa|Tu as vu, puis tu as parlé.</t>
+papa|Tes yeux ont parlé avant ta main.</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
@@ -13807,17 +13800,17 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>La chèvre pose le nez sur le ballon, près de les balançoires. Sa clochette sonne, courte, un peu rêche. La voix a dit : elle ouvre le loquet, c'est drôle. Sarah voit le loquet, à demi tiré. Elle n'y touche pas toute seule. Papa, le loquet. La voix voulait que je rie. Moi, je n'ai pas ri. On le referme ensemble, alors. Le ballon roule hors du passage. Le foin, lui, va dans son coin à elle. La chèvre mâche. La clochette se tait. Merci d'avoir dit drôle, et pas drôle.</t>
+          <t>La chèvre pose le nez sur le ballon, près des balançoires. Sa clochette sonne, courte, un peu rêche. La voix a dit : elle ouvre le loquet, c'est drôle. Sarah voit le loquet, à demi tiré. Elle n'y touche pas toute seule. Papa, le loquet. La voix voulait que je rie. Moi, je n'ai pas ri. On le referme ensemble, alors. Le ballon roule hors du passage. Le foin, lui, va dans son coin à elle. La chèvre mâche. La clochette se tait. Merci d'avoir dit drôle, et pas drôle.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La &lt;emphasis level="moderate"&gt;chèvre&lt;/emphasis&gt; pose le nez sur le ballon, près de les balançoires. Sa clochette sonne, courte, un peu rêche. La voix a dit : elle ouvre le loquet, c'est drôle. Sarah voit le loquet, à demi tiré. Elle n'y touche pas toute seule. Papa, le loquet. La voix voulait que je rie. Moi, je n'ai pas ri. On le referme ensemble, alors. Le ballon roule hors du passage. Le foin, lui, va dans son coin à elle. La chèvre mâche. La clochette se tait. Merci d'avoir dit drôle, et pas drôle.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La &lt;emphasis level="moderate"&gt;chèvre&lt;/emphasis&gt; pose le nez sur le ballon, près des balançoires. Sa clochette sonne, courte, un peu rêche. La voix a dit : elle ouvre le loquet, c'est drôle. Sarah voit le loquet, à demi tiré. Elle n'y touche pas toute seule. Papa, le loquet. La voix voulait que je rie. Moi, je n'ai pas ri. On le referme ensemble, alors. Le ballon roule hors du passage. Le foin, lui, va dans son coin à elle. La chèvre mâche. La clochette se tait. Merci d'avoir dit drôle, et pas drôle.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>La &lt;emphasis&gt;chèvre&lt;/emphasis&gt; pose le nez sur le ballon, près de les balançoires. Sa clochette sonne, courte, un peu rêche. La voix a dit : elle ouvre le loquet, c'est drôle. Sarah voit le loquet, à demi tiré. Elle n'y touche pas toute seule. Papa, le loquet. La voix voulait que je rie. Moi, je n'ai pas ri. On le referme ensemble, alors. Le ballon roule hors du passage. Le foin, lui, va dans son coin à elle. La chèvre mâche. La clochette se tait. Merci d'avoir dit drôle, et pas drôle. [pause]</t>
+          <t>La &lt;emphasis&gt;chèvre&lt;/emphasis&gt; pose le nez sur le ballon, près des balançoires. Sa clochette sonne, courte, un peu rêche. La voix a dit : elle ouvre le loquet, c'est drôle. Sarah voit le loquet, à demi tiré. Elle n'y touche pas toute seule. Papa, le loquet. La voix voulait que je rie. Moi, je n'ai pas ri. On le referme ensemble, alors. Le ballon roule hors du passage. Le foin, lui, va dans son coin à elle. La chèvre mâche. La clochette se tait. Merci d'avoir dit drôle, et pas drôle. [pause]</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr"/>
@@ -13951,7 +13944,7 @@
       </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|La chèvre pose le nez sur le ballon, près de les balançoires.
+          <t>narrateur|La chèvre pose le nez sur le ballon, près des balançoires.
 narrateur|Sa clochette sonne, courte, un peu rêche.
 enfant-f|La voix a dit : elle ouvre le loquet, c'est drôle.
 narrateur|Sarah voit le loquet, à demi tiré.
@@ -14185,17 +14178,17 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Le poulain souffle, près de les balançoires, loin du ballon. Sa crinière est en bataille, un peu claire. La voix a dit : agite le gilet, il court. Le gilet claque. Le poulain recule. Sarah s'arrête. Elle dégrafe le bouton. Je ne veux pas qu'il ait peur. On le plie, alors. Tout petit. Papa pose le ballon, loin des sabots. Sarah étale le foin, plat, sans le jeter. Le poulain avance. Son nez touche le foin. Il mange. Il ne court plus. Merci d'avoir retiré le gilet.</t>
+          <t>Le poulain souffle, près des balançoires, loin du ballon. Sa crinière est en bataille, un peu claire. La voix a dit : agite le gilet, il court. Le gilet claque. Le poulain recule. Sarah s'arrête. Elle dégrafe le bouton. Je ne veux pas qu'il ait peur. On le plie, alors. Tout petit. Papa pose le ballon, loin des sabots. Sarah étale le foin, plat, sans le jeter. Le poulain avance. Son nez touche le foin. Il mange. Il ne court plus. Merci d'avoir retiré le gilet.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;poulain&lt;/emphasis&gt; souffle, près de les balançoires, loin du ballon. Sa crinière est en bataille, un peu claire. La voix a dit : agite le gilet, il court. Le gilet claque. Le poulain recule. Sarah s'arrête. Elle dégrafe le bouton. Je ne veux pas qu'il ait peur. On le plie, alors. Tout petit. Papa pose le ballon, loin des sabots. Sarah étale le foin, plat, sans le jeter. Le poulain avance. Son nez touche le foin. Il mange. Il ne court plus. Merci d'avoir retiré le gilet.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;poulain&lt;/emphasis&gt; souffle, près des balançoires, loin du ballon. Sa crinière est en bataille, un peu claire. La voix a dit : agite le gilet, il court. Le gilet claque. Le poulain recule. Sarah s'arrête. Elle dégrafe le bouton. Je ne veux pas qu'il ait peur. On le plie, alors. Tout petit. Papa pose le ballon, loin des sabots. Sarah étale le foin, plat, sans le jeter. Le poulain avance. Son nez touche le foin. Il mange. Il ne court plus. Merci d'avoir retiré le gilet.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Le &lt;emphasis&gt;poulain&lt;/emphasis&gt; souffle, près de les balançoires, loin du ballon. Sa crinière est en bataille, un peu claire. La voix a dit : agite le gilet, il court. Le gilet claque. Le poulain recule. Sarah s'arrête. Elle dégrafe le bouton. Je ne veux pas qu'il ait peur. On le plie, alors. Tout petit. Papa pose le ballon, loin des sabots. Sarah étale le foin, plat, sans le jeter. Le poulain avance. Son nez touche le foin. Il mange. Il ne court plus. Merci d'avoir retiré le gilet. [pause]</t>
+          <t>Le &lt;emphasis&gt;poulain&lt;/emphasis&gt; souffle, près des balançoires, loin du ballon. Sa crinière est en bataille, un peu claire. La voix a dit : agite le gilet, il court. Le gilet claque. Le poulain recule. Sarah s'arrête. Elle dégrafe le bouton. Je ne veux pas qu'il ait peur. On le plie, alors. Tout petit. Papa pose le ballon, loin des sabots. Sarah étale le foin, plat, sans le jeter. Le poulain avance. Son nez touche le foin. Il mange. Il ne court plus. Merci d'avoir retiré le gilet. [pause]</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr"/>
@@ -14329,7 +14322,7 @@
       </c>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Le poulain souffle, près de les balançoires, loin du ballon.
+          <t>narrateur|Le poulain souffle, près des balançoires, loin du ballon.
 narrateur|Sa crinière est en bataille, un peu claire.
 enfant-f|La voix a dit : agite le gilet, il court.
 narrateur|Le gilet claque.
@@ -14951,17 +14944,17 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>La poule s'approche du seau, près de les balançoires. Elle saute un peu. Un grain tombe. La voix a dit de prendre l'œuf, vite. Sarah pose le seau. Elle ne plonge pas. Elle compte les plumes, une, deux, trois. Tu regardes. C'est bien. Derrière le seau, un nid bas, un œuf chaud. Le foin va autour, pas dessus. Ils font un croissant de foin, à distance. Son nid à elle. Le nôtre à côté. La poule picore le bord, puis s'installe. Merci d'avoir posé le seau, pas la main.</t>
+          <t>La poule s'approche du seau, près des balançoires. Elle saute un peu. Un grain tombe. La voix a dit de prendre l'œuf, vite. Sarah pose le seau. Elle ne plonge pas. Elle compte les plumes, une, deux, trois. Tu regardes. C'est bien. Derrière le seau, un nid bas, un œuf chaud. Le foin va autour, pas dessus. Ils font un croissant de foin, à distance. Son nid à elle. Le nôtre à côté. La poule picore le bord, puis s'installe. Merci d'avoir posé le seau, pas la main.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La &lt;emphasis level="moderate"&gt;poule&lt;/emphasis&gt; s'approche du seau, près de les balançoires. Elle saute un peu. Un grain tombe. La voix a dit de prendre l'œuf, vite. Sarah pose le seau. Elle ne plonge pas. Elle compte les plumes, une, deux, trois. Tu regardes. C'est bien. Derrière le seau, un nid bas, un œuf chaud. Le foin va autour, pas dessus. Ils font un croissant de foin, à distance. Son nid à elle. Le nôtre à côté. La poule picore le bord, puis s'installe. Merci d'avoir posé le seau, pas la main.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La &lt;emphasis level="moderate"&gt;poule&lt;/emphasis&gt; s'approche du seau, près des balançoires. Elle saute un peu. Un grain tombe. La voix a dit de prendre l'œuf, vite. Sarah pose le seau. Elle ne plonge pas. Elle compte les plumes, une, deux, trois. Tu regardes. C'est bien. Derrière le seau, un nid bas, un œuf chaud. Le foin va autour, pas dessus. Ils font un croissant de foin, à distance. Son nid à elle. Le nôtre à côté. La poule picore le bord, puis s'installe. Merci d'avoir posé le seau, pas la main.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>La &lt;emphasis&gt;poule&lt;/emphasis&gt; s'approche du seau, près de les balançoires. Elle saute un peu. Un grain tombe. La voix a dit de prendre l'œuf, vite. Sarah pose le seau. Elle ne plonge pas. Elle compte les plumes, une, deux, trois. Tu regardes. C'est bien. Derrière le seau, un nid bas, un œuf chaud. Le foin va autour, pas dessus. Ils font un croissant de foin, à distance. Son nid à elle. Le nôtre à côté. La poule picore le bord, puis s'installe. Merci d'avoir posé le seau, pas la main. [pause]</t>
+          <t>La &lt;emphasis&gt;poule&lt;/emphasis&gt; s'approche du seau, près des balançoires. Elle saute un peu. Un grain tombe. La voix a dit de prendre l'œuf, vite. Sarah pose le seau. Elle ne plonge pas. Elle compte les plumes, une, deux, trois. Tu regardes. C'est bien. Derrière le seau, un nid bas, un œuf chaud. Le foin va autour, pas dessus. Ils font un croissant de foin, à distance. Son nid à elle. Le nôtre à côté. La poule picore le bord, puis s'installe. Merci d'avoir posé le seau, pas la main. [pause]</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr"/>
@@ -15095,7 +15088,7 @@
       </c>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|La poule s'approche du seau, près de les balançoires.
+          <t>narrateur|La poule s'approche du seau, près des balançoires.
 narrateur|Elle saute un peu.
 narrateur|Un grain tombe.
 enfant-f|La voix a dit de prendre l'œuf, vite.
@@ -15330,17 +15323,17 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>La chèvre tire le foin du seau, près de les balançoires. L'anse penche. La clochette s'énerve. La voix a dit de la laisser sortir. Sarah voit le loquet. Elle recule d'un pas. Maman, je n'ouvre pas. Ça me serre. On ferme. On lui donne le foin ici. Papa rabat le loquet. Clic, net. Sarah pose le seau contre la planche. La chèvre mange, le poil chaud, rassuré. Son dîner, pas la porte. Bravo. Tu as fermé la phrase, et le loquet. Un brin de foin reste sur sa barbe.</t>
+          <t>La chèvre tire le foin du seau, près des balançoires. L'anse penche. La clochette s'énerve. La voix a dit de la laisser sortir. Sarah voit le loquet. Elle recule d'un pas. Maman, je n'ouvre pas. Ça me serre. On ferme. On lui donne le foin ici. Papa rabat le loquet. Clic, net. Sarah pose le seau contre la planche. La chèvre mange, le poil chaud, rassuré. Son dîner, pas la porte. La phrase est fermée, et le loquet aussi. Un brin de foin reste sur sa barbe.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La &lt;emphasis level="moderate"&gt;chèvre&lt;/emphasis&gt; tire le foin du seau, près de les balançoires. L'anse penche. La clochette s'énerve. La voix a dit de la laisser sortir. Sarah voit le loquet. Elle recule d'un pas. Maman, je n'ouvre pas. Ça me serre. On ferme. On lui donne le foin ici. Papa rabat le loquet. Clic, net. Sarah pose le seau contre la planche. La chèvre mange, le poil chaud, rassuré. Son dîner, pas la porte. Bravo. Tu as fermé la phrase, et le loquet. Un brin de foin reste sur sa barbe.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La &lt;emphasis level="moderate"&gt;chèvre&lt;/emphasis&gt; tire le foin du seau, près des balançoires. L'anse penche. La clochette s'énerve. La voix a dit de la laisser sortir. Sarah voit le loquet. Elle recule d'un pas. Maman, je n'ouvre pas. Ça me serre. On ferme. On lui donne le foin ici. Papa rabat le loquet. Clic, net. Sarah pose le seau contre la planche. La chèvre mange, le poil chaud, rassuré. Son dîner, pas la porte. La phrase est fermée, et le loquet aussi. Un brin de foin reste sur sa barbe.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>La &lt;emphasis&gt;chèvre&lt;/emphasis&gt; tire le foin du seau, près de les balançoires. L'anse penche. La clochette s'énerve. La voix a dit de la laisser sortir. Sarah voit le loquet. Elle recule d'un pas. Maman, je n'ouvre pas. Ça me serre. On ferme. On lui donne le foin ici. Papa rabat le loquet. Clic, net. Sarah pose le seau contre la planche. La chèvre mange, le poil chaud, rassuré. Son dîner, pas la porte. Bravo. Tu as fermé la phrase, et le loquet. Un brin de foin reste sur sa barbe. [pause]</t>
+          <t>La &lt;emphasis&gt;chèvre&lt;/emphasis&gt; tire le foin du seau, près des balançoires. L'anse penche. La clochette s'énerve. La voix a dit de la laisser sortir. Sarah voit le loquet. Elle recule d'un pas. Maman, je n'ouvre pas. Ça me serre. On ferme. On lui donne le foin ici. Papa rabat le loquet. Clic, net. Sarah pose le seau contre la planche. La chèvre mange, le poil chaud, rassuré. Son dîner, pas la porte. La phrase est fermée, et le loquet aussi. Un brin de foin reste sur sa barbe. [pause]</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr"/>
@@ -15474,7 +15467,7 @@
       </c>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|La chèvre tire le foin du seau, près de les balançoires.
+          <t>narrateur|La chèvre tire le foin du seau, près des balançoires.
 narrateur|L'anse penche.
 narrateur|La clochette s'énerve.
 enfant-f|La voix a dit de la laisser sortir.
@@ -15489,8 +15482,7 @@
 narrateur|Sarah pose le seau contre la planche.
 narrateur|La chèvre mange, le poil chaud, rassuré.
 enfant-f|Son dîner, pas la porte.
-papa|Bravo.
-papa|Tu as fermé la phrase, et le loquet.
+papa|La phrase est fermée, et le loquet aussi.
 narrateur|Un brin de foin reste sur sa barbe.</t>
         </is>
       </c>
@@ -15710,17 +15702,17 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Le poulain renifle le seau, près de les balançoires. Le gilet claque au vent. Il recule. La voix a dit de faire peur, pour rire. Rire, là, ça me serre. Sarah enlève le gilet. Elle le tend à maman. Je le tiens, plié, contre moi. Papa pose le seau. Le foin dépasse, calme. Le poulain revient. Son souffle est chaud. Il croque. Une paille d'or bouge sur sa lèvre. J'ai dit le rire. Puis je l'ai arrêté. Bravo. Il mange, sans courir. Le seau reste, vide, comme une auge.</t>
+          <t>Le poulain renifle le seau, près des balançoires. Le gilet claque au vent. Il recule. La voix a dit de faire peur, pour rire. Rire, là, ça me serre. Sarah enlève le gilet. Elle le tend à maman. Je le tiens, plié, contre moi. Papa pose le seau. Le foin dépasse, calme. Le poulain revient. Son souffle est chaud. Il croque. Une paille d'or bouge sur sa lèvre. J'ai dit le rire. Puis je l'ai arrêté. Il mange, sans courir. Le seau reste, vide, comme une auge.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;poulain&lt;/emphasis&gt; renifle le seau, près de les balançoires. Le gilet claque au vent. Il recule. La voix a dit de faire peur, pour rire. Rire, là, ça me serre. Sarah enlève le gilet. Elle le tend à maman. Je le tiens, plié, contre moi. Papa pose le seau. Le foin dépasse, calme. Le poulain revient. Son souffle est chaud. Il croque. Une paille d'or bouge sur sa lèvre. J'ai dit le rire. Puis je l'ai arrêté. Bravo. Il mange, sans courir. Le seau reste, vide, comme une auge.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le &lt;emphasis level="moderate"&gt;poulain&lt;/emphasis&gt; renifle le seau, près des balançoires. Le gilet claque au vent. Il recule. La voix a dit de faire peur, pour rire. Rire, là, ça me serre. Sarah enlève le gilet. Elle le tend à maman. Je le tiens, plié, contre moi. Papa pose le seau. Le foin dépasse, calme. Le poulain revient. Son souffle est chaud. Il croque. Une paille d'or bouge sur sa lèvre. J'ai dit le rire. Puis je l'ai arrêté. Il mange, sans courir. Le seau reste, vide, comme une auge.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Le &lt;emphasis&gt;poulain&lt;/emphasis&gt; renifle le seau, près de les balançoires. Le gilet claque au vent. Il recule. La voix a dit de faire peur, pour rire. Rire, là, ça me serre. Sarah enlève le gilet. Elle le tend à maman. Je le tiens, plié, contre moi. Papa pose le seau. Le foin dépasse, calme. Le poulain revient. Son souffle est chaud. Il croque. Une paille d'or bouge sur sa lèvre. J'ai dit le rire. Puis je l'ai arrêté. Bravo. Il mange, sans courir. Le seau reste, vide, comme une auge. [pause]</t>
+          <t>Le &lt;emphasis&gt;poulain&lt;/emphasis&gt; renifle le seau, près des balançoires. Le gilet claque au vent. Il recule. La voix a dit de faire peur, pour rire. Rire, là, ça me serre. Sarah enlève le gilet. Elle le tend à maman. Je le tiens, plié, contre moi. Papa pose le seau. Le foin dépasse, calme. Le poulain revient. Son souffle est chaud. Il croque. Une paille d'or bouge sur sa lèvre. J'ai dit le rire. Puis je l'ai arrêté. Il mange, sans courir. Le seau reste, vide, comme une auge. [pause]</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr"/>
@@ -15854,7 +15846,7 @@
       </c>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Le poulain renifle le seau, près de les balançoires.
+          <t>narrateur|Le poulain renifle le seau, près des balançoires.
 narrateur|Le gilet claque au vent.
 narrateur|Il recule.
 enfant-f|La voix a dit de faire peur, pour rire.
@@ -15870,7 +15862,6 @@
 narrateur|Une paille d'or bouge sur sa lèvre.
 enfant-f|J'ai dit le rire.
 enfant-f|Puis je l'ai arrêté.
-papa|Bravo.
 papa|Il mange, sans courir.
 narrateur|Le seau reste, vide, comme une auge.</t>
         </is>
@@ -16478,17 +16469,17 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>La poule frôle le doudou, près de les balançoires. Elle tire un fil gris, puis recule. La voix a dit : cache l'œuf dans le doudou. Sarah serre le doudou. Son ventre dit non. L'œuf n'est pas à cacher. Elle pose le doudou. Elle se penche. Un nid d'herbe, un œuf, tout près du bois. Le doudou veille, loin des pattes. Le foin fait un mur bas, pour le vent. Je n'ai rien pris. J'ai dit. La poule s'installe. L'œuf reste à elle. On a deux nids, et zéro secret lourd.</t>
+          <t>La poule frôle le doudou, près des balançoires. Elle tire un fil gris, puis recule. La voix a dit : cache l'œuf dans le doudou. Sarah serre le doudou. Son ventre dit non. L'œuf n'est pas à cacher. Elle pose le doudou. Elle se penche. Un nid d'herbe, un œuf, tout près du bois. Le doudou veille, loin des pattes. Le foin fait un mur bas, pour le vent. Je n'ai rien pris. J'ai dit. La poule s'installe. L'œuf reste à elle. On a deux nids, et zéro secret lourd.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La &lt;emphasis level="moderate"&gt;poule&lt;/emphasis&gt; frôle le doudou, près de les balançoires. Elle tire un fil gris, puis recule. La voix a dit : cache l'œuf dans le doudou. Sarah serre le doudou. Son ventre dit non. L'œuf n'est pas à cacher. Elle pose le doudou. Elle se penche. Un nid d'herbe, un œuf, tout près du bois. Le doudou veille, loin des pattes. Le foin fait un mur bas, pour le vent. Je n'ai rien pris. J'ai dit. La poule s'installe. L'œuf reste à elle. On a deux nids, et zéro secret lourd.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La &lt;emphasis level="moderate"&gt;poule&lt;/emphasis&gt; frôle le doudou, près des balançoires. Elle tire un fil gris, puis recule. La voix a dit : cache l'œuf dans le doudou. Sarah serre le doudou. Son ventre dit non. L'œuf n'est pas à cacher. Elle pose le doudou. Elle se penche. Un nid d'herbe, un œuf, tout près du bois. Le doudou veille, loin des pattes. Le foin fait un mur bas, pour le vent. Je n'ai rien pris. J'ai dit. La poule s'installe. L'œuf reste à elle. On a deux nids, et zéro secret lourd.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>La &lt;emphasis&gt;poule&lt;/emphasis&gt; frôle le doudou, près de les balançoires. Elle tire un fil gris, puis recule. La voix a dit : cache l'œuf dans le doudou. Sarah serre le doudou. Son ventre dit non. L'œuf n'est pas à cacher. Elle pose le doudou. Elle se penche. Un nid d'herbe, un œuf, tout près du bois. Le doudou veille, loin des pattes. Le foin fait un mur bas, pour le vent. Je n'ai rien pris. J'ai dit. La poule s'installe. L'œuf reste à elle. On a deux nids, et zéro secret lourd. [pause]</t>
+          <t>La &lt;emphasis&gt;poule&lt;/emphasis&gt; frôle le doudou, près des balançoires. Elle tire un fil gris, puis recule. La voix a dit : cache l'œuf dans le doudou. Sarah serre le doudou. Son ventre dit non. L'œuf n'est pas à cacher. Elle pose le doudou. Elle se penche. Un nid d'herbe, un œuf, tout près du bois. Le doudou veille, loin des pattes. Le foin fait un mur bas, pour le vent. Je n'ai rien pris. J'ai dit. La poule s'installe. L'œuf reste à elle. On a deux nids, et zéro secret lourd. [pause]</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr"/>
@@ -16622,7 +16613,7 @@
       </c>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|La poule frôle le doudou, près de les balançoires.
+          <t>narrateur|La poule frôle le doudou, près des balançoires.
 narrateur|Elle tire un fil gris, puis recule.
 enfant-f|La voix a dit : cache l'œuf dans le doudou.
 narrateur|Sarah serre le doudou.
@@ -16858,17 +16849,17 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>La chèvre mâchonne le doudou, près de les balançoires. Un fil gris pend à sa lèvre. Non ! Il n'est pas à manger ! Sarah tend la main, trop vite, trop près. Elle s'arrête. Elle appelle. Papa, le doudou. La voix a dit : laisse-la. On échange. Du foin contre le doudou. Maman tend le foin. La chèvre lâche le fil. Sarah reprend le doudou, un peu mouillé. J'ai demandé, au lieu de tirer. Merci. Le loquet, on le vérifie aussi. Clic. La clochette redevient petite.</t>
+          <t>La chèvre mâchonne le doudou, près des balançoires. Un fil gris pend à sa lèvre. Non ! Il n'est pas à manger ! Sarah tend la main, trop vite, trop près. Elle s'arrête. Elle appelle. Papa, le doudou. La voix a dit : laisse-la. On échange. Du foin contre le doudou. Maman tend le foin. La chèvre lâche le fil. Sarah reprend le doudou, un peu mouillé. J'ai demandé, au lieu de tirer. Merci. Le loquet, on le vérifie aussi. Clic. La clochette redevient petite.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La &lt;emphasis level="moderate"&gt;chèvre&lt;/emphasis&gt; mâchonne le doudou, près de les balançoires. Un fil gris pend à sa lèvre. Non ! Il n'est pas à manger ! Sarah tend la main, trop vite, trop près. Elle s'arrête. Elle appelle. Papa, le doudou. La voix a dit : laisse-la. On échange. Du foin contre le doudou. Maman tend le foin. La chèvre lâche le fil. Sarah reprend le doudou, un peu mouillé. J'ai demandé, au lieu de tirer. Merci. Le loquet, on le vérifie aussi. Clic. La clochette redevient petite.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La &lt;emphasis level="moderate"&gt;chèvre&lt;/emphasis&gt; mâchonne le doudou, près des balançoires. Un fil gris pend à sa lèvre. Non ! Il n'est pas à manger ! Sarah tend la main, trop vite, trop près. Elle s'arrête. Elle appelle. Papa, le doudou. La voix a dit : laisse-la. On échange. Du foin contre le doudou. Maman tend le foin. La chèvre lâche le fil. Sarah reprend le doudou, un peu mouillé. J'ai demandé, au lieu de tirer. Merci. Le loquet, on le vérifie aussi. Clic. La clochette redevient petite.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>La &lt;emphasis&gt;chèvre&lt;/emphasis&gt; mâchonne le doudou, près de les balançoires. Un fil gris pend à sa lèvre. Non ! Il n'est pas à manger ! Sarah tend la main, trop vite, trop près. Elle s'arrête. Elle appelle. Papa, le doudou. La voix a dit : laisse-la. On échange. Du foin contre le doudou. Maman tend le foin. La chèvre lâche le fil. Sarah reprend le doudou, un peu mouillé. J'ai demandé, au lieu de tirer. Merci. Le loquet, on le vérifie aussi. Clic. La clochette redevient petite. [pause]</t>
+          <t>La &lt;emphasis&gt;chèvre&lt;/emphasis&gt; mâchonne le doudou, près des balançoires. Un fil gris pend à sa lèvre. Non ! Il n'est pas à manger ! Sarah tend la main, trop vite, trop près. Elle s'arrête. Elle appelle. Papa, le doudou. La voix a dit : laisse-la. On échange. Du foin contre le doudou. Maman tend le foin. La chèvre lâche le fil. Sarah reprend le doudou, un peu mouillé. J'ai demandé, au lieu de tirer. Merci. Le loquet, on le vérifie aussi. Clic. La clochette redevient petite. [pause]</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr"/>
@@ -17002,7 +16993,7 @@
       </c>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|La chèvre mâchonne le doudou, près de les balançoires.
+          <t>narrateur|La chèvre mâchonne le doudou, près des balançoires.
 narrateur|Un fil gris pend à sa lèvre.
 enfant-f|Non !
 enfant-f|Il n'est pas à manger !
@@ -17612,7 +17603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A16"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -17725,6 +17716,13 @@
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
